--- a/mistral_translate_work/split_by_prompt/excel/skill_description/lang_multi_text/lang_multi_text__skill_description__part_0012.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/skill_description/lang_multi_text/lang_multi_text__skill_description__part_0012.xlsx
@@ -575,8 +575,8 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Sau khi Triệu Hồi Combat Machines, {Cus:Ipt,Touch=tap PC=click Gamepad=press} Bắt Đầu để khởi động mô phỏng. Discord sẽ di chuyển theo tuyến đường đã định.
-Nếu Discord chạm tới Energy Matrix, chúng sẽ làm giảm Độ Bền của nó. Mức độ suy giảm tùy thuộc vào loại Discord. Mô phỏng thất bại nếu Độ Bền giảm về 0.</t>
+          <t>Sau khi Triệu Hồi Máy Chiến Đấu, {Cus:Ipt,Touch=tap PC=click Gamepad=press} Bắt Đầu để khởi động mô phỏng. Tacet Discord sẽ di chuyển theo tuyến đường đã định.
+Nếu Tacet Discord chạm tới Ma Trận Năng Lượng, chúng sẽ làm giảm Độ Bền của nó. Mức độ suy giảm tùy thuộc vào loại Tacet Discord. Mô phỏng thất bại nếu Độ Bền giảm về 0.</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Trong Bài Kiểm Tra Phòng Thủ Total Lực của Chế Độ Bẫy Chết, Tacet Discord sẽ không ngừng tấn công và trở nên mạnh mẽ hơn sau mỗi đợt. Hãy chống trả dòng thù địch bất tận và cố gắng lập kỷ lục đợt cao nhất của riêng mình!</t>
+          <t>Trong Bài Kiểm Tra Phòng Thủ Tổng Lực của Chế Độ Bẫy Chết, Tacet Discord sẽ không ngừng tấn công và trở nên mạnh mẽ hơn sau mỗi đợt. Hãy chống trả dòng thù địch bất tận và cố gắng lập kỷ lục đợt cao nhất của riêng mình!</t>
         </is>
       </c>
     </row>
@@ -773,7 +773,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Sử dụng các Thiết bị Combat có hiệu ứng đẩy lùi và KU-Roro's Weapons để đẩy Tacet Discord ra khỏi rìa, tiêu diệt chúng ngay lập tức. Tacet Discord bị đánh bại theo cách này sẽ không kích hoạt hiệu ứng Âm Thanh Tử Thần.</t>
+          <t>Sử dụng các Thiết bị Chiến Đấu có hiệu ứng đẩy lùi và Vũ khí của KU-Roro để đẩy Tacet Discord ra khỏi rìa, tiêu diệt chúng ngay lập tức. Tacet Discord bị đánh bại theo cách này sẽ không kích hoạt hiệu ứng Âm Thanh Tử Thần.</t>
         </is>
       </c>
     </row>
@@ -970,9 +970,9 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;Frequency Neutralizer&lt;/color&gt; loại bỏ Nhiễm Tần Số.
-Khi &lt;color=#ffd12f&gt;carrying&lt;/color&gt; Frequency Neutralizer, cậu có thể triển khai Combat Machines đến các khu vực bị nhiễm. Hệ thống sẽ &lt;color=#ffd12f&gt;automatically consume&lt;/color&gt; số lượng Frequency Neutralizer cần thiết cho việc triển khai.
-Một số Combat Machines cũng có thể làm sạch nhiễm bẩn bằng các Mô-đun Tùy Chọn của chúng.</t>
+          <t>&lt;color=#ffd12f&gt;Bộ Trung Hòa Tần Số&lt;/color&gt; loại bỏ Nhiễm Tần Số.
+Khi &lt;color=#ffd12f&gt;mang theo&lt;/color&gt; Bộ Trung Hòa Tần Số, cậu có thể triển khai Máy Chiến Đấu đến các khu vực bị nhiễm. Hệ thống sẽ &lt;color=#ffd12f&gt;tự động tiêu thụ&lt;/color&gt; số lượng Bộ Trung Hòa Tần Số cần thiết cho việc triển khai.
+Một số Máy Chiến Đấu cũng có thể làm sạch nhiễm bẩn bằng các Mô-đun Tùy Chọn của chúng.</t>
         </is>
       </c>
     </row>
@@ -1038,8 +1038,8 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Khi Tacet Discord tiếp cận Energy Matrix, chúng sẽ làm giảm Độ Bền của nó dựa trên lượng sát thương gây ra. Các loại Tacet Discord khác nhau gây ra lượng sát thương khác nhau.
-Tacet Discord cấp tinh nhuệ và nguy hiểm gây ra &lt;color=#ffd12f&gt;extremely high DMG&lt;/color&gt; và có thể làm giảm đáng kể Độ Bền của Ma Trận. Cần phải xử lý chúng một cách cẩn thận.</t>
+          <t>Khi Tacet Discord tiếp cận Ma Trận Năng Lượng, chúng sẽ làm giảm Độ Bền của nó dựa trên lượng DMG gây ra. Các loại Tacet Discord khác nhau gây ra lượng DMG khác nhau.
+Tacet Discord cấp tinh nhuệ và nguy hiểm gây ra &lt;color=#ffd12f&gt;DMG cực cao&lt;/color&gt; và có thể làm giảm đáng kể Độ Bền của Ma Trận. Cần phải xử lý chúng một cách cẩn thận.</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Throw {0} Lưỡi Dao Lông vào mục tiêu để di chuyển nhanh</t>
+          <t>Ném Lưỡi Kiếm Lông vào mục tiêu để di chuyển nhanh {0}</t>
         </is>
       </c>
     </row>
@@ -1169,7 +1169,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>{0} Nắm bắt khoảnh khắc "thế giới" chuyển đổi để tung ra đòn kết liễu và tiêu diệt kẻ địch phía trước</t>
+          <t>{0} Nắm bắt khoảnh khắc "thế giới" chuyển đổi để tung đòn kết liễu và tiêu diệt kẻ địch phía trước.</t>
         </is>
       </c>
     </row>
@@ -1234,7 +1234,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Weapons sẽ tự động tấn công. Kẻ địch bị đánh bại sẽ rơi ra Mô-đun Tăng Cường, hãy đến gần để thu thập.</t>
+          <t>Vũ khí sẽ tự động tấn công. Kẻ địch bị đánh bại sẽ rơi ra Mô-đun Tăng Cường, hãy đến gần để thu thập.</t>
         </is>
       </c>
     </row>
@@ -1299,7 +1299,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Weapons sẽ tự động tấn công. Kẻ địch bị đánh bại sẽ rơi ra Mô-đun Tăng Cường, hãy đến gần để thu thập.</t>
+          <t>Vũ khí sẽ tự động tấn công. Kẻ địch bị đánh bại sẽ rơi ra Mô-đun Tăng Cường, hãy đến gần để thu thập.</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Weapons sẽ tự động tấn công. Kẻ địch bị đánh bại sẽ rơi ra Mô-đun Tăng Cường, hãy đến gần để thu thập.</t>
+          <t>Vũ khí sẽ tự động tấn công. Kẻ địch bị đánh bại sẽ rơi ra Mô-đun Tăng Cường, hãy đến gần để thu thập.</t>
         </is>
       </c>
     </row>
@@ -1495,7 +1495,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>"Băng cassette" của Galbrena giúp ổn định tần số của bạn. Concerto Energy và Concerto Energy sẽ tăng dần khi nó phát.
+          <t>"Băng cassette" của Galbrena giúp ổn định tần số của bạn. Năng Lượng Giao Hưởng và Concerto Energy sẽ tăng dần khi nó phát.
 Nắm bắt cơ hội này để chiến đấu và thoát ra.</t>
         </is>
       </c>
@@ -1627,7 +1627,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Galbrena thấm đẫm sức mạnh của Ác Quỷ Shadow vào Lưỡi Dao Feather. Khi nhắm và Dodgem chúng vào một điểm, cô sẽ di chuyển tức thì đến vị trí đó.
+          <t>Galbrena thấm đẫm sức mạnh của Ác Quỷ Bóng Tối vào Lưỡi Dao Lông Vũ. Khi nhắm và ném chúng vào một điểm, cô sẽ di chuyển tức thì đến vị trí đó.
 Nếu có kẻ địch tại điểm đích, cô sẽ tiêu diệt chúng ngay trong lúc di chuyển.</t>
         </is>
       </c>
@@ -1760,7 +1760,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Trong khu vực này, tổng Sát Thương của Resonators sẽ tăng dần theo thời gian. Đánh trúng, Dodge Phản Công hoặc Phản Đòn sẽ tăng tổng Sát Thương trong thời gian ngắn.</t>
+          <t>Trong khu vực này, tổng Sát Thương của Resonator sẽ tăng dần theo thời gian. Đánh trúng, Né Tránh Phản Công hoặc Phản Đòn sẽ tăng tổng Sát Thương trong thời gian ngắn.</t>
         </is>
       </c>
     </row>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Một số vũ khí có thể bị hấp thụ để tiến hóa vũ khí khác thành Ultimate Form. Yêu cầu tiến hóa sẽ khác nhau tùy vào từng Vũ Khí. Weapons sau tiến hóa sẽ kế thừa tất cả hiệu ứng tăng cường của vũ khí bị hấp thụ.</t>
+          <t>Một số vũ khí có thể bị hấp thụ để tiến hóa vũ khí khác thành Hình Thái Tối Thượng. Yêu cầu tiến hóa sẽ khác nhau tùy vào từng Vũ Khí. Vũ khí sau tiến hóa sẽ kế thừa tất cả hiệu ứng tăng cường của vũ khí bị hấp thụ.</t>
         </is>
       </c>
     </row>
@@ -1891,8 +1891,8 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Trong Helltide Mode, trận chiến cuối cùng không giới hạn thời gian. Mũi khoan chỉ dừng lại khi Resonator bị đánh bại hoặc khi tất cả TD bị tiêu diệt.
-TD sẽ liên tục xuất hiện, trong khi HP và Tấn Công của cả hai bên đều tăng định kỳ.</t>
+          <t>Trong Chế Độ Hỏa Ngục, trận chiến cuối cùng không giới hạn thời gian. Mũi khoan chỉ dừng lại khi Resonator bị đánh bại hoặc khi tất cả TD bị tiêu diệt.
+TD sẽ liên tục xuất hiện, trong khi HP và ATK của cả hai bên đều tăng định kỳ.</t>
         </is>
       </c>
     </row>
@@ -1957,7 +1957,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Đánh bại Elite cuối cùng trong một đợt sẽ ngay lập tức hoàn thành đợt đó. Sống sót đến khi hết thời gian cũng sẽ hoàn thành đợt.</t>
+          <t>Đánh bại Tinh Anh cuối cùng trong một đợt sẽ ngay lập tức hoàn thành đợt đó. Sống sót đến khi hết thời gian cũng sẽ hoàn thành đợt.</t>
         </is>
       </c>
     </row>
@@ -2090,10 +2090,10 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Vật phẩm xuất hiện khi tiêu diệt một số Echo nhất định, đạt đủ số đợt sóng hoặc tại các vị trí cụ thể trên bãi diễn tập. Nhặt chúng để nhận hiệu ứng tức thì:
+          <t>Vật phẩm xuất hiện khi tiêu diệt một số Tổ Tacet nhất định, đạt đủ số đợt sóng hoặc tại các vị trí cụ thể trên bãi diễn tập. Nhặt chúng để nhận hiệu ứng tức thì:
 - Từ tính: Tự động thu thập tất cả Mô-đun Tăng Cường trong phạm vi.
-- Restore: Khôi phục 20% HP tối đa.
-- Cuồng nộ: Tăng mạnh Sát Thương, Movement Speed và Attack Speed trong 10 giây.</t>
+- Hồi phục: Khôi phục 20% HP tối đa.
+- Cuồng nộ: Tăng mạnh Sát Thương, Tốc Độ Di Chuyển và Tốc Độ Tấn Công trong 10 giây.</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>{0} Aim vào kẻ địch để tấn công và tiêu diệt chúng</t>
+          <t>Ngắm vào kẻ địch để tấn công và tiêu diệt chúng.</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>{0} Nhắm vào kẻ địch để tấn công và tiêu diệt chúng</t>
+          <t>Ngắm vào kẻ địch để tấn công và tiêu diệt chúng.</t>
         </is>
       </c>
     </row>
@@ -2288,7 +2288,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Aim vào kẻ địch để tấn công và tiêu diệt chúng.</t>
+          <t>Ngắm vào kẻ địch để tấn công và tiêu diệt chúng.</t>
         </is>
       </c>
     </row>
@@ -2364,16 +2364,16 @@
       <c r="M29" t="inlineStr">
         <is>
           <t>Về sự kiện
-Khi dự án Tactical Simulacra tiến triển, Huaxu Academy đã thành công trong việc đo lường Tính Điều Chỉnh – thuộc tính giúp vô số Reverberation hội tụ thành Tacet Discord. Phá vỡ Tính Điều Chỉnh của chúng đồng nghĩa với đòn chí mạng khiến chúng tê liệt...
+Khi dự án Tactical Simulacra tiến triển, Học viện Huaxu đã thành công trong việc đo lường Tính Điều Chỉnh – thuộc tính giúp vô số Reverberation hội tụ thành Tacet Discord. Phá vỡ Tính Điều Chỉnh của chúng đồng nghĩa với đòn chí mạng khiến chúng tê liệt...
 Điều kiện tham gia
 Đạt Cấp Liên Minh 14.
 Quy tắc sự kiện
 1. Trong Tactical Simulacra: Off Tune, hãy đối đầu với làn sóng kẻ địch mạnh mẽ bằng các hiệu ứng đặc biệt trên các miền mô phỏng khác nhau.
 2. Hoàn thành càng nhiều thử thách, bạn sẽ mở khóa thêm các hiệu ứng đặc biệt mới cho các thử thách tiếp theo.
-3. Kết quả mỗi thử thách sẽ được tính dựa trên Points Quái Vật, Time Points và Technical Points.
-i. Points Quái Vật đạt được khi đánh bại kẻ địch trong thử thách.
-ii. Time Points dựa trên thời gian còn lại khi hoàn thành thử thách và hệ số chuyển đổi tăng theo số lượng kẻ địch bị tiêu diệt.
-iii. Technical Points đạt được khi kích hoạt Phản Đòn, Dodge thành công và Dodge Phản Đòn.</t>
+3. Kết quả mỗi thử thách sẽ được tính dựa trên Điểm Quái Vật, Điểm Thời Gian và Điểm Kỹ Thuật.
+i. Điểm Quái Vật đạt được khi đánh bại kẻ địch trong thử thách.
+ii. Điểm Thời Gian dựa trên thời gian còn lại khi hoàn thành thử thách và hệ số chuyển đổi tăng theo số lượng kẻ địch bị tiêu diệt.
+iii. Điểm Kỹ Thuật đạt được khi kích hoạt Phản Đòn, Né Tránh thành công và Né Tránh Phản Đòn.</t>
         </is>
       </c>
     </row>
@@ -2446,9 +2446,9 @@
       <c r="M30" t="inlineStr">
         <is>
           <t>[Giới Thiệu]
-Để khuyến khích các Tiên Phong chia sẻ thêm về những chuyến thám hiểm Lahai-Roi, Lollo Logistics đã hợp tác với Pioneer Association hân hạnh giới thiệu chiến dịch: Vượt Sóng! Tham gia và tải Nhật Ký Phiêu Lưu của bạn lên xe chuyển phát Lollo để nhận nhiều phần thưởng hấp dẫn!
+Để khuyến khích các Tiên Phong chia sẻ thêm về những chuyến thám hiểm Lahai-Roi, Lollo Logistics đã hợp tác với Hiệp Hội Tiên Phong hân hạnh giới thiệu chiến dịch: Vượt Sóng! Tham gia và tải Nhật Ký Phiêu Lưu của bạn lên xe chuyển phát Lollo để nhận nhiều phần thưởng hấp dẫn!
 [Điều Kiện Tham Gia]
-Đạt Cấp Liên Minh 14 và kích hoạt Nexus Resonance tại Học Viện Startorch trong Nhiệm Vụ Chính "Ngọn Lửa Dưới Băng Giá" để mở khóa.
+Đạt Cấp Liên Minh 14 và kích hoạt Nexus Cộng Hưởng tại Học Viện Startorch trong Nhiệm Vụ Chính "Ngọn Lửa Dưới Băng Giá" để mở khóa.
 [Thể Lệ Sự Kiện]
 Trong thời gian diễn ra sự kiện, bạn có thể hoàn thành các nhiệm vụ sự kiện mỗi ngày một lần để nhận được một số lượng Nhật Ký Phiêu Lưu nhất định.
 Mỗi Nhật Ký Phiêu Lưu có thể đổi lấy một Gói Phiêu Lưu; Gói Phiêu Lưu chứa cơ chế đặc biệt, khi kích hoạt sẽ mở khóa một lượng lớn phần thưởng.
@@ -2541,7 +2541,7 @@
           <t>[Doubled Pawns Matrix: Pilot]
 Trong Doubled Pawns Matrix: Pilot, kỹ năng của bạn sẽ được thử thách qua nhiều giai đoạn khó khăn. Đối đầu với kẻ địch và kiếm điểm để nhận những phần thưởng tương ứng.
 [Điều Kiện Tham Gia]
-Đạt ít nhất 24 Huy Hiệu trong một giai đoạn của Tower of Adversity và đạt ít nhất 3.500 điểm trong một giai đoạn của Dòng Nước Hồi Sinh: Thác Nước Trong Whimpering Wastes tại Whimpering Wastes sau khi phiên bản 3.0 ra mắt.
+Đạt ít nhất 24 Huy Hiệu trong một giai đoạn của Tháp Nghịch Cảnh và đạt ít nhất 3.500 điểm trong một giai đoạn của Dòng Nước Hồi Sinh: Thác Nước Trong Vùng Đất Than Khóc tại Whimpering Wastes sau khi phiên bản 3.0 ra mắt.
 [Ma Trận]
 Doubled Pawns Matrix: Pilot gồm hai Khu Vực: Stability Accords và Singularity Expansion. Kiếm đủ điểm yêu cầu trong Stability Accords để mở khóa Singularity Expansion.
 [Stability Accords]
@@ -2549,17 +2549,17 @@
 [Singularity Expansion]
 Không giới hạn số đội bạn có thể triển khai. Đánh bại tất cả kẻ địch trong một vòng sẽ mở vòng tiếp theo, với kẻ địch ngày càng mạnh hơn.
 [Power Circuits]
-Trong Doubled Pawns Matrix: Pilot, mỗi đội phải triển khai ba Resonators và chọn một Power Circuit trước khi bắt đầu thử thách.
+Trong Doubled Pawns Matrix: Pilot, mỗi đội phải triển khai ba Resonator và chọn một Power Circuit trước khi bắt đầu thử thách.
 [Demo Resonators]
-Demo Resonators chỉ khả dụng nếu bạn sở hữu Resonators tương ứng. Mỗi Demo Resonators được đặt ở cấp 90, trang bị vũ khí cấp 90 và bộ Echoes phù hợp với Echoes cấp 25. Họ kế thừa Resonance Chain từ Resonators của bạn.
-[Resonators Enhancements]
-Trong Doubled Pawns Matrix: Pilot, một số Resonators sẽ nhận được tăng cường kỹ năng đặc biệt.
+Demo Resonators chỉ khả dụng nếu bạn sở hữu Resonator tương ứng. Mỗi Demo Resonator được đặt ở cấp 90, trang bị vũ khí cấp 90 và bộ Echo phù hợp với Echo cấp 25. Họ kế thừa Resonance Chain từ Resonator của bạn.
+[Tăng Cường Resonator]
+Trong Doubled Pawns Matrix: Pilot, một số Resonator sẽ nhận được tăng cường kỹ năng đặc biệt.
 [Viral Infection]
 Trong Singularity Expansion, HP của kẻ địch tăng theo từng vòng, và các hiệu ứng kẻ địch mạnh hơn sẽ được mở khóa khi vòng đấu tiến triển.
 [Vigor]
-Mỗi lần một Resonators tham gia thử thách, 1 điểm Vigor sẽ bị tiêu hao. Resonators với 0 Vigor không thể được triển khai. Vigor được tính riêng cho Stability Accords và Singularity Expansion.
-[Weapon &amp; Echoes Occupation]
-Các Resonators khác nhau không thể sử dụng cùng một vũ khí và Echoes trong sự kiện này. Nếu một Resonators trong đội đã trang bị vũ khí hoặc Echoes mà một Resonators khác đã sử dụng trong thử thách trước đó, bạn không thể bắt đầu thử thách với đội này.</t>
+Mỗi lần một Resonator tham gia thử thách, 1 điểm Vigor sẽ bị tiêu hao. Resonator với 0 Vigor không thể được triển khai. Vigor được tính riêng cho Stability Accords và Singularity Expansion.
+[Weapon &amp; Echo Occupation]
+Các Resonator khác nhau không thể sử dụng cùng một vũ khí và Echo trong sự kiện này. Nếu một Resonator trong đội đã trang bị vũ khí hoặc Echo mà một Resonator khác đã sử dụng trong thử thách trước đó, bạn không thể bắt đầu thử thách với đội này.</t>
         </is>
       </c>
     </row>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Độ ổn định sẽ giảm khi bị Tacet Discord tấn công dưới ảnh hưởng của Dư Âm Than Khóc. Nếu &lt;color=#ffd12f&gt;all Stability is lost&lt;/color&gt;, &lt;color=#ffd12f&gt;the exploration will be terminated&lt;/color&gt;, và toàn bộ vật phẩm trong Storage Bag sẽ bị mất.</t>
+          <t>Độ ổn định sẽ giảm khi bị Tacet Discord tấn công dưới ảnh hưởng của Dư Âm Than Khóc. Nếu &lt;color=#ffd12f&gt;mất hết độ ổn định&lt;/color&gt;, &lt;color=#ffd12f&gt;cuộc thám hiểm sẽ bị chấm dứt&lt;/color&gt;, và toàn bộ vật phẩm trong Túi Lưu Trữ sẽ bị mất.</t>
         </is>
       </c>
     </row>
@@ -2689,7 +2689,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Nước Lấp Lánh có thể tìm thấy khắp Honami City. Phá vỡ chúng để khôi phục một phần Độ Stability và HP.</t>
+          <t>Nước Lấp Lánh có thể tìm thấy khắp Thành Phố Honami. Phá vỡ chúng để khôi phục một phần Độ Ổn Định và HP.</t>
         </is>
       </c>
     </row>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Do dư lượng Lament, các Echo ở Honami City sẽ ngày càng nguy hiểm theo thời gian, và kẻ địch sẽ gây Sát Thương Stability cao hơn. Hãy chú ý thời gian đã trôi qua trong quá trình khám phá.</t>
+          <t>Do dư lượng Lament, các Tổ Tacet ở Thành phố Honami sẽ ngày càng nguy hiểm theo thời gian, và kẻ địch sẽ gây Sát Thương Ổn Định cao hơn. Hãy chú ý thời gian đã trôi qua trong quá trình khám phá.</t>
         </is>
       </c>
     </row>
@@ -2887,10 +2887,10 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Một số đòn tấn công của cậu sẽ tích lũy Mức Độ Mistune cho kẻ địch nhất định.
-Khi Mức Độ Mistune đạt giới hạn, chúng sẽ rơi vào trạng thái Mistune.
-Trong trạng thái này, cậu có thể tung ra một đòn Tune Break cực mạnh để phá vỡ phòng thủ của chúng.
-Thực hiện thành công Tune Break sẽ đặt lại Mức Độ Mistune của kẻ địch và gây ra Tune Disruption, khiến chúng dễ bị tổn thương trước các đòn tấn công tiếp theo.</t>
+          <t>Một số đòn tấn công của cậu sẽ tích lũy Mức Độ Lệch Tần cho kẻ địch nhất định.
+Khi Mức Độ Lệch Tần đạt giới hạn, chúng sẽ rơi vào trạng thái Lệch Tần.
+Trong trạng thái này, cậu có thể tung ra một đòn Phá Tần cực mạnh để phá vỡ phòng thủ của chúng.
+Thực hiện thành công Phá Tần sẽ đặt lại Mức Độ Lệch Tần của kẻ địch và gây ra Rối Loạn Tần Số, khiến chúng dễ bị tổn thương trước các đòn tấn công tiếp theo.</t>
         </is>
       </c>
     </row>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Khi kẻ địch sử dụng Kỹ Năng Special (vòng tròn đỏ cảnh báo sẽ xuất hiện), nếu &lt;color=#ffd12f&gt;successfully Dodge or counter&lt;/color&gt;, kẻ địch sẽ ngay lập tức rơi vào trạng thái Mistune. Attack kẻ địch bằng Tune Break trong trạng thái này sẽ không làm reset cấp độ Off-Tune của chúng.</t>
+          <t>Khi kẻ địch sử dụng Kỹ Năng Đặc Biệt (vòng tròn đỏ cảnh báo sẽ xuất hiện), nếu &lt;color=#ffd12f&gt;né tránh hoặc phản công thành công&lt;/color&gt;, kẻ địch sẽ ngay lập tức rơi vào trạng thái Mistune. Tấn công kẻ địch bằng Tune Break trong trạng thái này sẽ không làm reset cấp độ Off-Tune của chúng.</t>
         </is>
       </c>
     </row>
@@ -3020,7 +3020,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Tái thiết mạng lưới tuyến đường Lahai-Roi để tăng Network Activity, giúp nhiều vật tư hơn đến được Spacetrek Observatory và đẩy nhanh quá trình tái thiết nơi đây.</t>
+          <t>Tái thiết mạng lưới tuyến đường Lahai-Roi để tăng Hoạt Động Mạng, giúp nhiều vật tư hơn đến được Đài Thiên Văn Spacetrek và đẩy nhanh quá trình tái thiết nơi đây.</t>
         </is>
       </c>
     </row>
@@ -3096,14 +3096,14 @@
         <is>
           <t>Về hệ thống
 Hệ thống Synchrolink hiện đã trực tuyến trong buồng mô phỏng Exostrider.
-Buồng lái được tích hợp các neuron của Exostrider, được thiết kế để huấn luyện các Đồng Bộ Giả trong trạng thái Resonance Tăng Cường với Exostrider.
+Buồng lái được tích hợp các neuron của Exostrider, được thiết kế để huấn luyện các Đồng Bộ Giả trong trạng thái Cộng Hưởng Tăng Cường với Exostrider.
 Trong quá trình này, Đồng Bộ Giả có thể đo lường và ghi lại mức độ căng thẳng cộng hưởng để đánh giá khả năng thích ứng và ngưỡng tải thần kinh.
 Hoàn thành các mục tiêu huấn luyện để nhận Synchro Coin do Bộ phận cấp, có thể đổi lấy nhiều vật phẩm hiếm và phần thưởng giá trị.
 Điều kiện tham gia
-Đạt Cấp Liên Minh 27 và kích hoạt Resonance Nexus của Startorch Academy trong Nhiệm vụ Main "What Burns Beneath Frostlands".
-Synchro Shop
-Hoàn thành Tactical Hologram: Synchronization để nhận Astrite và Synchro Coin, có thể đổi lấy phần thưởng tại Synchro Shop.
-Tactical Hologram: Synchronization là sự kiện thường trực, có thể trải nghiệm bất cứ lúc nào và sẽ tiếp tục cập nhật trong các phiên bản sau. Hãy theo dõi nhé.</t>
+Đạt Cấp Liên Minh 27 và kích hoạt Resonance Nexus của Học viện Startorch trong Nhiệm vụ Chính "What Burns Beneath Frostlands".
+Cửa hàng Synchro
+Hoàn thành Tactical Hologram: Synchronization to obtain Astrite and Synchro Coins, which can be exchanged for rewards at the Synchro Shop.
+Tactical Hologram: Synchronization is a permanent event that can be experienced at any time and will continue to be updated in future versions. Please stay tuned.</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Ngoài các Sticker phổ thông, Namipon Sticker còn bao gồm những Sticker độc quyền chỉ có hiệu lực với một số Resonators nhất định. Những sticker này có thể thay đổi hình thức kỹ năng hoặc mang lại hiệu ứng mới cho Resonators.</t>
+          <t>Ngoài các Sticker phổ thông, Namipon Sticker còn bao gồm những Sticker độc quyền chỉ có hiệu lực với một số Resonator nhất định. Những sticker này có thể thay đổi hình thức kỹ năng hoặc mang lại hiệu ứng mới cho Resonator.</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Các thử thách Neon Tower gồm ba giai đoạn, nơi anh sẽ đối đầu với những kẻ địch mạnh mẽ liên tiếp. Hạ gục từng kẻ địch để nhận được một lượng lớn Bánh Rice Dango.</t>
+          <t>Các thử thách Tháp Neon gồm ba giai đoạn, nơi anh sẽ đối đầu với những kẻ địch mạnh mẽ liên tiếp. Hạ gục từng kẻ địch để nhận được một lượng lớn Bánh Gạo Dango.</t>
         </is>
       </c>
     </row>
@@ -3298,7 +3298,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Sự ô nhiễm Irideglow bên trong Neon Tower không tăng theo thời gian, nhưng sẽ trở nên dữ dội hơn khi đánh bại kẻ địch.</t>
+          <t>Sự ô nhiễm Irideglow bên trong Tháp Neon không tăng theo thời gian, nhưng sẽ trở nên dữ dội hơn khi đánh bại kẻ địch.</t>
         </is>
       </c>
     </row>
@@ -3363,7 +3363,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Kẻ địch bị tiêu diệt sẽ rơi vật phẩm, khi nhặt lên sẽ được thêm vào Storage Bag của ngươi.</t>
+          <t>Kẻ địch bị tiêu diệt sẽ rơi vật phẩm, khi nhặt lên sẽ được thêm vào Túi Lưu Trữ của ngươi.</t>
         </is>
       </c>
     </row>
@@ -3428,7 +3428,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Kẻ địch bị tiêu diệt sẽ rơi vật phẩm, khi nhặt lên sẽ được thêm vào Storage Bag của ngươi.</t>
+          <t>Kẻ địch bị tiêu diệt sẽ rơi vật phẩm, khi nhặt lên sẽ được thêm vào Túi Lưu Trữ của ngươi.</t>
         </is>
       </c>
     </row>
@@ -3493,7 +3493,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Kẻ địch bị tiêu diệt sẽ rơi vật phẩm, khi nhặt lên sẽ được thêm vào Storage Bag của ngươi.</t>
+          <t>Kẻ địch bị tiêu diệt sẽ rơi vật phẩm, khi nhặt lên sẽ được thêm vào Túi Lưu Trữ của ngươi.</t>
         </is>
       </c>
     </row>
@@ -3566,12 +3566,12 @@
       <c r="M46" t="inlineStr">
         <is>
           <t>Về sự kiện
-Hỡi Rover được thủy triều dẫn lối, ngươi đã vượt qua những đỉnh cao của Jinzhou, lắng nghe sóng vỗ bờ đen tối. Ngươi đã đương đầu với bão tố, nghe thấy bản chất kép của niềm tin Ragunna, và nếm trải vinh quang trên đấu trường Septimont. Giờ đây, con đường đến vùng đất băng giá mở ra tại Honami City. Đã đến lúc lên đường đến Lahai-Roi.
+Hỡi Vận Mệnh Giả được thủy triều dẫn lối, ngươi đã vượt qua những đỉnh cao của Jinzhou, lắng nghe sóng vỗ bờ đen tối. Ngươi đã đương đầu với bão tố, nghe thấy bản chất kép của niềm tin Ragunna, và nếm trải vinh quang trên đấu trường Septimont. Giờ đây, con đường đến vùng đất băng giá mở ra tại Thành phố Honami. Đã đến lúc lên đường đến Lahai-Roi.
 Điều kiện tham gia
-Hãy đến Resonance Nexus ở Jinzhou và mở khóa Terminal trong Nhiệm vụ Main "First Resonance".
+Hãy đến Resonance Nexus ở Jinzhou và mở khóa Thiết bị đầu cuối trong Nhiệm vụ Chính "First Resonance".
 Quy tắc sự kiện
-Chương III của Nhiệm vụ Main hiện đã mở. Người chơi đủ điều kiện có thể trải nghiệm Chương này sớm. Chapters I, II và III hiện có thể chơi song song. Việc tham gia các Chương sau sớm không ảnh hưởng đến tiến trình của các Chương trước, và ngươi luôn có thể tiếp tục các Chương trước từ nơi đã dừng.
-Truy cập sớm Chương II/Chương III cũng mở khóa các chức năng Điều Chỉnh Thời Gian, Chuyển Đổi Resonance, cùng một số Công cụ khác.
+Chương III của Nhiệm vụ Chính hiện đã mở. Người chơi đủ điều kiện có thể trải nghiệm Chương này sớm. Các Chương I, II và III hiện có thể chơi song song. Việc tham gia các Chương sau sớm không ảnh hưởng đến tiến trình của các Chương trước, và ngươi luôn có thể tiếp tục các Chương trước từ nơi đã dừng.
+Truy cập sớm Chương II/Chương III cũng mở khóa các chức năng Điều Chỉnh Thời Gian, Chuyển Đổi Cộng Hưởng, cùng một số Tiện ích khác.
 *Để có trải nghiệm tối ưu, chúng tôi khuyến nghị hoàn thành Chương II - Đoạn chuyển "Flowing Starlight in the Iris" trước khi bắt đầu Chương III.</t>
         </is>
       </c>
@@ -3655,21 +3655,21 @@
         <is>
           <t>Những ký ức quá khứ chôn vùi sâu trong giấc mơ, và chìa khóa để khám phá chúng đang nằm trong tay cậu. Đừng quên, chỉ trong giấc mơ, câu trả lời mới được hé lộ.
 [Cập Nhật Hỗ Trợ Giấc Mơ]
-Resonators Hỗ Trợ Giấc Mơ hiện tại: Lynae, Zani, Jinhsi, Phoebe, Shorekeeper, Verina. Sử dụng ít nhất một Resonators Hỗ Trợ Giấc Mơ để nhận thưởng Points cộng 150%!
+Resonator Hỗ Trợ Giấc Mơ hiện tại: Lynae, Zani, Jinhsi, Phoebe, Shorekeeper, Verina. Sử dụng ít nhất một Resonator Hỗ Trợ Giấc Mơ để nhận thưởng Điểm cộng 150%!
 Hiệu ứng Hỗ Trợ Giấc Mơ hiện tại:
-- Tất cả Resonators trong đội nhận thêm 30% Spectro DMG.
-- Gây Spectro DMG sẽ nhận được 30 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi giây một lần.
-- Khi Năng Lượng Giấc Mơ đạt 500, cậu sẽ bước vào Giấc Mơ Tỉnh. Trong trạng thái này, một số Ẩn Dụ sẽ được tăng cường, Crit. Rate và Hồi Phục Năng Lượng của tất cả Resonators trong đội tăng lần lượt 50% và 100%, đồng thời Cooldown chiêu của Resonance Skill và Resonance Liberation giảm 50%. Giấc Mơ Tỉnh kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mơ khi kết thúc.
+- Tất cả Resonator trong đội nhận thêm 30% Sát Thương Spectro.
+- Gây Sát Thương Spectro sẽ nhận được 30 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi giây một lần.
+- Khi Năng Lượng Giấc Mơ đạt 500, cậu sẽ bước vào Giấc Mơ Tỉnh. Trong trạng thái này, một số Ẩn Dụ sẽ được tăng cường, Crit. Rate và Hồi Phục Năng Lượng của tất cả Resonator trong đội tăng lần lượt 50% và 100%, đồng thời thời gian hồi chiêu của Resonance Skill và Resonance Liberation giảm 50%. Giấc Mơ Tỉnh kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mơ khi kết thúc.
 [Khám Phá]
-- Chọn ba Resonators từ kho Resonators và bước vào những trận chiến hoành tráng trong Cõi Ảo.
-Skills Echo, Stats, Cấp Độ, Chuỗi Resonance và Vũ Khí của Resonators sẽ được giữ nguyên trong sự kiện.
+- Chọn ba Resonator từ kho Resonator và bước vào những trận chiến hoành tráng trong Cõi Ảo.
+Kỹ Năng Tiếng Vọng, Chỉ Số, Cấp Độ, Resonance Chain và Vũ Khí của Resonator sẽ được giữ nguyên trong sự kiện.
 - Trong Cõi Ảo, cậu có thể nhận được sức mạnh gia tăng từ các Ẩn Dụ. Những Ẩn Dụ có dấu hiệu Sức Mạnh Giấc Mơ sẽ mang lại hiệu ứng bổ sung khi kích hoạt Giấc Mơ Tỉnh thông qua Hỗ Trợ Giấc Mơ.
-- Mỗi trận chiến trong Cõi Ảo sẽ đối đầu với những kẻ địch khác nhau. Hoàn thành những thử thách này để kiếm Points Ảo và đạt các mốc thưởng để nhận những phần quà hậu hĩnh.
+- Mỗi trận chiến trong Cõi Ảo sẽ đối đầu với những kẻ địch khác nhau. Hoàn thành những thử thách này để kiếm Điểm Ảo và đạt các mốc thưởng để nhận những phần quà hậu hĩnh.
 [Tinh Thể Tàn Dư]
 Một Tinh Thể Tàn Dư sẽ xuất hiện trong Khu Vực Ký Ức sau khi đánh bại những kẻ địch mạnh nhất ở sâu nhất trong cõi. Sử dụng Waveplate để thu thập phần thưởng của nó.
 Mỗi tuần, hai lần thu thập phần thưởng đầu tiên từ Tinh Thể Tàn Dư sẽ miễn phí và không cần Waveplate. Các lần thu thập miễn phí sẽ không được chuyển sang tuần tiếp theo.
 [Độ Khó]
-Pha SOL3 cao hơn mang đến Khám Phá thử thách hơn trong Cõi Ảo với nhiều phần thưởng hơn từ Tinh Thể Tàn Dư và Points Ảo. Difficulty của Cõi Ảo phụ thuộc vào Pha SOL3 mà cậu đang ở khi Cõi Ảo được làm mới (04:00 mỗi thứ Hai). Việc điều chỉnh Pha SOL3 trong mỗi chu kỳ khám phá sẽ không ảnh hưởng đến độ khó và phần thưởng của chu kỳ hiện tại.</t>
+Pha SOL3 cao hơn mang đến Khám Phá thử thách hơn trong Cõi Ảo với nhiều phần thưởng hơn từ Tinh Thể Tàn Dư và Điểm Ảo. Độ khó của Cõi Ảo phụ thuộc vào Pha SOL3 mà cậu đang ở khi Cõi Ảo được làm mới (04:00 mỗi thứ Hai). Việc điều chỉnh Pha SOL3 trong mỗi chu kỳ khám phá sẽ không ảnh hưởng đến độ khó và phần thưởng của chu kỳ hiện tại.</t>
         </is>
       </c>
     </row>
@@ -3752,21 +3752,21 @@
         <is>
           <t>Những ký ức quá khứ chôn vùi sâu trong giấc mơ, và chìa khóa để khám phá nằm trong tay cậu. Đừng quên, chỉ trong giấc mơ, câu trả lời mới được hé lộ.
 [Cập Nhật Hỗ Trợ Giấc Mơ]
-Resonators Hỗ Trợ Giấc Mơ hiện tại: Qiuyuan, Iuno, Cartethyia, Ciaccona, Jiyan, Jianxin, Yangyang, Aalto. Sử dụng ít nhất một Resonators Hỗ Trợ Giấc Mơ để nhận thưởng Points cộng 150%!
+Resonator Hỗ Trợ Giấc Mơ hiện tại: Qiuyuan, Iuno, Cartethyia, Ciaccona, Jiyan, Jianxin, Yangyang, Aalto. Sử dụng ít nhất một Resonator Hỗ Trợ Giấc Mơ để nhận thưởng Điểm cộng 150%!
 Hiệu ứng Hỗ Trợ Giấc Mơ hiện tại:
-- Tất cả Resonators trong đội nhận thêm 30% Aero DMG.
-- Gây Aero DMG sẽ nhận được 30 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi giây một lần.
-- Khi Năng Lượng Giấc Mơ đạt 500, cậu sẽ bước vào Giấc Mơ Tỉnh. Trong trạng thái này, một số Ẩn Dụ sẽ được tăng cường, Crit. Rate và Tái Tạo Năng Lượng của tất cả Resonators trong đội tăng lần lượt 50% và 100%, đồng thời Cooldown chiêu của Resonance Skill và Resonance Liberation giảm 50%. Giấc Mơ Tỉnh kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mơ khi kết thúc.
+- Tất cả Resonator trong đội nhận thêm 30% Sát Thương Aero.
+- Gây Sát Thương Aero sẽ nhận được 30 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi giây một lần.
+- Khi Năng Lượng Giấc Mơ đạt 500, cậu sẽ bước vào Giấc Mơ Tỉnh. Trong trạng thái này, một số Ẩn Dụ sẽ được tăng cường, Crit. Rate và Tái Tạo Năng Lượng của tất cả Resonator trong đội tăng lần lượt 50% và 100%, đồng thời thời gian hồi chiêu của Resonance Skill và Resonance Liberation giảm 50%. Giấc Mơ Tỉnh kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mơ khi kết thúc.
 [Khám Phá]
-- Chọn ba Resonators từ kho Resonators và bước vào những trận chiến hoành tráng trong Cõi Ảo.
-Skills Echo, Stats, Cấp Độ, Chuỗi Resonance và Vũ Khí của Resonators sẽ được giữ nguyên trong sự kiện.
+- Chọn ba Resonator từ kho Resonator và bước vào những trận chiến hoành tráng trong Cõi Ảo.
+Kỹ Năng Tiếng Vọng, Chỉ Số, Cấp Độ, Resonance Chain và Vũ Khí của Resonator sẽ được giữ nguyên trong sự kiện.
 - Trong Cõi Ảo, cậu có thể nhận được những tăng cường mạnh mẽ từ Ẩn Dụ. Những Ẩn Dụ có dấu hiệu Sức Mạnh Giấc Mơ sẽ mang lại hiệu ứng bổ sung khi kích hoạt Giấc Mơ Tỉnh thông qua Hỗ Trợ Giấc Mơ.
-- Mỗi trận chiến trong Cõi Ảo sẽ đưa cậu đối đầu với những kẻ thù khác nhau. Hoàn thành những thử thách này để kiếm Points Ảo và đạt các mốc thưởng để nhận những phần quà hậu hĩnh.
+- Mỗi trận chiến trong Cõi Ảo sẽ đưa cậu đối đầu với những kẻ thù khác nhau. Hoàn thành những thử thách này để kiếm Điểm Ảo và đạt các mốc thưởng để nhận những phần quà hậu hĩnh.
 [Tinh Thể Tàn Dư]
 Một Tinh Thể Tàn Dư sẽ xuất hiện trong Khu Vực Ký Ức sau khi đánh bại những kẻ thù mạnh mẽ ở sâu nhất trong cõi. Sử dụng Waveplate để thu thập phần thưởng của nó.
 Mỗi tuần, hai lần thu thập phần thưởng đầu tiên từ Tinh Thể Tàn Dư sẽ miễn phí và không cần Waveplate. Số lần thu thập miễn phí sẽ không được chuyển sang tuần tiếp theo.
 [Độ Khó]
-Pha SOL3 cao hơn mang đến Khám Phá thử thách hơn trong Cõi Ảo với nhiều phần thưởng hơn từ Tinh Thể Tàn Dư và Points Ảo. Difficulty của Cõi Ảo phụ thuộc vào Pha SOL3 mà cậu đang ở khi Cõi Ảo được đặt lại (04:00 mỗi thứ Hai). Việc điều chỉnh Pha SOL3 trong mỗi chu kỳ khám phá sẽ không ảnh hưởng đến độ khó và phần thưởng của chu kỳ hiện tại.</t>
+Pha SOL3 cao hơn mang đến Khám Phá thử thách hơn trong Cõi Ảo với nhiều phần thưởng hơn từ Tinh Thể Tàn Dư và Điểm Ảo. Độ khó của Cõi Ảo phụ thuộc vào Pha SOL3 mà cậu đang ở khi Cõi Ảo được đặt lại (04:00 mỗi thứ Hai). Việc điều chỉnh Pha SOL3 trong mỗi chu kỳ khám phá sẽ không ảnh hưởng đến độ khó và phần thưởng của chu kỳ hiện tại.</t>
         </is>
       </c>
     </row>
@@ -3849,21 +3849,21 @@
         <is>
           <t>Những ký ức quá khứ chôn vùi sâu trong giấc mơ, và chìa khóa để khám phá chúng đang nằm trong tay cậu. Đừng quên nhé, chỉ trong giấc mơ, câu trả lời mới được hé lộ.
 [Cập Nhật Hỗ Trợ Giấc Mơ]
-Resonators Hỗ Trợ Giấc Mơ hiện tại: Chisa, Phrolova, Camellya, Roccia, Danjin, Cantarella. Sử dụng ít nhất một Resonators Hỗ Trợ Giấc Mơ để nhận thưởng Points cộng 150%!
+Resonator Hỗ Trợ Giấc Mơ hiện tại: Chisa, Phrolova, Camellya, Roccia, Danjin, Cantarella. Sử dụng ít nhất một Resonator Hỗ Trợ Giấc Mơ để nhận thưởng Điểm cộng 150%!
 Hiệu ứng Hỗ Trợ Giấc Mơ hiện tại:
-- Tất cả Resonators trong đội nhận thêm 30% Havoc DMG.
-- Gây Havoc DMG sẽ nhận được 30 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi giây một lần.
-- Khi Năng Lượng Giấc Mơ đạt 500, cậu sẽ bước vào Giấc Mơ Tỉnh Thức. Trong trạng thái này, một số Ảo Giác sẽ được tăng cường, Crit. Rate và Hồi Phục Năng Lượng của tất cả Resonators trong đội tăng lần lượt 50% và 100%, đồng thời Cooldown chiêu của Resonance Skill và Resonance Liberation giảm 50%. Giấc Mơ Tỉnh Thức kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mơ khi kết thúc.
+- Tất cả Resonator trong đội nhận thêm 30% Sát Thương Havoc.
+- Gây Sát Thương Havoc sẽ nhận được 30 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi giây một lần.
+- Khi Năng Lượng Giấc Mơ đạt 500, cậu sẽ bước vào Giấc Mơ Tỉnh Thức. Trong trạng thái này, một số Ảo Giác sẽ được tăng cường, Crit. Rate và Hồi Phục Năng Lượng của tất cả Resonator trong đội tăng lần lượt 50% và 100%, đồng thời thời gian hồi chiêu của Resonance Skill và Resonance Liberation giảm 50%. Giấc Mơ Tỉnh Thức kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mơ khi kết thúc.
 [Khám Phá]
-- Chọn ba Resonators từ kho Resonators và bước vào những trận chiến hoành tráng trong Thế Giới Ảo.
-Skills Echo, Stats, Cấp Độ, Chuỗi Resonance và Vũ Khí của Resonators sẽ được giữ nguyên trong sự kiện.
+- Chọn ba Resonator từ kho Resonator và bước vào những trận chiến hoành tráng trong Thế Giới Ảo.
+Kỹ Năng Tiếng Vọng, Chỉ Số, Cấp Độ, Resonance Chain và Vũ Khí của Resonator sẽ được giữ nguyên trong sự kiện.
 - Trong Thế Giới Ảo, cậu có thể nhận được những tăng cường mạnh mẽ từ Ảo Giác. Những Ảo Giác có dấu hiệu Sức Mạnh Giấc Mơ sẽ mang lại hiệu ứng bổ sung khi kích hoạt Giấc Mơ Tỉnh Thức thông qua Hỗ Trợ Giấc Mơ.
-- Mỗi trận chiến trong Thế Giới Ảo sẽ đưa cậu đối đầu với những kẻ thù khác nhau. Hoàn thành những thử thách này để kiếm Points Ảo và đạt các mốc thưởng để nhận những phần quà hậu hĩnh.
+- Mỗi trận chiến trong Thế Giới Ảo sẽ đưa cậu đối đầu với những kẻ thù khác nhau. Hoàn thành những thử thách này để kiếm Điểm Ảo và đạt các mốc thưởng để nhận những phần quà hậu hĩnh.
 [Tinh Thể Tàn Dư]
 Một Tinh Thể Tàn Dư sẽ xuất hiện trong Khu Vực Ký Ức sau khi đánh bại những kẻ thù mạnh mẽ ở sâu nhất trong Thế Giới Ảo. Sử dụng Waveplate để thu thập phần thưởng của nó.
 Mỗi tuần, hai lần thu thập phần thưởng đầu tiên từ Tinh Thể Tàn Dư sẽ miễn phí và không cần Waveplate. Các lần thu thập miễn phí sẽ không được chuyển sang tuần tiếp theo.
 [Độ Khó]
-Pha SOL3 cao hơn mang đến những thử thách Khám Phá khó khăn hơn trong Thế Giới Ảo, cùng với đó là nhiều phần thưởng hơn từ Tinh Thể Tàn Dư và Points Ảo. Difficulty của Thế Giới Ảo phụ thuộc vào Pha SOL3 của cậu khi Thế Giới Ảo được thiết lập lại (04:00 mỗi thứ Hai). Việc điều chỉnh Pha SOL3 trong mỗi chu kỳ khám phá sẽ không ảnh hưởng đến độ khó và phần thưởng của chu kỳ hiện tại.</t>
+Pha SOL3 cao hơn mang đến những thử thách Khám Phá khó khăn hơn trong Thế Giới Ảo, cùng với đó là nhiều phần thưởng hơn từ Tinh Thể Tàn Dư và Điểm Ảo. Độ khó của Thế Giới Ảo phụ thuộc vào Pha SOL3 của cậu khi Thế Giới Ảo được thiết lập lại (04:00 mỗi thứ Hai). Việc điều chỉnh Pha SOL3 trong mỗi chu kỳ khám phá sẽ không ảnh hưởng đến độ khó và phần thưởng của chu kỳ hiện tại.</t>
         </is>
       </c>
     </row>
@@ -3946,21 +3946,21 @@
         <is>
           <t>Những ký ức quá khứ chôn vùi sâu trong giấc mơ, và chìa khóa để khám phá nằm trong tay cậu. Đừng quên, chỉ trong giấc mơ, câu trả lời mới được hé lộ.
 [Cập Nhật Hỗ Trợ Giấc Mơ]
-Resonators Hỗ Trợ Giấc Mơ hiện tại: Mornye, Galbrena, Lupa, Brant, Changli, Encore, Chixia, Mortefi. Sử dụng ít nhất một Resonators Hỗ Trợ Giấc Mơ để nhận thưởng Points tăng 150%!
+Resonator Hỗ Trợ Giấc Mơ hiện tại: Mornye, Galbrena, Lupa, Brant, Changli, Encore, Chixia, Mortefi. Sử dụng ít nhất một Resonator Hỗ Trợ Giấc Mơ để nhận thưởng Điểm tăng 150%!
 Hiệu ứng Hỗ Trợ Giấc Mơ hiện tại:
-- Tất cả Resonators trong đội nhận thêm 30% Fusion DMG.
-- Gây Fusion DMG sẽ nhận được 30 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi giây một lần.
-- Khi Năng Lượng Giấc Mơ đạt 500, cậu sẽ bước vào Giấc Mơ Tỉnh. Trong trạng thái này, một số Ảo Ảnh sẽ được tăng cường, Crit. Rate và Hồi Phục Năng Lượng của tất cả Resonators trong đội tăng lần lượt 50% và 100%, đồng thời Cooldown chiêu của Resonance Skill và Resonance Liberation giảm 50%. Giấc Mơ Tỉnh kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mơ khi kết thúc.
+- Tất cả Resonator trong đội nhận thêm 30% Sát Thương Fusion.
+- Gây Sát Thương Fusion sẽ nhận được 30 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi giây một lần.
+- Khi Năng Lượng Giấc Mơ đạt 500, cậu sẽ bước vào Giấc Mơ Tỉnh. Trong trạng thái này, một số Ảo Ảnh sẽ được tăng cường, Crit. Rate và Hồi Phục Năng Lượng của tất cả Resonator trong đội tăng lần lượt 50% và 100%, đồng thời thời gian hồi chiêu của Resonance Skill và Resonance Liberation giảm 50%. Giấc Mơ Tỉnh kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mơ khi kết thúc.
 [Khám Phá]
-- Chọn ba Resonators từ kho Resonators và bước vào những trận chiến hoành tráng trong Thế Giới Ảo.
-Skills Echo, Stats, Cấp Độ, Chuỗi Resonance và Vũ Khí của Resonators sẽ được giữ nguyên trong sự kiện.
+- Chọn ba Resonator từ kho Resonator và bước vào những trận chiến hoành tráng trong Thế Giới Ảo.
+Kỹ Năng Tiếng Vọng, Chỉ Số, Cấp Độ, Resonance Chain và Vũ Khí của Resonator sẽ được giữ nguyên trong sự kiện.
 - Trong Thế Giới Ảo, cậu có thể nhận được sức mạnh gia tăng từ Ảo Ảnh. Những Ảo Ảnh có dấu hiệu Sức Mạnh Giấc Mơ sẽ mang lại hiệu ứng bổ sung khi kích hoạt Giấc Mơ Tỉnh thông qua Hỗ Trợ Giấc Mơ.
-- Mỗi trận chiến trong Thế Giới Ảo sẽ đối đầu với những kẻ địch khác nhau. Hoàn thành những thử thách này để kiếm Points Ảo và đạt các mốc thưởng để nhận những phần quà hậu hĩnh.
+- Mỗi trận chiến trong Thế Giới Ảo sẽ đối đầu với những kẻ địch khác nhau. Hoàn thành những thử thách này để kiếm Điểm Ảo và đạt các mốc thưởng để nhận những phần quà hậu hĩnh.
 [Tinh Thể Tàn Dư]
 Một Tinh Thể Tàn Dư sẽ xuất hiện trong Khu Vực Ký Ức sau khi đánh bại những kẻ địch mạnh nhất ở sâu nhất trong thế giới. Sử dụng Waveplate để thu thập phần thưởng của nó.
 Mỗi tuần, hai lần thu thập phần thưởng đầu tiên từ Tinh Thể Tàn Dư sẽ miễn phí và không cần Waveplate. Các lần thu thập miễn phí sẽ không được chuyển sang tuần tiếp theo.
 [Độ Khó]
-Pha SOL3 cao hơn mang đến Khám Phá thử thách hơn trong Thế Giới Ảo với nhiều phần thưởng hơn từ Tinh Thể Tàn Dư và Points Ảo. Difficulty của Thế Giới Ảo phụ thuộc vào Pha SOL3 mà cậu đang ở khi Thế Giới Ảo được làm mới (04:00 mỗi thứ Hai). Việc điều chỉnh Pha SOL3 trong mỗi chu kỳ khám phá sẽ không ảnh hưởng đến độ khó và phần thưởng của chu kỳ hiện tại.</t>
+Pha SOL3 cao hơn mang đến Khám Phá thử thách hơn trong Thế Giới Ảo với nhiều phần thưởng hơn từ Tinh Thể Tàn Dư và Điểm Ảo. Độ khó của Thế Giới Ảo phụ thuộc vào Pha SOL3 mà cậu đang ở khi Thế Giới Ảo được làm mới (04:00 mỗi thứ Hai). Việc điều chỉnh Pha SOL3 trong mỗi chu kỳ khám phá sẽ không ảnh hưởng đến độ khó và phần thưởng của chu kỳ hiện tại.</t>
         </is>
       </c>
     </row>
@@ -4042,21 +4042,21 @@
         <is>
           <t>Những ký ức quá khứ chôn vùi sâu trong giấc mơ, và chìa khóa để khám phá nằm trong tay cậu. Đừng quên, chỉ trong giấc mơ, câu trả lời mới được hé lộ.
 [Cập Nhật Hỗ Trợ Giấc Mơ]
-Resonators Hỗ Trợ Giấc Mơ hiện tại: Augusta, Xiangli Yao, Yinlin, Calcharo, Yuanwu, Buling. Sử dụng ít nhất một Resonators Hỗ Trợ Giấc Mơ để nhận thưởng Points cộng 150%!
+Resonator Hỗ Trợ Giấc Mơ hiện tại: Augusta, Xiangli Yao, Yinlin, Calcharo, Yuanwu, Buling. Sử dụng ít nhất một Resonator Hỗ Trợ Giấc Mơ để nhận thưởng Điểm cộng 150%!
 Hiệu ứng Hỗ Trợ Giấc Mơ hiện tại:
-- Tất cả Resonators trong đội nhận thêm 30% Electro DMG.
-- Gây Electro DMG sẽ nhận được 30 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi giây một lần.
-- Khi Năng Lượng Giấc Mơ đạt 500, cậu sẽ bước vào Giấc Mơ Tỉnh. Trong trạng thái này, một số Ẩn Dụ sẽ được tăng cường, Crit. Rate và Hồi Phục Năng Lượng của tất cả Resonators trong đội tăng lần lượt 50% và 100%, đồng thời Cooldown chiêu của Resonance Skill và Resonance Liberation giảm 50%. Giấc Mơ Tỉnh kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mơ khi kết thúc.
+- Tất cả Resonator trong đội nhận thêm 30% Sát Thương Electro.
+- Gây Sát Thương Electro sẽ nhận được 30 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi giây một lần.
+- Khi Năng Lượng Giấc Mơ đạt 500, cậu sẽ bước vào Giấc Mơ Tỉnh. Trong trạng thái này, một số Ẩn Dụ sẽ được tăng cường, Crit. Rate và Hồi Phục Năng Lượng của tất cả Resonator trong đội tăng lần lượt 50% và 100%, đồng thời thời gian hồi chiêu của Resonance Skill và Resonance Liberation giảm 50%. Giấc Mơ Tỉnh kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mơ khi kết thúc.
 [Khám Phá]
-- Chọn ba Resonators từ kho Resonators và bước vào những trận chiến hoành tráng trong Cõi Ảo.
-Skills Echo, Stats, Cấp Độ, Chuỗi Resonance và Vũ Khí của Resonators sẽ được giữ nguyên trong sự kiện.
+- Chọn ba Resonator từ kho Resonator và bước vào những trận chiến hoành tráng trong Cõi Ảo.
+Kỹ Năng Tiếng Vọng, Chỉ Số, Cấp Độ, Resonance Chain và Vũ Khí của Resonator sẽ được giữ nguyên trong sự kiện.
 - Trong Cõi Ảo, cậu có thể nhận được sức mạnh gia tăng từ các Ẩn Dụ. Những Ẩn Dụ có dấu hiệu Sức Mạnh Giấc Mơ sẽ mang lại hiệu ứng bổ sung khi kích hoạt Giấc Mơ Tỉnh thông qua Hỗ Trợ Giấc Mơ.
-- Mỗi trận chiến trong Cõi Ảo sẽ đưa cậu đối đầu với những kẻ thù khác nhau. Hoàn thành những thử thách này để kiếm Points Ảo và đạt các mốc thưởng để nhận những phần quà hậu hĩnh.
+- Mỗi trận chiến trong Cõi Ảo sẽ đưa cậu đối đầu với những kẻ thù khác nhau. Hoàn thành những thử thách này để kiếm Điểm Ảo và đạt các mốc thưởng để nhận những phần quà hậu hĩnh.
 [Tinh Thể Tàn Dư]
 Một Tinh Thể Tàn Dư sẽ xuất hiện trong Khu Vực Ký Ức sau khi đánh bại những kẻ thù mạnh mẽ nằm sâu nhất trong cõi. Sử dụng Waveplate để thu thập phần thưởng của nó.
 Mỗi tuần, hai lần thu thập phần thưởng đầu tiên từ Tinh Thể Tàn Dư sẽ miễn phí và không cần dùng Waveplate. Các lần thu thập miễn phí sẽ không được chuyển sang tuần tiếp theo.
 [Độ Khó]
-Pha SOL3 cao hơn mang đến những thử thách Khám Phá khó khăn hơn trong Cõi Ảo, cùng với nhiều phần thưởng hơn từ Tinh Thể Tàn Dư và Points Ảo. Difficulty của Cõi Ảo phụ thuộc vào Pha SOL3 mà cậu đang ở khi Cõi Ảo được làm mới (04:00 mỗi thứ Hai). Việc điều chỉnh Pha SOL3 trong mỗi chu kỳ khám phá sẽ không ảnh hưởng đến độ khó và phần thưởng của chu kỳ hiện tại.</t>
+Pha SOL3 cao hơn mang đến những thử thách Khám Phá khó khăn hơn trong Cõi Ảo, cùng với nhiều phần thưởng hơn từ Tinh Thể Tàn Dư và Điểm Ảo. Độ khó của Cõi Ảo phụ thuộc vào Pha SOL3 mà cậu đang ở khi Cõi Ảo được làm mới (04:00 mỗi thứ Hai). Việc điều chỉnh Pha SOL3 trong mỗi chu kỳ khám phá sẽ không ảnh hưởng đến độ khó và phần thưởng của chu kỳ hiện tại.</t>
         </is>
       </c>
     </row>
@@ -4139,21 +4139,21 @@
         <is>
           <t>Những ký ức quá khứ chôn vùi sâu trong giấc mơ, và chìa khóa để khám phá nằm trong tay cậu. Đừng quên nhé, chỉ trong giấc mơ, câu trả lời mới được hé lộ.
 [Cập Nhật Hỗ Trợ Giấc Mơ]
-Resonators Hỗ Trợ Giấc Mơ hiện tại: Carlotta, Zhezhi, Lingyang, Sanhua, Youhu, Baizhi. Sử dụng ít nhất một Resonators Hỗ Trợ Giấc Mơ để nhận thưởng Points tăng cường 150%!
+Resonator Hỗ Trợ Giấc Mơ hiện tại: Carlotta, Zhezhi, Lingyang, Sanhua, Youhu, Baizhi. Sử dụng ít nhất một Resonator Hỗ Trợ Giấc Mơ để nhận thưởng Điểm tăng cường 150%!
 Hiệu ứng Hỗ Trợ Giấc Mơ hiện tại:
-- Tất cả Resonators trong đội nhận thêm 30% Glacio DMG.
-- Gây Glacio DMG sẽ nhận được 30 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi giây một lần.
-- Khi Năng Lượng Giấc Mơ đạt 500, cậu sẽ bước vào Giấc Mơ Tỉnh. Trong trạng thái này, một số Ảo Ảnh sẽ được tăng cường, Crit. Rate và Hồi Phục Năng Lượng của tất cả Resonators trong đội tăng lần lượt 50% và 100%, đồng thời Cooldown chiêu của Resonance Skill và Resonance Liberation giảm 50%. Giấc Mơ Tỉnh kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mơ khi kết thúc.
+- Tất cả Resonator trong đội nhận thêm 30% Sát Thương Glacio.
+- Gây Sát Thương Glacio sẽ nhận được 30 Năng Lượng Giấc Mơ. Hiệu ứng này có thể kích hoạt mỗi giây một lần.
+- Khi Năng Lượng Giấc Mơ đạt 500, cậu sẽ bước vào Giấc Mơ Tỉnh. Trong trạng thái này, một số Ảo Ảnh sẽ được tăng cường, Crit. Rate và Hồi Phục Năng Lượng của tất cả Resonator trong đội tăng lần lượt 50% và 100%, đồng thời thời gian hồi chiêu của Resonance Skill và Resonance Liberation giảm 50%. Giấc Mơ Tỉnh kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mơ khi kết thúc.
 [Khám Phá]
-- Chọn ba Resonators từ kho Resonators và bước vào những trận chiến hoành tráng trong Cõi Ảo.
-Skills Echo, Stats, Cấp Độ, Chuỗi Resonance và Vũ Khí của Resonators sẽ được giữ nguyên trong sự kiện.
+- Chọn ba Resonator từ kho Resonator và bước vào những trận chiến hoành tráng trong Cõi Ảo.
+Kỹ Năng Tiếng Vọng, Chỉ Số, Cấp Độ, Resonance Chain và Vũ Khí của Resonator sẽ được giữ nguyên trong sự kiện.
 - Trong Cõi Ảo, cậu có thể nhận được sức mạnh tăng cường từ Ảo Ảnh. Những Ảo Ảnh có dấu hiệu Sức Mạnh Giấc Mơ sẽ mang lại hiệu ứng bổ sung khi kích hoạt Giấc Mơ Tỉnh thông qua Hỗ Trợ Giấc Mơ.
-- Mỗi trận chiến trong Cõi Ảo sẽ đối đầu với những kẻ địch khác nhau. Hoàn thành những thử thách này để kiếm Points Ảo và đạt các mốc thưởng để nhận những phần quà hậu hĩnh.
+- Mỗi trận chiến trong Cõi Ảo sẽ đối đầu với những kẻ địch khác nhau. Hoàn thành những thử thách này để kiếm Điểm Ảo và đạt các mốc thưởng để nhận những phần quà hậu hĩnh.
 [Tinh Thể Tàn Dư]
 Một Tinh Thể Tàn Dư sẽ xuất hiện trong Khu Vực Ký Ức sau khi đánh bại những kẻ địch mạnh nhất ở sâu nhất trong cõi. Sử dụng Waveplate để thu thập phần thưởng của nó.
 Mỗi tuần, hai lần thu thập phần thưởng đầu tiên từ Tinh Thể Tàn Dư sẽ miễn phí và không cần Waveplate. Các lần thu thập miễn phí sẽ không được chuyển sang tuần tiếp theo.
 [Độ Khó]
-Pha SOL3 cao hơn mang đến Khám Phá thử thách hơn trong Cõi Ảo với nhiều phần thưởng hơn từ Tinh Thể Tàn Dư và Points Ảo. Difficulty của Cõi Ảo phụ thuộc vào Pha SOL3 của cậu khi Cõi Ảo được làm mới (04:00 mỗi thứ Hai). Việc điều chỉnh Pha SOL3 trong mỗi chu kỳ khám phá sẽ không ảnh hưởng đến độ khó và phần thưởng của chu kỳ hiện tại.</t>
+Pha SOL3 cao hơn mang đến Khám Phá thử thách hơn trong Cõi Ảo với nhiều phần thưởng hơn từ Tinh Thể Tàn Dư và Điểm Ảo. Độ khó của Cõi Ảo phụ thuộc vào Pha SOL3 của cậu khi Cõi Ảo được làm mới (04:00 mỗi thứ Hai). Việc điều chỉnh Pha SOL3 trong mỗi chu kỳ khám phá sẽ không ảnh hưởng đến độ khó và phần thưởng của chu kỳ hiện tại.</t>
         </is>
       </c>
     </row>
@@ -4232,17 +4232,17 @@
         <is>
           <t>Ký ức quá khứ chôn vùi sâu trong giấc mơ, và chìa khóa để khám phá nằm trong tay cậu. Đừng quên, chỉ trong giấc mơ, câu trả lời mới được hé lộ.
 [Hỗ Trợ Giấc Mơ]
-Kích hoạt thủ công trạng thái Giấc Mơ Tiên Tri khi Năng Lượng Giấc Mơ đạt 500 điểm. Trong trạng thái này, Hiệu Ứng và một số Ẩn Dụ sẽ được tăng cường, Crit. Rate và Tái Tạo Năng Lượng của tất cả Resonators trong đội tăng lần lượt 50% và 100%. Cooldown chiêu sau khi sử dụng Resonance Skill hoặc Resonance Liberation giảm 50%, kích hoạt mỗi 4 giây. Giấc Mơ Tiên Tri kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mơ khi kết thúc.
+Kích hoạt thủ công trạng thái Giấc Mơ Tiên Tri khi Năng Lượng Giấc Mơ đạt 500 điểm. Trong trạng thái này, Hiệu Ứng và một số Ẩn Dụ sẽ được tăng cường, Crit. Rate và Tái Tạo Năng Lượng của tất cả Resonator trong đội tăng lần lượt 50% và 100%. Thời gian hồi chiêu sau khi sử dụng Resonance Skill hoặc Resonance Liberation giảm 50%, kích hoạt mỗi 4 giây. Giấc Mơ Tiên Tri kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mơ khi kết thúc.
 [Khám Phá]
-- Chọn ba Resonators và bước vào những trận chiến hoành tráng trong Ảo Cảnh.
-- Skills Echo, Stats, Cấp Độ, Chuỗi Resonance và Vũ Khí của Resonators sẽ được giữ nguyên trong sự kiện.
+- Chọn ba Resonator và bước vào những trận chiến hoành tráng trong Ảo Cảnh.
+- Kỹ Năng Tiếng Vọng, Chỉ Số, Cấp Độ, Resonance Chain và Vũ Khí của Resonator sẽ được giữ nguyên trong sự kiện.
 - Trong Ảo Cảnh, cậu có thể nhận được những tăng cường mạnh mẽ từ Ẩn Dụ. Hiệu Ứng và một số Ẩn Dụ sẽ mang lại hiệu ứng bổ sung khi Giấc Mơ Tiên Tri được kích hoạt thông qua Hỗ Trợ Giấc Mơ.
-- Mỗi trận chiến trong Ảo Cảnh sẽ đối đầu với những kẻ địch khác nhau. Hoàn thành những thử thách này để kiếm Points Ảo Cảnh và đạt các mốc thưởng để nhận những phần quà hậu hĩnh.
+- Mỗi trận chiến trong Ảo Cảnh sẽ đối đầu với những kẻ địch khác nhau. Hoàn thành những thử thách này để kiếm Điểm Ảo Cảnh và đạt các mốc thưởng để nhận những phần quà hậu hĩnh.
 [Tinh Thể Tàn Dư]
 Một Tinh Thể Tàn Dư sẽ xuất hiện trong Khu Vực Ký Ức sau khi đánh bại những kẻ địch mạnh nhất ở sâu nhất trong Ảo Cảnh. Sử dụng Bản Năng Lượng để thu thập phần thưởng của nó.
 Mỗi tuần, hai lần thu thập phần thưởng đầu tiên từ Tinh Thể Tàn Dư là miễn phí và không cần Bản Năng Lượng. Các lần thu thập miễn phí sẽ không được chuyển sang tuần tiếp theo.
 [Độ Khó]
-Pha SOL3 cao hơn mang đến những thử thách Khám Phá khó khăn hơn trong Ảo Cảnh, cùng với đó là nhiều phần thưởng hơn từ Tinh Thể Tàn Dư và Points Ảo Cảnh. Difficulty của Ảo Cảnh phụ thuộc vào Pha SOL3 mà cậu đang ở khi Ảo Cảnh được làm mới (04:00 mỗi thứ Hai). Việc điều chỉnh Pha SOL3 trong mỗi chu kỳ khám phá sẽ không ảnh hưởng đến độ khó và phần thưởng của chu kỳ hiện tại.</t>
+Pha SOL3 cao hơn mang đến những thử thách Khám Phá khó khăn hơn trong Ảo Cảnh, cùng với đó là nhiều phần thưởng hơn từ Tinh Thể Tàn Dư và Điểm Ảo Cảnh. Độ khó của Ảo Cảnh phụ thuộc vào Pha SOL3 mà cậu đang ở khi Ảo Cảnh được làm mới (04:00 mỗi thứ Hai). Việc điều chỉnh Pha SOL3 trong mỗi chu kỳ khám phá sẽ không ảnh hưởng đến độ khó và phần thưởng của chu kỳ hiện tại.</t>
         </is>
       </c>
     </row>
@@ -4321,17 +4321,17 @@
         <is>
           <t>Ký ức quá khứ chôn vùi sâu trong giấc mơ, và chìa khóa để khám phá nằm trong tay cậu. Đừng quên, chỉ trong giấc mơ, câu trả lời mới được hé lộ.
 [Hỗ Trợ Giấc Mơ]
-Kích hoạt thủ công trạng thái Giấc Mơ Tiên Tri khi Năng Lượng Giấc Mơ đạt 500 điểm. Trong trạng thái này, Hiệu Ứng và một số Ẩn Dụ sẽ được tăng cường, Crit. Rate và Tái Tạo Năng Lượng của tất cả Resonators trong đội tăng lần lượt 50% và 100%. Cooldown chiêu sau khi sử dụng Resonance Skill hoặc Resonance Liberation giảm 50%, kích hoạt mỗi 4 giây. Giấc Mơ Tiên Tri kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mơ khi kết thúc.
+Kích hoạt thủ công trạng thái Giấc Mơ Tiên Tri khi Năng Lượng Giấc Mơ đạt 500 điểm. Trong trạng thái này, Hiệu Ứng và một số Ẩn Dụ sẽ được tăng cường, Crit. Rate và Tái Tạo Năng Lượng của tất cả Resonator trong đội tăng lần lượt 50% và 100%. Thời gian hồi chiêu sau khi sử dụng Resonance Skill hoặc Resonance Liberation giảm 50%, kích hoạt mỗi 4 giây. Giấc Mơ Tiên Tri kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mơ khi kết thúc.
 [Khám Phá]
-- Chọn ba Resonators và bước vào những trận chiến hoành tráng trong Ảo Cảnh.
-- Skills Echo, Stats, Cấp Độ, Chuỗi Resonance và Vũ Khí của Resonators sẽ được giữ nguyên trong sự kiện.
+- Chọn ba Resonator và bước vào những trận chiến hoành tráng trong Ảo Cảnh.
+- Kỹ Năng Tiếng Vọng, Chỉ Số, Cấp Độ, Resonance Chain và Vũ Khí của Resonator sẽ được giữ nguyên trong sự kiện.
 - Trong Ảo Cảnh, cậu có thể nhận được những tăng cường mạnh mẽ từ Ẩn Dụ. Hiệu Ứng và một số Ẩn Dụ sẽ mang lại hiệu ứng bổ sung khi Giấc Mơ Tiên Tri được kích hoạt thông qua Hỗ Trợ Giấc Mơ.
-- Mỗi trận chiến trong Ảo Cảnh sẽ đối đầu với những kẻ địch khác nhau. Hoàn thành những thử thách này để kiếm Points Ảo Cảnh và đạt các mốc thưởng để nhận những phần quà hậu hĩnh.
+- Mỗi trận chiến trong Ảo Cảnh sẽ đối đầu với những kẻ địch khác nhau. Hoàn thành những thử thách này để kiếm Điểm Ảo Cảnh và đạt các mốc thưởng để nhận những phần quà hậu hĩnh.
 [Tinh Thể Tàn Dư]
 Một Tinh Thể Tàn Dư sẽ xuất hiện trong Khu Vực Ký Ức sau khi đánh bại những kẻ địch mạnh nhất ở sâu nhất trong Ảo Cảnh. Sử dụng Bản Năng Lượng để thu thập phần thưởng của nó.
 Mỗi tuần, hai lần thu thập phần thưởng đầu tiên từ Tinh Thể Tàn Dư là miễn phí và không cần Bản Năng Lượng. Các lần thu thập miễn phí sẽ không được chuyển sang tuần tiếp theo.
 [Độ Khó]
-Pha SOL3 cao hơn mang đến những thử thách Khám Phá khó khăn hơn trong Ảo Cảnh, cùng với đó là nhiều phần thưởng hơn từ Tinh Thể Tàn Dư và Points Ảo Cảnh. Difficulty của Ảo Cảnh phụ thuộc vào Pha SOL3 mà cậu đang ở khi Ảo Cảnh được làm mới (04:00 mỗi thứ Hai). Việc điều chỉnh Pha SOL3 trong mỗi chu kỳ khám phá sẽ không ảnh hưởng đến độ khó và phần thưởng của chu kỳ hiện tại.</t>
+Pha SOL3 cao hơn mang đến những thử thách Khám Phá khó khăn hơn trong Ảo Cảnh, cùng với đó là nhiều phần thưởng hơn từ Tinh Thể Tàn Dư và Điểm Ảo Cảnh. Độ khó của Ảo Cảnh phụ thuộc vào Pha SOL3 mà cậu đang ở khi Ảo Cảnh được làm mới (04:00 mỗi thứ Hai). Việc điều chỉnh Pha SOL3 trong mỗi chu kỳ khám phá sẽ không ảnh hưởng đến độ khó và phần thưởng của chu kỳ hiện tại.</t>
         </is>
       </c>
     </row>
@@ -4410,17 +4410,17 @@
         <is>
           <t>Ký ức quá khứ chôn vùi sâu trong giấc mơ, và chìa khóa để khám phá nằm trong tay cậu. Đừng quên, chỉ trong giấc mơ, câu trả lời mới được hé lộ.
 [Hỗ Trợ Giấc Mơ]
-Kích hoạt thủ công trạng thái Giấc Mơ Tiên Tri khi Năng Lượng Giấc Mơ đạt 500 điểm. Trong trạng thái này, Hiệu Ứng và một số Ẩn Dụ sẽ được tăng cường, Crit. Rate và Tái Tạo Năng Lượng của tất cả Resonators trong đội tăng lần lượt 50% và 100%. Cooldown chiêu sau khi sử dụng Resonance Skill hoặc Resonance Liberation giảm 50%, kích hoạt mỗi 4 giây. Giấc Mơ Tiên Tri kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mơ khi kết thúc.
+Kích hoạt thủ công trạng thái Giấc Mơ Tiên Tri khi Năng Lượng Giấc Mơ đạt 500 điểm. Trong trạng thái này, Hiệu Ứng và một số Ẩn Dụ sẽ được tăng cường, Crit. Rate và Tái Tạo Năng Lượng của tất cả Resonator trong đội tăng lần lượt 50% và 100%. Thời gian hồi chiêu sau khi sử dụng Resonance Skill hoặc Resonance Liberation giảm 50%, kích hoạt mỗi 4 giây. Giấc Mơ Tiên Tri kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mơ khi kết thúc.
 [Khám Phá]
-- Chọn ba Resonators và bước vào những trận chiến hoành tráng trong Ảo Cảnh.
-- Skills Echo, Stats, Cấp Độ, Chuỗi Resonance và Vũ Khí của Resonators sẽ được giữ nguyên trong sự kiện.
+- Chọn ba Resonator và bước vào những trận chiến hoành tráng trong Ảo Cảnh.
+- Kỹ Năng Tiếng Vọng, Chỉ Số, Cấp Độ, Resonance Chain và Vũ Khí của Resonator sẽ được giữ nguyên trong sự kiện.
 - Trong Ảo Cảnh, cậu có thể nhận được những tăng cường mạnh mẽ từ Ẩn Dụ. Hiệu Ứng và một số Ẩn Dụ sẽ mang lại hiệu ứng bổ sung khi Giấc Mơ Tiên Tri được kích hoạt thông qua Hỗ Trợ Giấc Mơ.
-- Mỗi trận chiến trong Ảo Cảnh sẽ đối đầu với những kẻ địch khác nhau. Hoàn thành những thử thách này để kiếm Points Ảo Cảnh và đạt các mốc thưởng để nhận những phần quà hậu hĩnh.
+- Mỗi trận chiến trong Ảo Cảnh sẽ đối đầu với những kẻ địch khác nhau. Hoàn thành những thử thách này để kiếm Điểm Ảo Cảnh và đạt các mốc thưởng để nhận những phần quà hậu hĩnh.
 [Tinh Thể Tàn Dư]
 Một Tinh Thể Tàn Dư sẽ xuất hiện trong Khu Vực Ký Ức sau khi đánh bại những kẻ địch mạnh nhất ở sâu nhất trong Ảo Cảnh. Sử dụng Bản Năng Lượng để thu thập phần thưởng của nó.
 Mỗi tuần, hai lần thu thập phần thưởng đầu tiên từ Tinh Thể Tàn Dư là miễn phí và không cần Bản Năng Lượng. Các lần thu thập miễn phí sẽ không được chuyển sang tuần tiếp theo.
 [Độ Khó]
-Pha SOL3 cao hơn mang đến những thử thách Khám Phá khó khăn hơn trong Ảo Cảnh, cùng với đó là nhiều phần thưởng hơn từ Tinh Thể Tàn Dư và Points Ảo Cảnh. Difficulty của Ảo Cảnh phụ thuộc vào Pha SOL3 mà cậu đang ở khi Ảo Cảnh được làm mới (04:00 mỗi thứ Hai). Việc điều chỉnh Pha SOL3 trong mỗi chu kỳ khám phá sẽ không ảnh hưởng đến độ khó và phần thưởng của chu kỳ hiện tại.</t>
+Pha SOL3 cao hơn mang đến những thử thách Khám Phá khó khăn hơn trong Ảo Cảnh, cùng với đó là nhiều phần thưởng hơn từ Tinh Thể Tàn Dư và Điểm Ảo Cảnh. Độ khó của Ảo Cảnh phụ thuộc vào Pha SOL3 mà cậu đang ở khi Ảo Cảnh được làm mới (04:00 mỗi thứ Hai). Việc điều chỉnh Pha SOL3 trong mỗi chu kỳ khám phá sẽ không ảnh hưởng đến độ khó và phần thưởng của chu kỳ hiện tại.</t>
         </is>
       </c>
     </row>
@@ -4499,17 +4499,17 @@
         <is>
           <t>Ký ức quá khứ chôn vùi sâu trong giấc mơ, và chìa khóa để khám phá nằm trong tay cậu. Đừng quên, chỉ trong giấc mơ, câu trả lời mới được hé lộ.
 [Hỗ Trợ Giấc Mơ]
-Kích hoạt thủ công trạng thái Giấc Mơ Tiên Tri khi Năng Lượng Giấc Mơ đạt 500 điểm. Trong trạng thái này, Hiệu Ứng và một số Ẩn Dụ sẽ được tăng cường, Crit. Rate và Tái Tạo Năng Lượng của tất cả Resonators trong đội tăng lần lượt 50% và 100%. Cooldown chiêu sau khi sử dụng Resonance Skill hoặc Resonance Liberation giảm 50%, kích hoạt mỗi 4 giây. Giấc Mơ Tiên Tri kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mơ khi kết thúc.
+Kích hoạt thủ công trạng thái Giấc Mơ Tiên Tri khi Năng Lượng Giấc Mơ đạt 500 điểm. Trong trạng thái này, Hiệu Ứng và một số Ẩn Dụ sẽ được tăng cường, Crit. Rate và Tái Tạo Năng Lượng của tất cả Resonator trong đội tăng lần lượt 50% và 100%. Thời gian hồi chiêu sau khi sử dụng Resonance Skill hoặc Resonance Liberation giảm 50%, kích hoạt mỗi 4 giây. Giấc Mơ Tiên Tri kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mơ khi kết thúc.
 [Khám Phá]
-- Chọn ba Resonators và bước vào những trận chiến hoành tráng trong Ảo Cảnh.
-- Skills Echo, Stats, Cấp Độ, Chuỗi Resonance và Vũ Khí của Resonators sẽ được giữ nguyên trong sự kiện.
+- Chọn ba Resonator và bước vào những trận chiến hoành tráng trong Ảo Cảnh.
+- Kỹ Năng Tiếng Vọng, Chỉ Số, Cấp Độ, Resonance Chain và Vũ Khí của Resonator sẽ được giữ nguyên trong sự kiện.
 - Trong Ảo Cảnh, cậu có thể nhận được những tăng cường mạnh mẽ từ Ẩn Dụ. Hiệu Ứng và một số Ẩn Dụ sẽ mang lại hiệu ứng bổ sung khi Giấc Mơ Tiên Tri được kích hoạt thông qua Hỗ Trợ Giấc Mơ.
-- Mỗi trận chiến trong Ảo Cảnh sẽ đối đầu với những kẻ địch khác nhau. Hoàn thành những thử thách này để kiếm Points Ảo Cảnh và đạt các mốc thưởng để nhận những phần quà hậu hĩnh.
+- Mỗi trận chiến trong Ảo Cảnh sẽ đối đầu với những kẻ địch khác nhau. Hoàn thành những thử thách này để kiếm Điểm Ảo Cảnh và đạt các mốc thưởng để nhận những phần quà hậu hĩnh.
 [Tinh Thể Tàn Dư]
 Một Tinh Thể Tàn Dư sẽ xuất hiện trong Khu Vực Ký Ức sau khi đánh bại những kẻ địch mạnh nhất ở sâu nhất trong Ảo Cảnh. Sử dụng Bản Năng Lượng để thu thập phần thưởng của nó.
 Mỗi tuần, hai lần thu thập phần thưởng đầu tiên từ Tinh Thể Tàn Dư là miễn phí và không cần Bản Năng Lượng. Các lần thu thập miễn phí sẽ không được chuyển sang tuần tiếp theo.
 [Độ Khó]
-Pha SOL3 cao hơn mang đến những thử thách Khám Phá khó khăn hơn trong Ảo Cảnh, cùng với đó là nhiều phần thưởng hơn từ Tinh Thể Tàn Dư và Points Ảo Cảnh. Difficulty của Ảo Cảnh phụ thuộc vào Pha SOL3 mà cậu đang ở khi Ảo Cảnh được làm mới (04:00 mỗi thứ Hai). Việc điều chỉnh Pha SOL3 trong mỗi chu kỳ khám phá sẽ không ảnh hưởng đến độ khó và phần thưởng của chu kỳ hiện tại.</t>
+Pha SOL3 cao hơn mang đến những thử thách Khám Phá khó khăn hơn trong Ảo Cảnh, cùng với đó là nhiều phần thưởng hơn từ Tinh Thể Tàn Dư và Điểm Ảo Cảnh. Độ khó của Ảo Cảnh phụ thuộc vào Pha SOL3 mà cậu đang ở khi Ảo Cảnh được làm mới (04:00 mỗi thứ Hai). Việc điều chỉnh Pha SOL3 trong mỗi chu kỳ khám phá sẽ không ảnh hưởng đến độ khó và phần thưởng của chu kỳ hiện tại.</t>
         </is>
       </c>
     </row>
@@ -4588,17 +4588,17 @@
         <is>
           <t>Ký ức quá khứ chôn vùi sâu trong giấc mơ, và chìa khóa để khám phá nằm trong tay cậu. Đừng quên, chỉ trong giấc mơ, câu trả lời mới được hé lộ.
 [Hỗ Trợ Giấc Mơ]
-Kích hoạt thủ công trạng thái Giấc Mơ Tiên Tri khi Năng Lượng Giấc Mơ đạt 500 điểm. Trong trạng thái này, Hiệu Ứng và một số Ẩn Dụ sẽ được tăng cường, Crit. Rate và Tái Tạo Năng Lượng của tất cả Resonators trong đội tăng lần lượt 50% và 100%. Cooldown chiêu sau khi sử dụng Resonance Skill hoặc Resonance Liberation giảm 50%, kích hoạt mỗi 4 giây. Giấc Mơ Tiên Tri kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mơ khi kết thúc.
+Kích hoạt thủ công trạng thái Giấc Mơ Tiên Tri khi Năng Lượng Giấc Mơ đạt 500 điểm. Trong trạng thái này, Hiệu Ứng và một số Ẩn Dụ sẽ được tăng cường, Crit. Rate và Tái Tạo Năng Lượng của tất cả Resonator trong đội tăng lần lượt 50% và 100%. Thời gian hồi chiêu sau khi sử dụng Resonance Skill hoặc Resonance Liberation giảm 50%, kích hoạt mỗi 4 giây. Giấc Mơ Tiên Tri kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mơ khi kết thúc.
 [Khám Phá]
-- Chọn ba Resonators và bước vào những trận chiến hoành tráng trong Ảo Cảnh.
-- Skills Echo, Stats, Cấp Độ, Chuỗi Resonance và Vũ Khí của Resonators sẽ được giữ nguyên trong sự kiện.
+- Chọn ba Resonator và bước vào những trận chiến hoành tráng trong Ảo Cảnh.
+- Kỹ Năng Tiếng Vọng, Chỉ Số, Cấp Độ, Resonance Chain và Vũ Khí của Resonator sẽ được giữ nguyên trong sự kiện.
 - Trong Ảo Cảnh, cậu có thể nhận được những tăng cường mạnh mẽ từ Ẩn Dụ. Hiệu Ứng và một số Ẩn Dụ sẽ mang lại hiệu ứng bổ sung khi Giấc Mơ Tiên Tri được kích hoạt thông qua Hỗ Trợ Giấc Mơ.
-- Mỗi trận chiến trong Ảo Cảnh sẽ đối đầu với những kẻ địch khác nhau. Hoàn thành những thử thách này để kiếm Points Ảo Cảnh và đạt các mốc thưởng để nhận những phần quà hậu hĩnh.
+- Mỗi trận chiến trong Ảo Cảnh sẽ đối đầu với những kẻ địch khác nhau. Hoàn thành những thử thách này để kiếm Điểm Ảo Cảnh và đạt các mốc thưởng để nhận những phần quà hậu hĩnh.
 [Tinh Thể Tàn Dư]
 Một Tinh Thể Tàn Dư sẽ xuất hiện trong Khu Vực Ký Ức sau khi đánh bại những kẻ địch mạnh nhất ở sâu nhất trong Ảo Cảnh. Sử dụng Bản Năng Lượng để thu thập phần thưởng của nó.
 Mỗi tuần, hai lần thu thập phần thưởng đầu tiên từ Tinh Thể Tàn Dư là miễn phí và không cần Bản Năng Lượng. Các lần thu thập miễn phí sẽ không được chuyển sang tuần tiếp theo.
 [Độ Khó]
-Pha SOL3 cao hơn mang đến những thử thách Khám Phá khó khăn hơn trong Ảo Cảnh, cùng với đó là nhiều phần thưởng hơn từ Tinh Thể Tàn Dư và Points Ảo Cảnh. Difficulty của Ảo Cảnh phụ thuộc vào Pha SOL3 mà cậu đang ở khi Ảo Cảnh được làm mới (04:00 mỗi thứ Hai). Việc điều chỉnh Pha SOL3 trong mỗi chu kỳ khám phá sẽ không ảnh hưởng đến độ khó và phần thưởng của chu kỳ hiện tại.</t>
+Pha SOL3 cao hơn mang đến những thử thách Khám Phá khó khăn hơn trong Ảo Cảnh, cùng với đó là nhiều phần thưởng hơn từ Tinh Thể Tàn Dư và Điểm Ảo Cảnh. Độ khó của Ảo Cảnh phụ thuộc vào Pha SOL3 mà cậu đang ở khi Ảo Cảnh được làm mới (04:00 mỗi thứ Hai). Việc điều chỉnh Pha SOL3 trong mỗi chu kỳ khám phá sẽ không ảnh hưởng đến độ khó và phần thưởng của chu kỳ hiện tại.</t>
         </is>
       </c>
     </row>
@@ -4677,17 +4677,17 @@
         <is>
           <t>Ký ức quá khứ chôn vùi sâu trong giấc mơ, và chìa khóa để khám phá nằm trong tay cậu. Đừng quên, chỉ trong giấc mơ, câu trả lời mới được hé lộ.
 [Hỗ Trợ Giấc Mơ]
-Kích hoạt thủ công trạng thái Giấc Mơ Tiên Tri khi Năng Lượng Giấc Mơ đạt 500 điểm. Trong trạng thái này, Hiệu Ứng và một số Ẩn Dụ sẽ được tăng cường, Crit. Rate và Tái Tạo Năng Lượng của tất cả Resonators trong đội tăng lần lượt 50% và 100%. Cooldown chiêu sau khi sử dụng Resonance Skill hoặc Resonance Liberation giảm 50%, kích hoạt mỗi 4 giây. Giấc Mơ Tiên Tri kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mơ khi kết thúc.
+Kích hoạt thủ công trạng thái Giấc Mơ Tiên Tri khi Năng Lượng Giấc Mơ đạt 500 điểm. Trong trạng thái này, Hiệu Ứng và một số Ẩn Dụ sẽ được tăng cường, Crit. Rate và Tái Tạo Năng Lượng của tất cả Resonator trong đội tăng lần lượt 50% và 100%. Thời gian hồi chiêu sau khi sử dụng Resonance Skill hoặc Resonance Liberation giảm 50%, kích hoạt mỗi 4 giây. Giấc Mơ Tiên Tri kéo dài 10 giây và tiêu hao toàn bộ Năng Lượng Giấc Mơ khi kết thúc.
 [Khám Phá]
-- Chọn ba Resonators và bước vào những trận chiến hoành tráng trong Ảo Cảnh.
-- Skills Echo, Stats, Cấp Độ, Chuỗi Resonance và Vũ Khí của Resonators sẽ được giữ nguyên trong sự kiện.
+- Chọn ba Resonator và bước vào những trận chiến hoành tráng trong Ảo Cảnh.
+- Kỹ Năng Tiếng Vọng, Chỉ Số, Cấp Độ, Resonance Chain và Vũ Khí của Resonator sẽ được giữ nguyên trong sự kiện.
 - Trong Ảo Cảnh, cậu có thể nhận được những tăng cường mạnh mẽ từ Ẩn Dụ. Hiệu Ứng và một số Ẩn Dụ sẽ mang lại hiệu ứng bổ sung khi Giấc Mơ Tiên Tri được kích hoạt thông qua Hỗ Trợ Giấc Mơ.
-- Mỗi trận chiến trong Ảo Cảnh sẽ đối đầu với những kẻ địch khác nhau. Hoàn thành những thử thách này để kiếm Points Ảo Cảnh và đạt các mốc thưởng để nhận những phần quà hậu hĩnh.
+- Mỗi trận chiến trong Ảo Cảnh sẽ đối đầu với những kẻ địch khác nhau. Hoàn thành những thử thách này để kiếm Điểm Ảo Cảnh và đạt các mốc thưởng để nhận những phần quà hậu hĩnh.
 [Tinh Thể Tàn Dư]
 Một Tinh Thể Tàn Dư sẽ xuất hiện trong Khu Vực Ký Ức sau khi đánh bại những kẻ địch mạnh nhất ở sâu nhất trong Ảo Cảnh. Sử dụng Bản Năng Lượng để thu thập phần thưởng của nó.
 Mỗi tuần, hai lần thu thập phần thưởng đầu tiên từ Tinh Thể Tàn Dư là miễn phí và không cần Bản Năng Lượng. Các lần thu thập miễn phí sẽ không được chuyển sang tuần tiếp theo.
 [Độ Khó]
-Pha SOL3 cao hơn mang đến những thử thách Khám Phá khó khăn hơn trong Ảo Cảnh, cùng với đó là nhiều phần thưởng hơn từ Tinh Thể Tàn Dư và Points Ảo Cảnh. Difficulty của Ảo Cảnh phụ thuộc vào Pha SOL3 mà cậu đang ở khi Ảo Cảnh được làm mới (04:00 mỗi thứ Hai). Việc điều chỉnh Pha SOL3 trong mỗi chu kỳ khám phá sẽ không ảnh hưởng đến độ khó và phần thưởng của chu kỳ hiện tại.</t>
+Pha SOL3 cao hơn mang đến những thử thách Khám Phá khó khăn hơn trong Ảo Cảnh, cùng với đó là nhiều phần thưởng hơn từ Tinh Thể Tàn Dư và Điểm Ảo Cảnh. Độ khó của Ảo Cảnh phụ thuộc vào Pha SOL3 mà cậu đang ở khi Ảo Cảnh được làm mới (04:00 mỗi thứ Hai). Việc điều chỉnh Pha SOL3 trong mỗi chu kỳ khám phá sẽ không ảnh hưởng đến độ khó và phần thưởng của chu kỳ hiện tại.</t>
         </is>
       </c>
     </row>
@@ -4765,18 +4765,18 @@
       <c r="M59" t="inlineStr">
         <is>
           <t>[Cấp Độ Cải Tiến Xe]
-Cấp Độ Cải Tiến Xe có thể được nâng lên bằng cách hoàn thành nhiệm vụ ở Lahai-Roi, mở Supply Chest và đánh bại kẻ địch. Đạt đến cấp độ cải tiến tiếp theo sẽ cải thiện hiệu suất xe và mở khóa nhiều phần thưởng hấp dẫn.
-Đánh bại kẻ địch ở Lahai-Roi (bao gồm Discord Nest, Challenge Boss và Void Storm) để tích lũy EXP Cải Tiến, tối đa 5.000 điểm mỗi ngày. Limited này được đặt lại vào lúc 04:00 sáng theo giờ máy chủ. EXP Cải Tiến sẽ không thể kiếm thêm khi đạt đến cấp độ cải tiến tối đa.
+Cấp Độ Cải Tiến Xe có thể được nâng lên bằng cách hoàn thành nhiệm vụ ở Lahai-Roi, mở Rương Vật Tư và đánh bại kẻ địch. Đạt đến cấp độ cải tiến tiếp theo sẽ cải thiện hiệu suất xe và mở khóa nhiều phần thưởng hấp dẫn.
+Đánh bại kẻ địch ở Lahai-Roi (bao gồm Tổ Tacet Discord, Thử Thách Trùm và Bão Hư Không) để tích lũy Điểm Kinh Nghiệm Cải Tiến, tối đa 5.000 điểm mỗi ngày. Giới hạn này được đặt lại vào lúc 04:00 sáng theo giờ máy chủ. Điểm Kinh Nghiệm Cải Tiến sẽ không thể kiếm thêm khi đạt đến cấp độ cải tiến tối đa.
 [Thông Số Xe]
-Một số thông số của xe có thể được cải thiện bằng cách nâng cấp Cấp Độ Cải Tiến. Tấn Công và Độ Mạnh Shield của xe tăng theo Pha SOL3 của bạn.
+Một số thông số của xe có thể được cải thiện bằng cách nâng cấp Cấp Độ Cải Tiến. ATK và Độ Mạnh Khiên của xe tăng theo Pha SOL3 của bạn.
 [Mô-đun Mở Rộng Xe]
-Hoàn thành Nhiệm Vụ Cải Tiến Xe để nhận Points Cải Tiến cho các mô-đun cụ thể, sau đó dùng những điểm đó để nâng cấp mô-đun và mở khóa thêm chức năng cho xe.
-Mô-đun Mở Rộng gồm hai loại: Cốt Core và Chuyên Biệt. Mô-đun Chuyên Biệt chỉ có hiệu lực sau khi được nâng cấp và lắp đặt vào Mô-đun Mở Rộng Xe tương ứng. Core Mô-đun có thể lắp đặt vào bất kỳ Mô-đun Mở Rộng Xe nào để nhận hiệu ứng khi được nâng cấp.
+Hoàn thành Nhiệm Vụ Cải Tiến Xe để nhận Điểm Cải Tiến cho các mô-đun cụ thể, sau đó dùng những điểm đó để nâng cấp mô-đun và mở khóa thêm chức năng cho xe.
+Mô-đun Mở Rộng gồm hai loại: Cốt Lõi và Chuyên Biệt. Mô-đun Chuyên Biệt chỉ có hiệu lực sau khi được nâng cấp và lắp đặt vào Mô-đun Mở Rộng Xe tương ứng. Mô-đun Cốt Lõi có thể lắp đặt vào bất kỳ Mô-đun Mở Rộng Xe nào để nhận hiệu ứng khi được nâng cấp.
 [Nhiệm Vụ Cải Tiến Xe]
-Mỗi Mô-đun Mở Rộng có Points Cải Tiến và Nhiệm Vụ Cải Tiến tương ứng.
-Nhiệm Vụ Cải Tiến gồm ba loại: Thường Xuyên, Limited Thời Gian và Định Kỳ.
-Nhiệm vụ Limited Thời Gian phải được hoàn thành trong thời gian quy định. Quá thời hạn, nhiệm vụ sẽ không thể tiếp tục và không nhận được phần thưởng nếu chưa hoàn thành.
-Các Nhiệm Vụ Limited Thời Gian trong phiên bản này sẽ được thay thế bằng Nhiệm Vụ Định Kỳ sau bản cập nhật tiếp theo. Nhiệm Vụ Định Kỳ cũng là nhiệm vụ thường xuyên. Bạn có thể hoàn thành các nhiệm vụ này để kiếm đủ điểm cho Mô-đun Mở Rộng tương ứng.</t>
+Mỗi Mô-đun Mở Rộng có Điểm Cải Tiến và Nhiệm Vụ Cải Tiến tương ứng.
+Nhiệm Vụ Cải Tiến gồm ba loại: Thường Xuyên, Giới Hạn Thời Gian và Định Kỳ.
+Nhiệm vụ Giới Hạn Thời Gian phải được hoàn thành trong thời gian quy định. Quá thời hạn, nhiệm vụ sẽ không thể tiếp tục và không nhận được phần thưởng nếu chưa hoàn thành.
+Các Nhiệm Vụ Giới Hạn Thời Gian trong phiên bản này sẽ được thay thế bằng Nhiệm Vụ Định Kỳ sau bản cập nhật tiếp theo. Nhiệm Vụ Định Kỳ cũng là nhiệm vụ thường xuyên. Bạn có thể hoàn thành các nhiệm vụ này để kiếm đủ điểm cho Mô-đun Mở Rộng tương ứng.</t>
         </is>
       </c>
     </row>
@@ -4847,7 +4847,7 @@
           <t>Về Sự Kiện
 Sự kiện hợp tác chủ đề với Persona 5 Royal, Persona 3 Reload và Sonic the Hedgehog. Hoàn thành nhiệm vụ sự kiện để nhận Bộ Vỏ Xe Hợp Tác và vật liệu.
 Điều Kiện Tham Gia
-Đạt Cấp Liên Minh 8 và kích hoạt Điểm Resonance Học Viện Startorch trong Nhiệm Vụ Chính "Điều Gì Nung Nấu Dưới Lãnh Nguyên".</t>
+Đạt Cấp Liên Minh 8 và kích hoạt Điểm Cộng Hưởng Học Viện Startorch trong Nhiệm Vụ Chính "Điều Gì Nung Nấu Dưới Lãnh Nguyên".</t>
         </is>
       </c>
     </row>
@@ -4912,7 +4912,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Tiêu diệt kẻ địch ở Lahai-Roi (bao gồm Discord Nest, Challenge Boss và Void Storm) để tích lũy Điểm Modding, tối đa 5.000 điểm mỗi ngày. Giới hạn này sẽ được làm mới vào lúc 04:00 sáng theo giờ máy chủ. Khi đạt cấp Modding tối đa, bạn sẽ không thể kiếm thêm Điểm Modding nữa.</t>
+          <t>Tiêu diệt kẻ địch ở Lahai-Roi (bao gồm Tổ Tacet Discord, Thử Thách Trùm và Bão Hư Không) để tích lũy Điểm Modding, tối đa 5.000 điểm mỗi ngày. Giới hạn này sẽ được làm mới vào lúc 04:00 sáng theo giờ máy chủ. Khi đạt cấp Modding tối đa, bạn sẽ không thể kiếm thêm Điểm Modding nữa.</t>
         </is>
       </c>
     </row>
@@ -4980,10 +4980,10 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>[Cấp Độ Resonators]
-Khi SOL3 Giai đoạn của bạn tăng lên, cấp độ Resonators Hỗ Trợ có thể sử dụng sẽ tăng đến giới hạn cấp độ của SOL3 Giai đoạn hiện tại.
+          <t>[Cấp Độ Resonator]
+Khi Giai Đoạn SOL3 của bạn tăng lên, cấp độ Resonator Hỗ Trợ có thể sử dụng sẽ tăng đến giới hạn cấp độ của Giai Đoạn SOL3 hiện tại.
 [Cấp Đồng Bộ]
-Nếu bạn đạt SOL3 Giai đoạn mới trong trận chiến khi có Resonators Hỗ Trợ trong đội, họ sẽ không thể tự động tăng cấp. Bạn có thể tăng cấp cho Resonators Hỗ Trợ sau đó bằng cách thủ công qua trang sự kiện, sau khi rời khỏi trạng thái chiến đấu.</t>
+Nếu bạn đạt Giai Đoạn SOL3 mới trong trận chiến khi có Resonator Hỗ Trợ trong đội, họ sẽ không thể tự động tăng cấp. Bạn có thể tăng cấp cho Resonator Hỗ Trợ sau đó bằng cách thủ công qua trang sự kiện, sau khi rời khỏi trạng thái chiến đấu.</t>
         </is>
       </c>
     </row>
@@ -5050,7 +5050,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Dùng Spacetrek Observatory để phát tín hiệu điều khiển, điều chỉnh Mảng Dự Báo Bầu Trời nhằm tạo thời tiết mô phỏng trên toàn Lahai-Roi.
+          <t>Dùng Đài Thiên Văn Spacetrek để phát tín hiệu điều khiển, điều chỉnh Mảng Dự Báo Bầu Trời nhằm tạo thời tiết mô phỏng trên toàn Lahai-Roi.
 Một số loại thời tiết chỉ có thể mô phỏng vào thời điểm và khu vực nhất định. Hãy đảm bảo bạn đã điều chỉnh đúng thời gian hoặc di chuyển đến khu vực tương ứng để mô phỏng.
 Một số loại thời tiết có thể kích hoạt sự kiện đặc biệt.</t>
         </is>
@@ -5120,10 +5120,10 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Trong Khu Void Storm có hai đợt kẻ địch.
-Do ảnh hưởng của Void Storm, Resonators sẽ mất HP mỗi giây, hiệu quả hồi máu và Hiệu Quả Healing bị giảm một nửa.
-Resonators sẽ bị Trạng Thái Warp khi trúng đòn, làm tăng sát thương nhận vào.
-Sử dụng Tune Break lên kẻ địch ở Đợt 2 sẽ gây sát thương cực lớn, hồi máu cho Resonators và loại bỏ trạng thái Warp.</t>
+          <t>Trong Khu Bão Hư Không có hai đợt kẻ địch.
+Do ảnh hưởng của Bão Hư Không, Resonator sẽ mất HP mỗi giây, hiệu quả hồi máu và Hiệu Quả Hồi Phục bị giảm một nửa.
+Resonator sẽ bị Trạng Thái Warp khi trúng đòn, làm tăng sát thương nhận vào.
+Sử dụng Tune Break lên kẻ địch ở Đợt 2 sẽ gây sát thương cực lớn, hồi máu cho Resonator và loại bỏ trạng thái Warp.</t>
         </is>
       </c>
     </row>
@@ -5189,8 +5189,8 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Hoàn thành Void Storm Zone lần đầu để nhận Tidal Heritages hiếm.
-Kẻ địch trong Void Storm Zone sẽ hồi sinh mỗi ngày. Lặp lại thử thách để kiếm EXP Modding cho xe máy thám hiểm của bạn.</t>
+          <t>Hoàn thành Khu Vực Bão Hư Không lần đầu để nhận Tidal Heritages hiếm.
+Kẻ địch trong Khu Vực Bão Hư Không sẽ hồi sinh mỗi ngày. Lặp lại thử thách để kiếm EXP Modding cho xe máy thám hiểm của bạn.</t>
         </is>
       </c>
     </row>
@@ -5255,7 +5255,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Khi điều khiển xe máy thám hiểm, bạn có thể sử dụng các tính năng như Tăng Tốc, Phóng Nhanh, Trượt Drift và Bật Nhảy. Trong lúc di chuyển, một trường lực sẽ được triển khai quanh xe, và Resonator sẽ bị buộc phải xuống xe nếu chịu sát thương hoặc bị kiểm soát sau khi trường lực biến mất.</t>
+          <t>Khi điều khiển xe máy thám hiểm, bạn có thể sử dụng các tính năng như Tăng Tốc, Phóng Nhanh, Trượt Drift và Nhảy Bật. Trong lúc di chuyển, một trường lực sẽ được triển khai quanh xe, và Resonator sẽ bị buộc phải xuống xe nếu chịu sát thương hoặc bị kiểm soát sau khi trường lực biến mất.</t>
         </is>
       </c>
     </row>
@@ -5321,7 +5321,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Khi lái xe máy trong khuôn viên Startorch Academy, bạn phải tuân thủ giới hạn tốc độ và không được Boost. Một số khu vực sẽ hạn chế xe máy đi vào.
+          <t>Khi lái xe máy trong khuôn viên Học viện Startorch, bạn phải tuân thủ giới hạn tốc độ và không được Boost. Một số khu vực sẽ hạn chế xe máy đi vào.
 Lái xe máy và Boost trên những con đường được trang trí sẽ không tiêu hao Năng Lượng.</t>
         </is>
       </c>
@@ -5647,7 +5647,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Dodge thành công để kích hoạt Tune Break</t>
+          <t>Né thành công để kích hoạt Tune Break</t>
         </is>
       </c>
     </row>
@@ -6039,7 +6039,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Một số kẻ địch trong Nhiệm Vụ Chính "Khúc Ca Sunrise Thứ Hai" có thể bị tiêu diệt ngay lập tức bằng Tune Break.</t>
+          <t>Một số kẻ địch trong Nhiệm Vụ Chính "Khúc Ca Bình Minh Thứ Hai" có thể bị tiêu diệt ngay lập tức bằng Phá Giai Điệu.</t>
         </is>
       </c>
     </row>
@@ -6104,7 +6104,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Một số kẻ địch trong Nhiệm Vụ Chính "Khúc Ca Sunrise Thứ Hai" có thể bị tiêu diệt ngay lập tức bằng Tune Break.</t>
+          <t>Một số kẻ địch trong Nhiệm Vụ Chính "Khúc Ca Bình Minh Thứ Hai" có thể bị tiêu diệt ngay lập tức bằng Phá Giai Điệu.</t>
         </is>
       </c>
     </row>
@@ -6169,7 +6169,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Một số kẻ địch trong Nhiệm Vụ Chính "Khúc Ca Sunrise Thứ Hai" có thể bị tiêu diệt ngay lập tức bằng Tune Break.</t>
+          <t>Một số kẻ địch trong Nhiệm Vụ Chính "Khúc Ca Bình Minh Thứ Hai" có thể bị tiêu diệt ngay lập tức bằng Phá Giai Điệu.</t>
         </is>
       </c>
     </row>
@@ -6234,7 +6234,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Một số đòn tấn công của Resonators sẽ tích lũy Mức Lệch Nhịp lên một số kẻ địch. Khi Mức Lệch Nhịp đầy, kẻ địch sẽ rơi vào trạng thái &lt;color=#ffd12f&gt;Mistune&lt;/color&gt;.</t>
+          <t>Một số đòn tấn công của Resonator sẽ tích lũy Mức Lệch Nhịp lên một số kẻ địch. Khi Mức Lệch Nhịp đầy, kẻ địch sẽ rơi vào trạng thái &lt;color=#ffd12f&gt;Mistune&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -6299,7 +6299,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Một chỉ báo sẽ hiện lên khi Resonator tấn công hoặc Dodge thành công kẻ địch trong trạng thái Mistune. {Cus:Ipt,Touch=Touch PC=press Gamepad=press} để thực hiện &lt;color=#ffd12f&gt;Tune Break&lt;/color&gt; mạnh mẽ, phá vỡ trạng thái Mistune của kẻ địch.</t>
+          <t>Một chỉ báo sẽ hiện lên khi Resonator tấn công hoặc né thành công kẻ địch trong trạng thái Mistune. {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} để thực hiện &lt;color=#ffd12f&gt;Tune Break&lt;/color&gt; mạnh mẽ, phá vỡ trạng thái Mistune của kẻ địch.</t>
         </is>
       </c>
     </row>
@@ -6624,7 +6624,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Twin Nova: Collapsar Blade và Nova Song Sinh: Pháo Đài Tinh Vân sẽ chịu thêm sát thương trong một khoảng thời gian nhất định sau khi bị Tune Break đánh trúng.</t>
+          <t>Tân Tinh Song Sinh: Collapsar Blade and Twin Nova: Nebulous Cannon take more DMG for a certain period of time after being hit by Tune Break.</t>
         </is>
       </c>
     </row>
@@ -6949,7 +6949,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Sau khi hồi phục từ trạng thái Bất Động lần đầu, Dreamless bước vào trạng thái Loạn Khí Đe Dọa. Trong trạng thái này, Dreamless phóng ra những Ngọn Giáo Hủy Diệt và Véc-tơ Hỗn Mang có thể đánh lệch. Nếu đánh lệch thành công, Concerto Vibrancy của Dreamless sẽ giảm. Dodge tránh Ngọn Giáo Hủy Diệt và Véc-tơ Hỗn Mang sẽ không kích hoạt Dodge Thành Công.</t>
+          <t>Sau khi hồi phục từ trạng thái Bất Động lần đầu, Vô Mộng bước vào trạng thái Loạn Khí Đe Dọa. Trong trạng thái này, Vô Mộng phóng ra những Ngọn Giáo Hủy Diệt và Véc-tơ Hỗn Mang có thể đánh lệch. Nếu đánh lệch thành công, Sức Mạnh Rung Động của Vô Mộng sẽ giảm. Né tránh Ngọn Giáo Hủy Diệt và Véc-tơ Hỗn Mang sẽ không kích hoạt Né Tránh Thành Công.</t>
         </is>
       </c>
     </row>
@@ -7080,8 +7080,8 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Sabercat Prowler thiếu thị lực và dựa vào sóng tần số Dodge được để xác định vị trí kẻ địch.
-Trước khi xác định được vị trí kẻ địch, Sabercat Prowler sẽ không chủ động tấn công và sẽ phát ra sóng tần số định vị theo chu kỳ để dò tìm kẻ địch. Một khi xác định được kẻ địch, nó sẽ bắt đầu tấn công và tiếp tục phát sóng định vị để theo dõi chuyển động của kẻ địch.</t>
+          <t>Kẻ Rình Rập Mèo Đao thiếu thị lực và dựa vào sóng tần số né tránh được để xác định vị trí kẻ địch.
+Trước khi xác định được vị trí kẻ địch, Kẻ Rình Rập Mèo Đao sẽ không chủ động tấn công và sẽ phát ra sóng tần số định vị theo chu kỳ để dò tìm kẻ địch. Một khi xác định được kẻ địch, nó sẽ bắt đầu tấn công và tiếp tục phát sóng định vị để theo dõi chuyển động của kẻ địch.</t>
         </is>
       </c>
     </row>
@@ -7211,7 +7211,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Lahai-Roi Resonance Beacon</t>
+          <t>Đèn Tần Số Lahai-Roi</t>
         </is>
       </c>
     </row>
@@ -7276,7 +7276,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Sau khi vượt qua vùng rào cản và vào chế độ hack chậm, &lt;color=#ffd12f&gt;rotate the camera to aim&lt;/color&gt; nhiều mục tiêu. Khi các mục tiêu đã được đánh dấu, {Cus:Ipt,Touch=tap PC=press Gamepad=press} nút để hoàn tất hack.</t>
+          <t>Sau khi vượt qua vùng rào cản và vào chế độ hack chậm, &lt;color=#ffd12f&gt;xoay camera để ngắm&lt;/color&gt; nhiều mục tiêu. Khi các mục tiêu đã được đánh dấu, {Cus:Ipt,Touch=tap PC=press Gamepad=press} nút để hoàn tất hack.</t>
         </is>
       </c>
     </row>
@@ -7408,7 +7408,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Resonance Beacon sẽ tự động kích hoạt khi bạn di chuyển vào phạm vi của nó.</t>
+          <t>Điểm Cộng Hưởng sẽ tự động kích hoạt khi bạn di chuyển vào phạm vi của nó.</t>
         </is>
       </c>
     </row>
@@ -7473,7 +7473,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Khi điều khiển mô tô, phạm vi tương tác của ngươi và Terminal được mở rộng.</t>
+          <t>Khi điều khiển mô tô, phạm vi tương tác của ngươi và Thiết bị đầu cuối được mở rộng.</t>
         </is>
       </c>
     </row>
@@ -7538,7 +7538,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Khi đến gần đường trượt, nút Nhảy sẽ sáng lên và chuyển thành nút Trượt Ray. {Cus:Ipt,Touch=Touch PC=Ấn Gamepad=Ấn} nút này để xe máy nhảy lên ray và bắt đầu Trượt Ray. Hạ cánh từ trên không xuống ray cũng sẽ kích hoạt Trượt Ray.</t>
+          <t>Khi đến gần đường trượt, nút Nhảy sẽ sáng lên và chuyển thành nút Trượt Ray. {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} nút này để xe máy nhảy lên ray và bắt đầu Trượt Ray. Hạ cánh từ trên không xuống ray cũng sẽ kích hoạt Trượt Ray.</t>
         </is>
       </c>
     </row>
@@ -7737,9 +7737,9 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Vật phẩm Đặc Biệt có thể đặt vào Vùng Triển khai như Echoes, nhưng không trực tiếp tham gia vào Sân Chiến. Thay vào đó, chúng tác động đến trận đấu bằng những khả năng độc đáo như Triển khai Nhanh, rút thêm bài, hoặc tăng chỉ số.
+          <t>Vật phẩm Đặc Biệt có thể đặt vào Vùng Triển Khai như Echo, nhưng không trực tiếp tham gia vào Sân Chiến. Thay vào đó, chúng tác động đến trận đấu bằng những khả năng độc đáo như Triển Khai Nhanh, rút thêm bài, hoặc tăng chỉ số.
 Lưu ý rằng Vật phẩm Đặc Biệt thường có thời hạn sử dụng hoặc số lần dùng nhất định, và sẽ được xáo lại vào bộ bài sau khi hết hạn hoặc dùng hết số lần.
-Trong khi bạn chỉ có thể triển khai tối đa 4 Echoes, Vật phẩm Đặc Biệt không bị giới hạn như vậy.</t>
+Trong khi bạn chỉ có thể triển khai tối đa 4 Echo, Vật phẩm Đặc Biệt không bị giới hạn như vậy.</t>
         </is>
       </c>
     </row>
@@ -7804,7 +7804,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Bộ bài của cậu chỉ được phép chứa một thẻ Lãnh Địa. Mỗi Lãnh Địa sở hữu một Active Skill mạnh mẽ, như phục hồi Năng Lượng, rút thêm bài, hoặc Triển khai Nhanh. Chúng thậm chí có thể đạt được hiệu ứng mới nếu bộ bài của cậu đáp ứng một số điều kiện nhất định.</t>
+          <t>Bộ bài của cậu chỉ được phép chứa một thẻ Lãnh Địa. Mỗi Lãnh Địa sở hữu một Kỹ Năng Chủ Động mạnh mẽ, như phục hồi Năng Lượng, rút thêm bài, hoặc Triển Khai Nhanh. Chúng thậm chí có thể đạt được hiệu ứng mới nếu bộ bài của cậu đáp ứng một số điều kiện nhất định.</t>
         </is>
       </c>
     </row>
@@ -7871,9 +7871,9 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Dùng &lt;color=#ffd12f&gt;Directional Input&lt;/color&gt; để di chuyển Cube Blocker. Đưa &lt;color=#ffd12f&gt;Cube Blocker&lt;/color&gt; đến &lt;color=#ffd12f&gt;Endpoint Mô-đun&lt;/color&gt; để kích hoạt lại Khối Smartprint.
-Cube Blocker dài (1x2) phải căn chỉnh chính xác mới kích hoạt được quá trình biên dịch của Khối Smartprint.
-Nhấn &lt;color=#ffd12f&gt;Đặt lại&lt;/color&gt; để đặt lại tiến trình.</t>
+          <t>Dùng &lt;color=#ffd12f&gt;Điều Khiển Hướng&lt;/color&gt; để di chuyển Khối Chặn. Đưa &lt;color=#ffd12f&gt;Khối Chặn&lt;/color&gt; đến &lt;color=#ffd12f&gt;Mô-đun Điểm Cuối&lt;/color&gt; để kích hoạt lại Khối Smartprint.
+Khối Chặn dài (1x2) phải căn chỉnh chính xác mới kích hoạt được quá trình biên dịch của Khối Smartprint.
+Nhấn &lt;color=#ffd12f&gt;Nút Reset&lt;/color&gt; để đặt lại tiến trình.</t>
         </is>
       </c>
     </row>
@@ -7940,8 +7940,8 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Mô-đun Bật Dodgem Cube Blocker đi hai ô theo hướng mũi tên, giúp Khối vượt qua các thành phần hỏng trên mạch điện.
-Cube Blocker dài phải căn chỉnh hoàn hảo mới kích hoạt được mô-đun này.
+          <t>Mô-đun Bật ném Khối Chặn đi hai ô theo hướng mũi tên, giúp Khối vượt qua các thành phần hỏng trên mạch điện.
+Khối Chặn dài phải căn chỉnh hoàn hảo mới kích hoạt được mô-đun này.
 Mô-đun sẽ không hoạt động nếu không đủ không gian an toàn cho Khối ở hướng mục tiêu.</t>
         </is>
       </c>
@@ -8008,8 +8008,8 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Di chuyển Cube Blocker đến nút kết nối với Faulty Component để phá vỡ linh kiện.
-Cube Blocker Dài phải căn chỉnh hoàn hảo để kích hoạt mô-đun.</t>
+          <t>Di chuyển Khối Chặn đến nút kết nối với Linh Kiện Lỗi để phá vỡ linh kiện.
+Khối Chặn Dài phải căn chỉnh hoàn hảo để kích hoạt mô-đun.</t>
         </is>
       </c>
     </row>
@@ -8075,8 +8075,8 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Stability Accords: Tối đa ba đội có thể được triển khai. Hoàn thành thử thách bằng cách đánh bại tất cả kẻ địch trong một lượt.
-Singularity Expansion: Số đội triển khai không giới hạn. Sau khi đánh bại tất cả kẻ địch trong một lượt, kẻ địch mạnh hơn sẽ xuất hiện để đội tiếp theo đối phó.</t>
+          <t>Hiệp Ước Ổn Định: Tối đa ba đội có thể được triển khai. Hoàn thành thử thách bằng cách đánh bại tất cả kẻ địch trong một lượt.
+Mở Rộng Điểm Kỳ Dị: Số đội triển khai không giới hạn. Sau khi đánh bại tất cả kẻ địch trong một lượt, kẻ địch mạnh hơn sẽ xuất hiện để đội tiếp theo đối phó.</t>
         </is>
       </c>
     </row>
@@ -8206,7 +8206,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Trong giai đoạn Singularity Expansion, kẻ địch sẽ hồi sinh theo thứ tự trong danh sách sau khi bị đánh bại.</t>
+          <t>Trong giai đoạn Mở Rộng Điểm Kỳ Dị, kẻ địch sẽ hồi sinh theo thứ tự trong danh sách sau khi bị đánh bại.</t>
         </is>
       </c>
     </row>
@@ -8422,16 +8422,16 @@
       <c r="M114" t="inlineStr">
         <is>
           <t>Về nhiệm vụ
-Lollo Campaign lại gặp khủng hoảng! Để cứu vớt sự nghiệp của Maji và giữ cho khoản thu nhập thêm ấy không bị đứt đoạn, hãy giúp cậu ấy hoàn thành chương trình mới: Lollo Mùa Xuân!
+Chiến dịch Lollo lại gặp khủng hoảng! Để cứu vớt sự nghiệp của Maji và giữ cho khoản thu nhập thêm ấy không bị đứt đoạn, hãy giúp cậu ấy hoàn thành chương trình mới: Lollo Mùa Xuân!
 Hoàn thành nhiệm vụ hàng ngày để nhận Tem Lollo đổi lấy ân huệ. Tem Lollo có thể đổi lấy các kiện hàng đặc biệt từ Lollo Helper.
 Điều kiện tham gia
-Đạt Cấp Liên Minh 14 và kích hoạt Resonance Nexus tại Startorch Academy trong Nhiệm vụ Main "What Burns Beneath Frostlands" để mở khóa.
+Đạt Cấp Liên Minh 14 và kích hoạt Resonance Nexus tại Học viện Startorch trong Nhiệm vụ Chính "What Burns Beneath Frostlands" để mở khóa.
 Quy tắc sự kiện
-Trong sự kiện, cậu có thể hoàn thành Lollo Campaign để nhận một số lượng Tem Lollo nhất định.
+Trong sự kiện, cậu có thể hoàn thành Chiến dịch Lollo để nhận một số lượng Tem Lollo nhất định.
 Mỗi Tem Lollo có thể đổi lấy một kiện hàng đặc biệt từ Lollo Helper.
 Có 3 Kho hàng cho kiện hàng đặc biệt của Lollo Helper. Khi thu thập đủ tất cả kiện hàng trong một Kho, Kho tiếp theo sẽ được mở.
 Nếu giành được dịch vụ giao hàng đặc biệt Lollo Express, cậu có thể nhận tất cả kiện hàng trong Kho hiện tại.
-Sau khi sự kiện kết thúc, các Lollo Campaign chưa hoàn thành sẽ không còn khả dụng, và tất cả Tem Lollo còn lại sẽ bị thu hồi.</t>
+Sau khi sự kiện kết thúc, các Chiến dịch Lollo chưa hoàn thành sẽ không còn khả dụng, và tất cả Tem Lollo còn lại sẽ bị thu hồi.</t>
         </is>
       </c>
     </row>
@@ -8562,8 +8562,8 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>&lt;color=#ffd12f&gt;Domain&lt;/color&gt; sở hữu Active Skill mạnh mẽ, như hồi phục Năng Lượng, rút thêm bài, hay Triển khai Nhanh. Chúng thậm chí có thể nhận thêm hiệu ứng mới nếu bộ bài của ngươi đáp ứng điều kiện nhất định. Mỗi bộ bài phải chứa đúng 1 lá Domain.
-- &lt;color=#ffd12f&gt;Novelties&lt;/color&gt; có thể đặt vào Vùng Triển khai như Tâm Ảnh, nhưng không tham gia trực tiếp vào Battle Stage. Một bộ bài phải có tổng cộng 20 Tâm Ảnh Thường hoặc Vật phẩm Độc Đáo để bắt đầu trận đấu.</t>
+          <t>&lt;color=#ffd12f&gt;Tổ Tacet&lt;/color&gt; sở hữu Kỹ Năng Chủ Động mạnh mẽ, như hồi phục Năng Lượng, rút thêm bài, hay Triển Khai Nhanh. Chúng thậm chí có thể nhận thêm hiệu ứng mới nếu bộ bài của ngươi đáp ứng điều kiện nhất định. Mỗi bộ bài phải chứa đúng 1 lá Tổ Tacet.
+- &lt;color=#ffd12f&gt;Vật phẩm Độc Đáo&lt;/color&gt; có thể đặt vào Vùng Triển Khai như Tâm Ảnh, nhưng không tham gia trực tiếp vào Giai Đoạn Chiến Đấu. Một bộ bài phải có tổng cộng 20 Tâm Ảnh Thường hoặc Vật phẩm Độc Đáo để bắt đầu trận đấu.</t>
         </is>
       </c>
     </row>
@@ -8649,15 +8649,15 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Event web "Mạch Đất Băng Giá" đã bắt đầu! Tham gia để nhận Astrites và các phần thưởng khác.
+          <t>Sự kiện web "Mạch Đất Băng Giá" đã bắt đầu! Tham gia để nhận Astrites và các phần thưởng khác.
 Hãy dấn thân vào vùng đất băng giá phủ đầy tuyết và giúp sửa chữa các đường dây cung cấp năng lượng. Nhận Astrites và Shell Credits trên đường đi!
-Hoàn thành nhiệm vụ để nhận thêm phần thưởng, bao gồm cả Advanced Sealed Tube.
+Hoàn thành nhiệm vụ để nhận thêm phần thưởng, bao gồm cả Ống Niêm Phong Cao Cấp.
 [Thời Gian]
 26/02/2026 04:00 sáng đến 12/03/2026 03:59 sáng (UTC+8)
 [Điều Kiện Tham Gia]
 Đạt Cấp Liên Minh 8
-[Details]
-1. Trong sự kiện, bạn có thể nhận phần thưởng trong game như Astrite, Shell Credits và Advanced Sealed Tube bằng cách vượt qua các giai đoạn sự kiện và hoàn thành nhiệm vụ.
+[Chi Tiết]
+1. Trong sự kiện, bạn có thể nhận phần thưởng trong game như Astrite, Shell Credits và Ống Niêm Phong Cao Cấp bằng cách vượt qua các giai đoạn sự kiện và hoàn thành nhiệm vụ.
 2. Lịch Mở Giai Đoạn Sự Kiện:
 Giai đoạn 1–2: Mở từ 26/02/2026, 04:00 sáng (UTC+8)
 Giai đoạn 3–4: Mở từ 27/02/2026, 04:00 sáng (Giờ Máy Chủ)
@@ -8665,11 +8665,11 @@
 3. Tất cả các giai đoạn sự kiện có thể được thách đấu nhiều lần.
 [Phần Thưởng]
 1. Hoàn thành tất cả các giai đoạn sự kiện để nhận tổng cộng 90 Astrite.
-2. Repair các đường dây đặc biệt trong giai đoạn sự kiện để nhận thêm phần thưởng tổng cộng 60.000 Shell Credit.
-3. Hoàn thành tất cả nhiệm vụ sự kiện để nhận 10 Astrite, 5 Advanced Energy Core, 5 Thuốc Resonance Cao Cấp, 5 Advanced Sealed Tube.
+2. Sửa chữa các đường dây đặc biệt trong giai đoạn sự kiện để nhận thêm phần thưởng tổng cộng 60.000 Shell Credit.
+3. Hoàn thành tất cả nhiệm vụ sự kiện để nhận 10 Astrite, 5 Lõi Năng Lượng Cao Cấp, 5 Thuốc Cộng Hưởng Cao Cấp, 5 Ống Niêm Phong Cao Cấp.
 [Lưu Ý]
 1. Các giai đoạn sự kiện sẽ không còn truy cập được sau khi sự kiện kết thúc. Hãy tham gia đúng thời hạn.
-2. Đảm bảo đăng nhập vào game và nhận phần thưởng trong thời gian diễn ra sự kiện. Rewards chưa nhận sẽ không còn sau khi sự kiện kết thúc.
+2. Đảm bảo đăng nhập vào game và nhận phần thưởng trong thời gian diễn ra sự kiện. Phần thưởng chưa nhận sẽ không còn sau khi sự kiện kết thúc.
 3. Nội dung của sự kiện web này không liên quan đến cốt truyện và thiết lập nhân vật trong game.</t>
         </is>
       </c>
@@ -8744,10 +8744,10 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Data Modification có thể thay đổi chỉ số của Echoes.
-Dùng Modifier để chuyển đổi Chỉ Số Chính đầu tiên của Echoes đã chọn sang chỉ số chỉ định. Chức năng này chỉ áp dụng cho Echoes 5 sao chưa nâng cấp.
-Mỗi lần Điều Chỉnh Chỉ Số Chính sẽ tiêu tốn 1 Modifier.
-Dùng Bộ Chuyển Đổi để điều chỉnh Ngẫu Nhiên các Chỉ Số Phụ của Echoes đã chọn, trừ những chỉ số đã khóa. Chức năng này chỉ áp dụng cho Echoes 5 sao đã tinh chỉnh toàn bộ.
+          <t>Điều Chỉnh Dữ Liệu có thể thay đổi chỉ số của Echo.
+Dùng Bộ Điều Chỉnh để chuyển đổi Chỉ Số Chính đầu tiên của Echo đã chọn sang chỉ số chỉ định. Chức năng này chỉ áp dụng cho Echo 5 sao chưa nâng cấp.
+Mỗi lần Điều Chỉnh Chỉ Số Chính sẽ tiêu tốn 1 Bộ Điều Chỉnh.
+Dùng Bộ Chuyển Đổi để điều chỉnh Ngẫu Nhiên các Chỉ Số Phụ của Echo đã chọn, trừ những chỉ số đã khóa. Chức năng này chỉ áp dụng cho Echo 5 sao đã tinh chỉnh toàn bộ.
 Số lượng Chỉ Số Phụ bị khóa sẽ quyết định số Bộ Chuyển Đổi tiêu hao mỗi lần Điều Chỉnh:
 Với 2 hoặc ít hơn chỉ số bị khóa, tiêu hao 1 Bộ Chuyển Đổi.
 Với 3 chỉ số bị khóa, tiêu hao 2 Bộ Chuyển Đổi.
@@ -8818,7 +8818,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Sự phối hợp chặt chẽ giữa H.E.R.M.E.S. và tay đua là yếu tố then chốt để vượt qua thử thách. Khi thử thách bắt đầu, H.E.R.M.E.S. sẽ tự động di chuyển dọc theo đường đua. Tay đua điều khiển trái-phải để Dodge chướng ngại vật và nhắm vào kẻ địch phía trước.</t>
+          <t>Sự phối hợp chặt chẽ giữa H.E.R.M.E.S. và tay đua là yếu tố then chốt để vượt qua thử thách. Khi thử thách bắt đầu, H.E.R.M.E.S. sẽ tự động di chuyển dọc theo đường đua. Tay đua điều khiển trái-phải để né tránh chướng ngại vật và nhắm vào kẻ địch phía trước.</t>
         </is>
       </c>
     </row>
@@ -8883,7 +8883,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Dữ liệu hệ thống dư thừa hiện hình thành kẻ địch trên đường đua. Hạ gục chúng để nhận hiệu ứng tăng cường, hoặc đâm xuyên qua để dọn đường. Nhưng đâm xuyên sẽ gây sát thương tương đương với HP còn lại của kẻ địch.</t>
+          <t>Dữ liệu hệ thống dư thừa hiện hình thành kẻ địch trên đường đua. Hạ gục chúng để nhận hiệu ứng tăng cường, hoặc đâm xuyên qua để dọn đường. Nhưng đâm xuyên sẽ gây DMG tương đương với HP còn lại của kẻ địch.</t>
         </is>
       </c>
     </row>
@@ -9013,7 +9013,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Nếu không đánh bại trùm trước khi đếm ngược kết thúc, nó sẽ đâm vào người lái xe, gây sát thương dựa trên HP còn lại của trùm. Tiến trình thử thách sẽ được lưu sau khi đánh bại trùm và nhận Vật phẩm Hỗ trợ.</t>
+          <t>Nếu không đánh bại trùm trước khi đếm ngược kết thúc, nó sẽ đâm vào người lái xe, gây DMG dựa trên HP còn lại của trùm. Tiến trình thử thách sẽ được lưu sau khi đánh bại trùm và nhận Vật phẩm Hỗ trợ.</t>
         </is>
       </c>
     </row>
@@ -9078,7 +9078,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Kẻ địch tinh nhuệ có HP cao hơn và khó nhằn hơn. Hãy tiêu diệt chúng nhanh chóng, nếu không người lái xe sẽ không thể Dodge và bị thương.</t>
+          <t>Kẻ địch tinh nhuệ có HP cao hơn và khó nhằn hơn. Hãy tiêu diệt chúng nhanh chóng, nếu không người lái xe sẽ không thể né tránh và bị thương.</t>
         </is>
       </c>
     </row>
@@ -9143,7 +9143,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Trong thử thách này, H.E.R.M.E.S. được trang bị Vũ Khí Main: Mô-đun Tia Điện. Nó bắn thêm một chùm tia laser theo chu kỳ đều đặn, gây sát thương cực lớn.</t>
+          <t>Trong thử thách này, H.E.R.M.E.S. được trang bị Vũ Khí Chính: Mô-đun Tia Điện. Nó bắn thêm một chùm tia laser theo chu kỳ đều đặn, gây sát thương cực lớn.</t>
         </is>
       </c>
     </row>
@@ -9208,7 +9208,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Trong thử thách này, H.E.R.M.E.S. được trang bị Vũ Khí Main: Mô-đun Lặp Lại. Nó bắn nhiều đạn trong một loạt ngắn, rất phù hợp để tập trung hỏa lực vào một mục tiêu duy nhất.</t>
+          <t>Trong thử thách này, H.E.R.M.E.S. được trang bị Vũ Khí Chính: Mô-đun Lặp Lại. Nó bắn nhiều đạn trong một loạt ngắn, rất phù hợp để tập trung hỏa lực vào một mục tiêu duy nhất.</t>
         </is>
       </c>
     </row>
@@ -9273,7 +9273,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Trong thử thách này, H.E.R.M.E.S. được trang bị Vũ Khí Main: Shotgun Mô-đun. Nó bắn nhiều đạn cùng lúc theo hình quạt rộng phía trước, rất hiệu quả khi đối phó với nhóm địch.</t>
+          <t>Trong thử thách này, H.E.R.M.E.S. được trang bị Vũ Khí Chính: Mô-đun Súng Ngắn. Nó bắn nhiều đạn cùng lúc theo hình quạt rộng phía trước, rất hiệu quả khi đối phó với nhóm địch.</t>
         </is>
       </c>
     </row>
@@ -9338,7 +9338,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Trong thử thách này, Hỗ Trợ Droid của H.E.R.M.E.S. được trang bị Giao Thức Tấn Công Quỹ Đạo. Khi tấn công, nó sẽ tự động khóa mục tiêu và gọi một đợt laser quỹ đạo, gây sát thương diện rộng lên khu vực chỉ định.</t>
+          <t>Trong thử thách này, Droid Hỗ Trợ của H.E.R.M.E.S. được trang bị Giao Thức Tấn Công Quỹ Đạo. Khi tấn công, nó sẽ tự động khóa mục tiêu và gọi một đợt laser quỹ đạo, gây sát thương diện rộng lên khu vực chỉ định.</t>
         </is>
       </c>
     </row>
@@ -9403,7 +9403,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Trong thử thách này, Hỗ Trợ Droid của H.E.R.M.E.S. được trang bị Sustained Combustion Protocol. Nó bắn ra các đạn gây hiệu ứng bỏng, liên tục gây sát thương lên mục tiêu.</t>
+          <t>Trong thử thách này, Droid Hỗ Trợ của H.E.R.M.E.S. được trang bị Giao Thức Đốt Cháy Liên Tục. Nó bắn ra các đạn gây hiệu ứng bỏng, liên tục gây sát thương lên mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -9468,7 +9468,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Trong thử thách này, Hỗ Trợ Droid của H.E.R.M.E.S. được trang bị Guided Missile Protocol. Nó sẽ tự động phóng một tên lửa dẫn đường, khóa và tấn công mục tiêu gần nhất.</t>
+          <t>Trong thử thách này, Droid Hỗ Trợ của H.E.R.M.E.S. được trang bị Giao Thức Tên Lửa Điều Khiển. Nó sẽ tự động phóng một tên lửa dẫn đường, khóa và tấn công mục tiêu gần nhất.</t>
         </is>
       </c>
     </row>
@@ -9598,7 +9598,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Kỹ Năng Của Rover: Bộ Bài</t>
+          <t>Kỹ Năng Của Vận Mệnh Giả: Rover's Skill</t>
         </is>
       </c>
     </row>
@@ -9665,9 +9665,9 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Nhiệm vụ: Dồn Exoswarm vào góc và chặn mọi lối thoát của chúng.
-Thất bại: Mục tiêu Exoswarm thoát khỏi khu vực và không còn xuất hiện.
-Mẹo của Abby: Exoswarm đi lạc rất dễ hoảng sợ. Hãy đặt những cây Gậy Shepherd quanh viền ngoài trước để dễ dàng hơn.</t>
+          <t>Nhiệm vụ: Corner the Exoswarm and block all their escape routes.
+Defeat: The target Exoswarm escape the area and can no longer be sighted.
+Abby's tip: Strayed Exoswarm are easily spooked. Place the Shepherd's Staffs around the outer edges first to make things easier.</t>
         </is>
       </c>
     </row>
@@ -9732,7 +9732,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Increase Đồng Hồ Cảm Xúc để mở khóa thêm trang trí khu vực và nội dung chơi.</t>
+          <t>Tăng Đồng Hồ Cảm Xúc để mở khóa thêm trang trí khu vực và nội dung chơi.</t>
         </is>
       </c>
     </row>
@@ -9933,9 +9933,9 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Khi một Cube Chặn đi qua &lt;color=#ffd12f&gt;Data Expansion Mô-đun&lt;/color&gt;, tất cả &lt;color=#ffd12f&gt;Digital Shadow Modules&lt;/color&gt; trên mạch sẽ &lt;color=#ffd12f&gt;chuyển đổi hình dạng&lt;/color&gt;.
-Tuy nhiên, nếu một Cube Chặn khác đã đứng sẵn trên &lt;color=#ffd12f&gt;Digital Shadow Mô-đun&lt;/color&gt;, &lt;color=#ffd12f&gt;Digital Shadow Mô-đun&lt;/color&gt; này sẽ không chuyển đổi hình dạng.
-Các Cube Chặn dài (1×2) phải căn chỉnh hoàn hảo với &lt;color=#ffd12f&gt;Data Expansion Mô-đun&lt;/color&gt; mới kích hoạt được hiệu ứng.</t>
+          <t>Khi một Cube Blocker đi qua &lt;color=#ffd12f&gt;Data Expansion Module&lt;/color&gt;, tất cả &lt;color=#ffd12f&gt;Digital Shadow Modules&lt;/color&gt; trên mạch sẽ &lt;color=#ffd12f&gt;thay đổi hình dạng&lt;/color&gt;.
+Tuy nhiên, nếu một Cube Blocker khác đã đứng trên &lt;color=#ffd12f&gt;Digital Shadow Module&lt;/color&gt;, thì module đó sẽ không thay đổi hình dạng.
+Cube Blocker dài (1×2) phải căn chỉnh chính xác với Data Expansion Module mới kích hoạt được hiệu ứng.</t>
         </is>
       </c>
     </row>
@@ -10001,7 +10001,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Rover có thể dùng kỹ năng này mỗi khi đối thủ rút Thẻ Hoang Dã để phủ quyết và bắt rút lại.
+          <t>Vận Mệnh Giả có thể dùng kỹ năng này mỗi khi đối thủ rút Thẻ Hoang Dã để phủ quyết và bắt rút lại.
 Chỉ được dùng một lần mỗi ván.</t>
         </is>
       </c>
@@ -10202,7 +10202,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Sigillum nhận một tầng Lạc Nhịp khi bị tấn công bởi Kỹ Năng Echoes, tối đa 5 tầng. Các Echoes cùng tên chỉ có thể kích hoạt hiệu ứng này một lần.
+          <t>Sigillum nhận một tầng Lạc Nhịp khi bị tấn công bởi Kỹ Năng Echo, tối đa 5 tầng. Các Echo cùng tên chỉ có thể kích hoạt hiệu ứng này một lần.
 Mỗi tầng Lạc Nhịp khiến Sigillum chịu thêm 10% Tổng Sát Thương. Khi đạt 5 tầng, Tổng Sát Thương nhận vào sẽ tăng thêm 30% nữa.</t>
         </is>
       </c>
@@ -10270,7 +10270,7 @@
       <c r="M141" t="inlineStr">
         <is>
           <t>Những lời chỉ dạy hồi nhỏ của cậu giờ đây đã trở thành lưỡi kiếm Aemeath vung lên để bảo vệ gia đình. Trong thời gian giới hạn, {Cus:Ipt,Touch=tap PC=press Gamepad=press} Resonance Skill để Aemeath thi triển những chiêu thức cậu từng dạy, tung ra đòn tấn công liên hoàn. 
-Trong thời gian này, Aemeath không thể sử dụng Kỹ Năng Echo hay Resonance Liberation.</t>
+Trong thời gian này, Aemeath không thể sử dụng Kỹ Năng Tiếng Vọng hay Resonance Liberation.</t>
         </is>
       </c>
     </row>
@@ -10400,7 +10400,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>Nếu Aemeath sử dụng Resonance Skill trong một khoảng thời gian nhất định sau khi thực hiện Basic Attack Stage 2, 3 hoặc 4, cô có thể thi triển Kỹ Năng Liên Hoàn Đồng Bộ Attack: Hợp Nhất Vũ Khí hoặc Đồng Bộ Attack: Tiếng Gọi Dawn. Sau đó, Aemeath có thể tiếp tục thực hiện Basic Attack hoặc Resonance Skill Liên Hoàn để tăng Synchronization Rate.</t>
+          <t>Nếu Aemeath sử dụng Resonance Skill trong một khoảng thời gian nhất định sau khi thực hiện Đòn Basic Attack Giai Đoạn 2, 3 hoặc 4, cô có thể thi triển Kỹ Năng Liên Hoàn Đồng Bộ Tấn Công: Hợp Nhất Vũ Khí hoặc Đồng Bộ Tấn Công: Tiếng Gọi Bình Minh. Sau đó, Aemeath có thể tiếp tục thực hiện Đòn Basic Attack hoặc Resonance Skill Liên Hoàn để tăng Tỷ Lệ Đồng Bộ.</t>
         </is>
       </c>
     </row>
@@ -10467,9 +10467,9 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Khi Synchronization Rate của cô đạt 50%, Aemeath có thể tung Resonance Skill trong một khoảng thời gian nhất định sau khi thực hiện Basic Attack Stage 4, sau đó sử dụng Kỹ Năng Liên Kết Seraphic Duet: Overture hoặc Seraphic Duet: Encore.
-Sau đó, Aemeath có thể sử dụng Resonance Skill Liên Kết Nâng Cao, Intro Skill hoặc Resonance Liberation để tăng Resonance Rate.
-Khi Synchronization Rate và Resonance Rate của cô đạt tối đa, Aemeath có thể sử dụng Resonance Liberation Nâng Cao - Heavenfall Edict: Finale.</t>
+          <t>Khi Tỷ Lệ Đồng Bộ của cô đạt 50%, Aemeath có thể tung Resonance Skill trong một khoảng thời gian nhất định sau khi thực hiện Đòn Basic Attack Giai Đoạn 4, sau đó sử dụng Kỹ Năng Liên Kết Seraphic Duet: Overture or Seraphic Duet: Encore.
+After that, Aemeath can cast Enhanced Chained Resonance Skill, Intro Skill, or Resonance Liberation to increase her Resonance Rate.
+When her Synchronization Rate and Resonance Rate are full, Aemeath can cast Enhanced Resonance Liberation - Heavenfall Edict: Finale.</t>
         </is>
       </c>
     </row>
@@ -10535,8 +10535,8 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>The Nameless Thám Hiểm bay lên không trung, chuẩn bị thi triển Phán Quyết Của Những Vì Sao.
-Hãy dùng các ngôi sao trên chiến trường để di chuyển lên bệ cao hơn, rồi dùng Grapple kéo bóng dáng trạm vũ trụ đổ nát xuống để chặn kỹ năng.</t>
+          <t>Kẻ Vô Danh Thám Hiểm bay lên không trung, chuẩn bị thi triển Phán Quyết Của Những Vì Sao.
+Hãy dùng các ngôi sao trên chiến trường để di chuyển lên bệ cao hơn, rồi dùng Móc Câu kéo bóng dáng trạm vũ trụ đổ nát xuống để chặn kỹ năng.</t>
         </is>
       </c>
     </row>
@@ -10603,9 +10603,9 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Khi ở trạng thái Đoạn Tần Căng Thẳng – Dịch Chuyển, Nameless Explorer nhận thêm một tầng Đoạn Tần Căng Thẳng – Nhiễu Loạn mỗi khi bị Tune Break Hủy trúng.
-Resonators có thể gây thêm tối đa 2 tầng Đoạn Tần Căng Thẳng – Nhiễu Loạn lên Nameless Explorer.
-Mỗi tầng Đoạn Tần Căng Thẳng làm tăng tổng sát thương nhận vào thêm 4%.</t>
+          <t>Khi ở trạng thái Đoạn Tần Căng Thẳng – Dịch Chuyển, Nhà Thám Hiểm Vô Danh nhận thêm một tầng Đoạn Tần Căng Thẳng – Nhiễu Loạn mỗi khi bị Đoạn Tần Phá Hủy trúng.
+Resonator có thể gây thêm tối đa 2 tầng Đoạn Tần Căng Thẳng – Nhiễu Loạn lên Nhà Thám Hiểm Vô Danh.
+Mỗi tầng Đoạn Tần Căng Thẳng làm tăng tổng DMG nhận vào thêm 4%.</t>
         </is>
       </c>
     </row>
@@ -10673,8 +10673,8 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Sau một thời gian chiến đấu, chúng sẽ bước vào trạng thái Feather Nộ và được tăng cường.
-Khi bị Tune Break đánh trúng, chúng sẽ thoát khỏi trạng thái Feather Nộ.
+          <t>Sau một thời gian chiến đấu, chúng sẽ bước vào trạng thái Lông Vũ Nộ và được tăng cường.
+Khi bị Tune Break đánh trúng, chúng sẽ thoát khỏi trạng thái Lông Vũ Nộ.
 Nếu bị Tune Break đánh trúng trong trạng thái Tune Rupture - Shifting, Kháng toàn bộ thuộc tính của chúng sẽ giảm mạnh.
 Thực hiện phản đòn thành công có thể làm tổn thương huy hiệu và đôi cánh của chúng, làm suy yếu đòn tấn công và giảm số lượng đạn tầm xa.</t>
         </is>
@@ -10808,7 +10808,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Xe máy thám hiểm giờ đã mở khóa thêm tính năng mới. Khi tiếp cận mục tiêu mà Hỗ Trợ Mô-đun có thể phá hủy, mô-đun sẽ tự động triệu hồi và ngắm bắn chúng.</t>
+          <t>Xe máy thám hiểm giờ đã mở khóa thêm tính năng mới. Khi tiếp cận mục tiêu mà Mô-đun Hỗ trợ có thể phá hủy, mô-đun sẽ tự động triệu hồi và ngắm bắn chúng.</t>
         </is>
       </c>
     </row>
@@ -10873,7 +10873,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Lõi năng lượng của Thiết Bị Truyền Khối Lượng có thể khôi phục các giọt Etheric Sea bị rối loạn bởi Vật Chất Hư Không về trạng thái ổn định, dọn sạch chướng ngại vật cản đường cậu.</t>
+          <t>Lõi năng lượng của Thiết Bị Truyền Khối Lượng có thể khôi phục các giọt Biển Ether bị rối loạn bởi Vật Chất Hư Không về trạng thái ổn định, dọn sạch chướng ngại vật cản đường cậu.</t>
         </is>
       </c>
     </row>
@@ -10940,9 +10940,9 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Trong Khu Void Storm ở Bề Mặt Frostlands có hai đợt kẻ địch.
-Do ảnh hưởng của Void Storm, Resonators sẽ mất HP mỗi giây, hiệu quả hồi máu và Hiệu Quả Healing bị giảm một nửa. Resonators sẽ bị Trạng Thái Warp khi trúng đòn, làm tăng sát thương nhận vào.
-Khi sử dụng Tune Break lên kẻ địch ở đợt thứ hai sẽ kích hoạt Recurrence Impact. Hiệu ứng này gây sát thương diện rộng, hồi máu cho Resonators đang hoạt động và loại bỏ tất cả trạng thái Warp.</t>
+          <t>Trong Khu Bão Hư Không ở Bề Mặt Frostlands có hai đợt kẻ địch.
+Do ảnh hưởng của Bão Hư Không, Resonator sẽ mất HP mỗi giây, hiệu quả hồi máu và Hiệu Quả Hồi Phục bị giảm một nửa. Resonator sẽ bị Trạng Thái Warp khi trúng đòn, làm tăng DMG nhận vào.
+Khi sử dụng Tune Break lên kẻ địch ở đợt thứ hai sẽ kích hoạt Recurrence Impact. Hiệu ứng này gây DMG diện rộng, hồi máu cho Resonator đang hoạt động và loại bỏ tất cả trạng thái Warp.</t>
         </is>
       </c>
     </row>
@@ -11082,11 +11082,11 @@
           <t>Về sự kiện
 Bên ngoài Mind Dive Arcade, một học sinh tên Tetoris mời gọi ngươi thử trò chơi mới nhất được mệnh danh là "Game of the Year" - Lahai-Roi Blocks. Cô ấy nói trò chơi này có rất nhiều đặc tính kỳ diệu...
 Điều kiện tham gia
-Đạt Cấp Liên minh 14, và kích hoạt Resonance Nexus của Startorch Academy trong Nhiệm vụ Main "What Burns Beneath Frostlands" để mở khóa.
+Đạt Cấp Liên minh 14, và kích hoạt Resonance Nexus của Học viện Startorch trong Nhiệm vụ Chính "What Burns Beneath Frostlands" để mở khóa.
 Quy tắc
 Mỗi ngày trong sự kiện sẽ mở khóa một màn chơi mới.
-Mỗi màn chơi có hai độ khó: Thường và Khó. Finish độ khó Thường để mở khóa thử thách Khó.
-Finish các mục tiêu của từng màn để nhận phần thưởng.</t>
+Mỗi màn chơi có hai độ khó: Thường và Khó. Hoàn thành độ khó Thường để mở khóa thử thách Khó.
+Hoàn thành các mục tiêu của từng màn để nhận phần thưởng.</t>
         </is>
       </c>
     </row>
@@ -11181,13 +11181,13 @@
           <t>[Ma trận Tận thế]
 Trong Ma trận Tận thế, kỹ năng của ngươi sẽ được thử thách qua những trận chiến khốc liệt. Đối đầu với kẻ địch và kiếm điểm để đổi lấy phần thưởng tương ứng.
 [Điều kiện tham gia]
-Đạt ít nhất 24 Huy hiệu trong một giai đoạn của Tower of Adversity và đạt tối thiểu 3.500 điểm trong một giai đoạn của Dòng Nước Tái Sinh: Dòng Chảy Uất Hận tại Whimpering Wastes sau khi phiên bản 3.2 ra mắt.
+Đạt ít nhất 24 Huy hiệu trong một giai đoạn của Tháp Nghịch Cảnh và đạt tối thiểu 3.500 điểm trong một giai đoạn của Dòng Nước Tái Sinh: Dòng Chảy Uất Hận tại Vùng Đất Than Thở sau khi phiên bản 3.2 ra mắt.
 [Chu kỳ &amp; Giai đoạn thử thách]
-Ma trận Tận thế tiến triển qua các Chu kỳ Thử thách. Mỗi Chu kỳ Thử thách kéo dài qua nhiều Giai đoạn Thử thách, được đặt lại khi phiên bản cập nhật. Rewards được trao riêng cho từng Chu kỳ Thử thách và Giai đoạn Thử thách.
-[Rewards Chu kỳ - Chu kỳ Doomsday]
-Chu kỳ Thử thách hiện tại là "Chu kỳ Doomsday". Hoàn thành Nhiệm vụ Chu kỳ và Nhiệm vụ Thử thách để kiếm Dữ liệu Mã hóa và mở khóa phần thưởng độc quyền. Dữ liệu Mã hóa sẽ bị xóa khi Chu kỳ kết thúc.
-- Nhiệm vụ Chu kỳ sẽ được đặt lại khi bắt đầu Giai đoạn Thử thách mới. Trong Chu kỳ Doomsday, ngươi có thể kiếm tối đa 420 điểm Dữ liệu Mã hóa từ Nhiệm vụ Cycle.
-- Nhiệm vụ Thử thách cập nhật theo từng Giai đoạn Thử thách và kéo dài trong suốt Chu kỳ Thử thách. Trong Chu kỳ Doomsday, mỗi Nhiệm vụ Thử thách có thể mang lại 20 điểm Dữ liệu Mã hóa, tổng cộng tối đa 180 điểm.
+Ma trận Tận thế tiến triển qua các Chu kỳ Thử thách. Mỗi Chu kỳ Thử thách kéo dài qua nhiều Giai đoạn Thử thách, được đặt lại khi phiên bản cập nhật. Phần thưởng được trao riêng cho từng Chu kỳ Thử thách và Giai đoạn Thử thách.
+[Phần thưởng Chu kỳ - Chu kỳ Ngày Tận Thế]
+Chu kỳ Thử thách hiện tại là "Chu kỳ Ngày Tận Thế". Hoàn thành Nhiệm vụ Chu kỳ và Nhiệm vụ Thử thách để kiếm Dữ liệu Mã hóa và mở khóa phần thưởng độc quyền. Dữ liệu Mã hóa sẽ bị xóa khi Chu kỳ kết thúc.
+- Nhiệm vụ Chu kỳ sẽ được đặt lại khi bắt đầu Giai đoạn Thử thách mới. Trong Chu kỳ Ngày Tận Thế, ngươi có thể kiếm tối đa 420 điểm Dữ liệu Mã hóa từ Nhiệm vụ Chu kỳ.
+- Nhiệm vụ Thử thách cập nhật theo từng Giai đoạn Thử thách và kéo dài trong suốt Chu kỳ Thử thách. Trong Chu kỳ Ngày Tận Thế, mỗi Nhiệm vụ Thử thách có thể mang lại 20 điểm Dữ liệu Mã hóa, tổng cộng tối đa 180 điểm.
 [Ma trận]
 Ma trận Tận thế bao gồm hai Khu vực: Hiệp ước Ổn định và Mở rộng Điểm Kỳ dị. Kiếm đủ điểm yêu cầu trong Hiệp ước Ổn định để mở khóa Mở rộng Điểm Kỳ dị.
 [Hiệp ước Ổn định]
@@ -11195,17 +11195,17 @@
 [Mở rộng Điểm Kỳ dị]
 Không giới hạn số đội ngươi có thể triển khai. Đánh bại tất cả kẻ địch trong một lượt sẽ mở ra lượt tiếp theo, với kẻ địch ngày càng mạnh hơn.
 [Mạch Năng lượng]
-Trong Ma trận Tận thế, mỗi đội phải triển khai ba Resonators và chọn một Mạch Năng lượng trước khi bắt đầu thử thách.
-[Resonators Demo]
-Resonators Demo chỉ khả dụng nếu ngươi sở hữu Resonators tương ứng. Mỗi Resonators Demo được đặt ở cấp 90, trang bị vũ khí cấp 90 và bộ Echoes phù hợp với Echoes cấp 25. Họ kế thừa Chuỗi Resonance từ Resonators của ngươi.
-[Resonators Enhancement]
-Trong Ma trận Tận thế, một số Resonators sẽ nhận được tăng cường kỹ năng đặc biệt.
+Trong Ma trận Tận thế, mỗi đội phải triển khai ba Resonator và chọn một Mạch Năng lượng trước khi bắt đầu thử thách.
+[Resonator Demo]
+Resonator Demo chỉ khả dụng nếu ngươi sở hữu Resonator tương ứng. Mỗi Resonator Demo được đặt ở cấp 90, trang bị vũ khí cấp 90 và bộ Echo phù hợp với Echo cấp 25. Họ kế thừa Resonance Chain từ Resonator của ngươi.
+[Tăng cường Resonator]
+Trong Ma trận Tận thế, một số Resonator sẽ nhận được tăng cường kỹ năng đặc biệt.
 [Nhiễm Khuẩn]
 Trong Mở rộng Điểm Kỳ dị, HP của kẻ địch sẽ tăng theo từng lượt, và hiệu ứng kẻ địch mạnh hơn sẽ được mở khóa khi lượt tiến triển.
 [Năng lượng]
-Mỗi lần một Resonators tham gia thử thách, 1 điểm Năng lượng sẽ bị tiêu hao. Resonators với 0 Năng lượng không thể được triển khai. Năng lượng được tính riêng cho Hiệp ước Ổn định và Mở rộng Điểm Kỳ dị.
-[Chiếm dụng Weapon &amp; Echoes]
-Các Resonators khác nhau không thể sử dụng cùng một vũ khí và Echoes trong sự kiện này. Nếu một Resonators trong đội đã trang bị vũ khí hoặc Echoes mà Resonators khác đã sử dụng trong thử thách trước đó, ngươi không thể bắt đầu thử thách với đội này.</t>
+Mỗi lần một Resonator tham gia thử thách, 1 điểm Năng lượng sẽ bị tiêu hao. Resonator với 0 Năng lượng không thể được triển khai. Năng lượng được tính riêng cho Hiệp ước Ổn định và Mở rộng Điểm Kỳ dị.
+[Chiếm dụng Vũ khí &amp; Echo]
+Các Resonator khác nhau không thể sử dụng cùng một vũ khí và Echo trong sự kiện này. Nếu một Resonator trong đội đã trang bị vũ khí hoặc Echo mà Resonator khác đã sử dụng trong thử thách trước đó, ngươi không thể bắt đầu thử thách với đội này.</t>
         </is>
       </c>
     </row>
@@ -11278,10 +11278,10 @@
         <is>
           <t>[Điều Kiện Tham Gia]
 Đạt Cấp Liên Minh 14 và mở khóa xe máy thám hiểm trong Nhiệm Vụ Chính "Ngọn Lửa Dưới Băng Giá".
-[Event Rules]
+[Quy Tắc Sự Kiện]
 1. Trong kỳ thi, hãy khám phá, đánh bại kẻ địch mạnh và sửa chữa Mechascout trên khắp Lahai-Roi để nhận nhiều phần thưởng giá trị, bao gồm cả Astrites.
-2. Nâng cấp GPA Level bằng cách đánh bại kẻ địch hoặc sửa chữa Mechascout. Mỗi 25 cấp, bạn có thể kích hoạt một hiệu ứng tăng cường.
-3. Bạn có thể tăng GPA Level Tạm Thời ngay trong trận chiến. Hãy tận dụng các kỹ năng sẵn có để nâng cao hiệu quả chiến đấu.
+2. Nâng cấp Cấp GPA bằng cách đánh bại kẻ địch hoặc sửa chữa Mechascout. Mỗi 25 cấp, bạn có thể kích hoạt một hiệu ứng tăng cường.
+3. Bạn có thể tăng Cấp GPA Tạm Thời ngay trong trận chiến. Hãy tận dụng các kỹ năng sẵn có để nâng cao hiệu quả chiến đấu.
 ※ Đây là sự kiện thời hạn, sẽ kết thúc khi Phiên Bản 3.2 kết thúc.</t>
         </is>
       </c>
@@ -11355,7 +11355,7 @@
 Lần đầu tiêu diệt các kẻ địch Grand và Common Knights sẽ nhận được điểm kinh nghiệm Cấp Độ GPA.
 ["Cấp Độ GPA Tạm Thời"]
 Mở rương và tiêu diệt kẻ địch rải rác trong kỳ thi sẽ nhận được Cấp Độ GPA Tạm Thời, có hiệu lực trong suốt kỳ thi hiện tại.
-Thực hiện các động tác như Phản Công và Dodge Phản Đòn sẽ nhận được Cấp Độ GPA Tạm Thời, nhưng sẽ giảm dần theo thời gian khi không chiến đấu.</t>
+Thực hiện các động tác như Phản Công và Né Tránh Phản Đòn sẽ nhận được Cấp Độ GPA Tạm Thời, nhưng sẽ giảm dần theo thời gian khi không chiến đấu.</t>
         </is>
       </c>
     </row>
@@ -11434,15 +11434,15 @@
         <is>
           <t>Về sự kiện
 Bước vào thế giới Stellar Orbit Beats và điều khiển phi thuyền của bạn vượt qua vũ trụ bao la.
-Nhấn các nút theo nhịp điệu trong cuộc so tài âm nhạc với Resonators khác.
+Nhấn các nút theo nhịp điệu trong cuộc so tài âm nhạc với các Resonator khác.
 Điều kiện tham gia
-Đạt Cấp Liên Minh 14 và kích hoạt Resonance Nexus tại Startorch Academy trong Nhiệm vụ Main "What Burns Beneath Frostlands" để mở khóa (nên hoàn thành nhiệm vụ trước đó của sự kiện này là "Gold Suspended in Shadows" để có trải nghiệm tốt nhất).
+Đạt Cấp Liên Minh 14 và kích hoạt Resonance Nexus tại Học viện Startorch trong Nhiệm vụ Chính "What Burns Beneath Frostlands" để mở khóa (nên hoàn thành nhiệm vụ trước đó của sự kiện này là "Gold Suspended in Shadows" để có trải nghiệm tốt nhất).
 Nội quy
-1. Bạn có thể tham gia sự kiện qua máy Stellar Orbit Beats tại Mind Dive Arcade hoặc trang Event. Điều khiển phi thuyền cùng Resonators khác và nhấn đúng nốt nhạc theo nhịp để hoàn thành bản nhạc. Một giai đoạn hoàn thành khi phi thuyền kết thúc hành trình.
-2. Bay xuyên không gian và nhấn các nút theo nhịp! Đánh trúng nốt nhạc đúng thời điểm để kiếm Points Giai Đoạn. Đạt mục tiêu của từng giai đoạn để mở khóa phần thưởng.
-3. Dựa trên điểm số cuối cùng, bạn sẽ nhận Ranking Giai Đoạn là SSS, SS, S, A hoặc B. Giai đoạn sẽ không được ghi nhận nếu bạn thoát giữa chừng.
+1. Bạn có thể tham gia sự kiện qua máy Stellar Orbit Beats tại Mind Dive Arcade hoặc trang Sự kiện. Điều khiển phi thuyền cùng các Resonator khác và nhấn đúng nốt nhạc theo nhịp để hoàn thành bản nhạc. Một giai đoạn hoàn thành khi phi thuyền kết thúc hành trình.
+2. Bay xuyên không gian và nhấn các nút theo nhịp! Đánh trúng nốt nhạc đúng thời điểm để kiếm Điểm Giai Đoạn. Đạt mục tiêu của từng giai đoạn để mở khóa phần thưởng.
+3. Dựa trên điểm số cuối cùng, bạn sẽ nhận Xếp hạng Giai Đoạn là SSS, SS, S, A hoặc B. Giai đoạn sẽ không được ghi nhận nếu bạn thoát giữa chừng.
 4. Mỗi bản nhạc có 3 độ khó: Dễ, Thường và Khó. Dễ và Thường được mở khóa mặc định. Khó sẽ mở khóa sau khi hoàn thành mục tiêu ở độ khó Thường.
-5. Bạn có thể kết hợp với Resonators Đồng Hành đã mở khóa để cùng nhau thách thức một giai đoạn. Mỗi Resonators Đồng Hành đều có kỹ năng riêng mang lại hiệu ứng tăng cường độc đáo.
+5. Bạn có thể kết hợp với các Resonator Đồng Hành đã mở khóa để cùng nhau thách thức một giai đoạn. Mỗi Resonator Đồng Hành đều có kỹ năng riêng mang lại hiệu ứng tăng cường độc đáo.
 6. Độ khó Khó của mỗi bản nhạc có bảng xếp hạng Bạn bè. Bạn đã làm chủ được nhịp điệu chưa? Hãy tranh tài với bạn bè để giành vị trí cao nhất!
 7. Các phần thưởng chưa nhận sẽ tự động gửi vào hộp thư trong game nếu bạn đăng nhập trong vòng 30 ngày sau khi sự kiện kết thúc.</t>
         </is>
@@ -11600,13 +11600,13 @@
 [Điều Kiện Tham Gia]
 Đạt Cấp Liên Minh 10, với tài khoản được tạo trong chu kỳ thu thập dữ liệu sự kiện.
 *Dữ liệu sự kiện được thu thập từ 10:00 23/05/2024 đến 23:59:59 31/03/2026 (UTC+8).
-[Details]
+[Chi Tiết]
 1. Trong sự kiện, bạn có thể xem báo cáo Chương Trình Ký Ức của mình.
 2. Hoàn thành nhiệm vụ sự kiện để nhận các phần thưởng trong game như Astrite, Shell Credits và Advanced Sealed Tube.
 [Lưu Ý]
-1. Hãy đăng nhập vào game và nhận thưởng trong thời gian diễn ra sự kiện. Unclaimed reward sẽ không còn hiệu lực sau khi sự kiện kết thúc.
+1. Hãy đăng nhập vào game và nhận thưởng trong thời gian diễn ra sự kiện. Phần thưởng chưa nhận sẽ không còn hiệu lực sau khi sự kiện kết thúc.
 2. Nội dung của sự kiện web này không liên quan đến cốt truyện và thiết lập nhân vật trong game.
-3. Một số dữ liệu Resonator sẽ không được tính vào thống kê của Rover: Spectro, Rover: Havoc và Rover: Aero. Exploration Progress hiển thị trong sự kiện là dữ liệu tổng hợp từ các khu vực khác nhau trong game.
+3. Một số dữ liệu Resonator sẽ không được tính vào thống kê của Rover: Spectro, Rover: Havoc và Rover: Aero. Tiến Độ Thám Hiểm hiển thị trong sự kiện là dữ liệu tổng hợp từ các khu vực khác nhau trong game.
 4. Số liệu tài khoản hiển thị trong sự kiện chỉ mang tính tham khảo và có thể thay đổi. Vui lòng xem dữ liệu trong game để có thông tin chính xác.</t>
         </is>
       </c>
@@ -11672,7 +11672,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Ở Freefly Mode, điểm số của ngươi sẽ tự động tăng lên</t>
+          <t>Ở Chế Độ Bay Tự Do, điểm số của ngươi sẽ tự động tăng lên</t>
         </is>
       </c>
     </row>
@@ -11737,7 +11737,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Ở Freefly Mode, điểm số của ngươi sẽ tự động tăng lên</t>
+          <t>Ở Chế Độ Bay Tự Do, điểm số của ngươi sẽ tự động tăng lên</t>
         </is>
       </c>
     </row>
@@ -11802,7 +11802,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Ở Freefly Mode, điểm số của ngươi sẽ tự động tăng lên</t>
+          <t>Ở Chế Độ Bay Tự Do, điểm số của ngươi sẽ tự động tăng lên</t>
         </is>
       </c>
     </row>
@@ -11867,7 +11867,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Resonator Skill Giả Stage 2</t>
+          <t>Kỹ Năng Resonator Giai Đoạn 2</t>
         </is>
       </c>
     </row>
@@ -11932,7 +11932,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Resonator Skill Giả Stage 3</t>
+          <t>Kỹ Năng Resonator Giai Đoạn 3</t>
         </is>
       </c>
     </row>
@@ -11997,7 +11997,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Resonator Skill Giả Stage 4</t>
+          <t>Kỹ Năng Resonator Giai Đoạn 4</t>
         </is>
       </c>
     </row>
@@ -12062,7 +12062,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Resonator Skill Giả Stage 5</t>
+          <t>Kỹ Năng Resonator Giai Đoạn 5</t>
         </is>
       </c>
     </row>
@@ -12127,7 +12127,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Resonator Skill Giả Stage 6</t>
+          <t>Kỹ Năng Resonator Giai Đoạn 6</t>
         </is>
       </c>
     </row>
@@ -12192,7 +12192,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Resonator Skill Giả Stage 7</t>
+          <t>Kỹ Năng Resonator Giai Đoạn 7</t>
         </is>
       </c>
     </row>
@@ -12322,7 +12322,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>Khi những chiếc bình cá "Nứt! Sét!" xuất hiện, hãy tránh Dodge ngay, nếu không chúng có thể làm giảm Speed của cậu tạm thời.</t>
+          <t>Khi những chiếc bình cá "Nứt! Sét!" xuất hiện, hãy tránh né ngay, nếu không chúng có thể làm giảm Tốc Độ của cậu tạm thời.</t>
         </is>
       </c>
     </row>
@@ -12387,7 +12387,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>Luuk Herssen: Tạm thời giảm Speed nhưng tăng mạnh việc tạo Điểm Ẩm Thực.</t>
+          <t>Luuk Herssen: Tạm thời giảm Tốc Độ nhưng tăng mạnh việc tạo Điểm Ẩm Thực.</t>
         </is>
       </c>
     </row>
@@ -12452,7 +12452,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>Tăng nhẹ Speed và Tạo Điểm Ẩm Thực trong một khoảng thời gian vừa phải.</t>
+          <t>Tăng nhẹ Tốc Độ và Tạo Điểm Ẩm Thực trong một khoảng thời gian vừa phải.</t>
         </is>
       </c>
     </row>
@@ -12582,7 +12582,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>Denia: Increase toàn bộ chỉ số và kéo dài thời gian đếm ngược thử thách.</t>
+          <t>Denia: Tăng toàn bộ chỉ số và kéo dài thời gian đếm ngược thử thách.</t>
         </is>
       </c>
     </row>
@@ -12647,7 +12647,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Lucilla: Tăng mạnh toàn bộ chỉ số.</t>
+          <t>Lucilla: Tăng tất cả chỉ số lên mức tối đa.</t>
         </is>
       </c>
     </row>
@@ -13039,7 +13039,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>Sửa lại các Hiệp Sĩ Common rải rác trên chiến trường có thể làm suy yếu Giám Khảo, giảm Shield bảo vệ kẻ địch xung quanh Hiệp Sĩ Cấp Cao.</t>
+          <t>Sửa lại các Hiệp Sĩ Thường rải rác trên chiến trường có thể làm suy yếu Giám Khảo, giảm Khiên bảo vệ kẻ địch xung quanh Hiệp Sĩ Cấp Cao.</t>
         </is>
       </c>
     </row>
@@ -13179,9 +13179,9 @@
       <c r="M183" t="inlineStr">
         <is>
           <t>[Giới Thiệu]
-Để khuyến khích các Tiên Phong chia sẻ thêm về những chuyến thám hiểm vùng Roya Băng Giá, Lollo Logistics đã hợp tác với Pioneer Association hân hạnh giới thiệu chiến dịch: Vượt Sóng! Tham gia và tải Nhật Ký Phiêu Lưu của bạn để nhận nhiều phần thưởng hấp dẫn!
+Để khuyến khích các Tiên Phong chia sẻ thêm về những chuyến thám hiểm vùng Roya Băng Giá, Lollo Logistics đã hợp tác với Hiệp Hội Tiên Phong hân hạnh giới thiệu chiến dịch: Vượt Sóng! Tham gia và tải Nhật Ký Phiêu Lưu của bạn để nhận nhiều phần thưởng hấp dẫn!
 [Điều Kiện Tham Gia]
-Đạt Cấp Liên Minh 14 và kích hoạt Nexus Resonance tại Học Viện Startorch trong Nhiệm Vụ Chính "Ngọn Lửa Dưới Băng Giá" để mở khóa.
+Đạt Cấp Liên Minh 14 và kích hoạt Nexus Cộng Hưởng tại Học Viện Startorch trong Nhiệm Vụ Chính "Ngọn Lửa Dưới Băng Giá" để mở khóa.
 [Thể Lệ Sự Kiện]
 - Trong thời gian diễn ra sự kiện, hoàn thành các nhiệm vụ sự kiện mỗi ngày một lần để nhận được một số lượng Nhật Ký Phiêu Lưu nhất định.
 - Mỗi Nhật Ký Phiêu Lưu có thể đổi lấy một Gói Phiêu Lưu. Gói Phiêu Lưu chứa cơ chế đặc biệt, khi kích hoạt sẽ mở khóa một lượng lớn phần thưởng.
@@ -13333,10 +13333,10 @@
       <c r="M185" t="inlineStr">
         <is>
           <t>["Giới Thiệu"]
-Event Cộng tác "Resident Evil Anniversary 30 năm", "Angry Birds" và "Kaiju Không. 8". Hoàn thành nhiệm vụ trong sự kiện để nhận được Mẫu Xe Cộng tác tương ứng cùng nhiều nguyên liệu nâng cấp.
+Sự kiện Cộng tác "Resident Evil Kỷ niệm 30 năm", "Angry Birds" và "Kaiju No. 8". Hoàn thành nhiệm vụ trong sự kiện để nhận được Mẫu Xe Cộng tác tương ứng cùng nhiều nguyên liệu nâng cấp.
 [Điều kiện tham gia]
-Đạt Cấp Liên Minh 14 và kích hoạt Nexus Resonance Startorch Academy trong Nhiệm vụ Main "Điều Gì Nung Nấu Dưới Băng Giá" để mở khóa.
-Nếu bạn có phần thưởng chưa nhận khi sự kiện kết thúc, bạn có thể đăng nhập trong vòng 30 ngày sau đó để nhận qua Mail trong game.</t>
+Đạt Cấp Liên Minh 14 và kích hoạt Nexus Cộng Hưởng Học viện Startorch trong Nhiệm vụ Chính "Điều Gì Nung Nấu Dưới Băng Giá" để mở khóa.
+Nếu bạn có phần thưởng chưa nhận khi sự kiện kết thúc, bạn có thể đăng nhập trong vòng 30 ngày sau đó để nhận qua Thư trong game.</t>
         </is>
       </c>
     </row>
@@ -13406,10 +13406,10 @@
       <c r="M186" t="inlineStr">
         <is>
           <t>Về sự kiện
-Event hợp tác "PRAGMATA", "Riders Republic" và "HAIKYU!!" (anime). Hoàn thành nhiệm vụ trong sự kiện để nhận được Livery hợp tác tương ứng và nhiều loại vật liệu nâng cấp.
+Sự kiện hợp tác "PRAGMATA", "Riders Republic" và "HAIKYU!!" (anime). Hoàn thành nhiệm vụ trong sự kiện để nhận được Livery hợp tác tương ứng và nhiều loại vật liệu nâng cấp.
 Điều kiện tham gia
-Đạt Cấp Liên Minh 14 và kích hoạt Nexus Resonance Startorch Academy trong Nhiệm Vụ Chính "Ngọn Lửa Dưới Băng Giá" để mở khóa.
-Nếu sự kiện kết thúc mà bạn vẫn còn phần thưởng chưa nhận, hãy đăng nhập trong vòng 30 ngày sau đó để nhận qua Mail.</t>
+Đạt Cấp Liên Minh 14 và kích hoạt Nexus Cộng Hưởng Học viện Startorch trong Nhiệm Vụ Chính "Ngọn Lửa Dưới Băng Giá" để mở khóa.
+Nếu sự kiện kết thúc mà bạn vẫn còn phần thưởng chưa nhận, hãy đăng nhập trong vòng 30 ngày sau đó để nhận qua Thư.</t>
         </is>
       </c>
     </row>
@@ -13488,13 +13488,13 @@
       <c r="M187" t="inlineStr">
         <is>
           <t>Sự kiện trực tuyến "Trở Về Solaris" đã bắt đầu! Tham gia để nhận tới 530 Astrites.
-Invite những người bạn cũ trở lại và cùng hoàn thành nhiệm vụ để nhận Astrites, Shell Credits cùng nhiều phần thưởng khác! Những Rover quay lại liên kết tài khoản sẽ được nhận thêm quà tặng đặc biệt!
+Mời những người bạn cũ trở lại và cùng hoàn thành nhiệm vụ để nhận Astrites, Shell Credits cùng nhiều phần thưởng khác! Những Rover quay lại liên kết tài khoản sẽ được nhận thêm quà tặng đặc biệt!
 [Điều kiện tham gia]
 Cấp Liên Minh ≥ 8.
 [Quy định]
-1. Share mã mời của bạn với tối đa 3 người chơi quay lại trong máy chủ, hoàn thành nhiệm vụ trong game để nhận Startorch Sigils và đổi lấy tối đa Astrite x480 cùng Shell Credit x300.000.
+1. Chia sẻ mã mời của bạn với tối đa 3 người chơi quay lại trong máy chủ, hoàn thành nhiệm vụ trong game để nhận Startorch Sigils và đổi lấy tối đa Astrite x480 cùng Shell Credit x300.000.
 2. Người chơi quay lại có thể liên kết tài khoản với người chơi đã mời bằng mã mời tương ứng. Việc liên kết chỉ thực hiện được một lần và không thể thay đổi sau đó. Sau khi liên kết, người chơi quay lại đủ điều kiện nhận phần thưởng gồm Astrite x50, Advanced Enclosure TankⅡ x5 và Shell Credit x50.000.
-※ Mail phần thưởng trong game có thể nhận trong vòng 30 ngày kể từ khi được phát hành.
+※ Thư phần thưởng trong game có thể nhận trong vòng 30 ngày kể từ khi được phát hành.
 ※ Sau khi hoàn thành nhiệm vụ sự kiện, có thể có chút trễ trước khi nhận được phần thưởng. Nếu gặp trường hợp này, hãy đợi ít nhất 2 phút trước khi làm mới trang hoặc khởi động lại game.
 ※ Một người chơi quay lại không thể vừa là người mời vừa là người được mời của một người chơi quay lại khác.
 [Điều kiện người chơi quay lại]
@@ -13581,17 +13581,17 @@
           <t>Về sự kiện
 Cánh cổng Somnoire đột nhiên xuất hiện ở Lahai-Roi, kéo theo một giấc mơ hỗn độn, rối rắm. Kỳ lạ thay, ngay trong hỗn loạn ấy, ngươi còn thấy cả Namipon...
 Điều kiện tham gia
-Đạt Cấp Liên Minh 14 và mở Khối Liên Kết Resonance của Học Viện Startorch trong Nhiệm Vụ Chính "Điều Gì Nung Nấu Dưới Băng Giá".
+Đạt Cấp Liên Minh 14 và mở Khối Liên Kết Cộng Hưởng của Học Viện Startorch trong Nhiệm Vụ Chính "Điều Gì Nung Nấu Dưới Băng Giá".
 Quy tắc sự kiện
 1. Sau khi sự kiện bắt đầu, nói chuyện với Namipon tại Học Viện Startorch để nhận nhiệm vụ và bắt đầu thử thách.
-2. Thử thách gồm ba giai đoạn "Surface of Illusions" và một giai đoạn "Độ Sâu Ảo Ảnh". Trước khi vào, ngươi có thể điều chỉnh tỷ lệ phần thưởng qua Tuning Tần Số. Tỷ lệ càng cao, phần thưởng càng lớn. Hoàn thành các giai đoạn sẽ nhận được Mẫu Ảo và Memory Points.
+2. Thử thách gồm ba giai đoạn "Bề Mặt Ảo Ảnh" và một giai đoạn "Độ Sâu Ảo Ảnh". Trước khi vào, ngươi có thể điều chỉnh tỷ lệ phần thưởng qua Điều Chỉnh Tần Số. Tỷ lệ càng cao, phần thưởng càng lớn. Hoàn thành các giai đoạn sẽ nhận được Mẫu Ảo và Điểm Ký Ức.
 3. Dùng Mẫu Ảo để đổi lấy Astrites và các phần thưởng khác.
-4. Tiêu Memory Points trong Cuộc Cách Mạng Tư Tưởng để nâng cấp khả năng, giúp các thử thách sau dễ dàng hơn.
-5. Thu thập các hiệu ứng tăng cường mạnh mẽ như Echoes Ảo, Ẩn Dụ và Resonators Enhancements khi khám phá Somnoire. Xây dựng tổ hợp tối ưu để chinh phục những tầng sâu nhất của giấc mơ.
-※ Ngươi có thể khám phá Thế Giới Ảo Ảnh với Resonators sau:
-※ Resonators có sẵn: Luuk Herssen, Aemeath, Mornye, Lynae, Chisa, Qiuyuan, Galbrena, Iuno, Augusta, Phrolova, Lupa, Cartethyia, Ciaccona, Zani, Cantarella, Brant, Phoebe, Roccia, Carlotta, Camellya, Shorekeeper, Xiangli Yao, Zhezhi, Changli, Jinhsi, Yinlin, Jiyan, Calcharo, Lingyang, Jianxin, Verina, Encore, Rover: Aero, Rover: Havoc, Rover: Spectro, Buling, Lumi, Youhu, Yuanwu, Danjin, Sanhua, Mortefi, Taoqi, Aalto, Baizhi, Yangyang, và Chixia.
-※ Cấp độ, Chuỗi Resonance và vũ khí của Resonators được chọn sẽ được giữ nguyên trong Thế Giới Ảo Ảnh, nhưng chỉ số Echoes và kỹ năng Echoes sẽ không.
-※ Trang phục của Resonators được chọn sẽ không hiển thị trong một số màn hình khi khám phá Thế Giới Ảo Ảnh.</t>
+4. Tiêu Điểm Ký Ức trong Cuộc Cách Mạng Tư Tưởng để nâng cấp khả năng, giúp các thử thách sau dễ dàng hơn.
+5. Thu thập các hiệu ứng tăng cường mạnh mẽ như Echo Ảo, Ẩn Dụ và Tăng Cường Resonator khi khám phá Somnoire. Xây dựng tổ hợp tối ưu để chinh phục những tầng sâu nhất của giấc mơ.
+※ Ngươi có thể khám phá Thế Giới Ảo Ảnh với các Resonator sau:
+※ Resonator có sẵn: Luuk Herssen, Aemeath, Mornye, Lynae, Chisa, Qiuyuan, Galbrena, Iuno, Augusta, Phrolova, Lupa, Cartethyia, Ciaccona, Zani, Cantarella, Brant, Phoebe, Roccia, Carlotta, Camellya, Shorekeeper, Xiangli Yao, Zhezhi, Changli, Jinhsi, Yinlin, Jiyan, Calcharo, Lingyang, Jianxin, Verina, Encore, Rover: Aero, Rover: Havoc, Rover: Spectro, Buling, Lumi, Youhu, Yuanwu, Danjin, Sanhua, Mortefi, Taoqi, Aalto, Baizhi, Yangyang, và Chixia.
+※ Cấp độ, Resonance Chain và vũ khí của Resonator được chọn sẽ được giữ nguyên trong Thế Giới Ảo Ảnh, nhưng chỉ số Echo và kỹ năng Echo sẽ không.
+※ Trang phục của Resonator được chọn sẽ không hiển thị trong một số màn hình khi khám phá Thế Giới Ảo Ảnh.</t>
         </is>
       </c>
     </row>
@@ -13853,7 +13853,7 @@
       <c r="M192" t="inlineStr">
         <is>
           <t>Các yếu tố cản trở sự phát triển của Voidbane Eldertrees đã được loại bỏ, nhưng sau thời gian dài tiếp xúc với Voidmatter, thực vật đã rơi vào trạng thái ngủ đông thích nghi...
-&lt;color=#ffd12f&gt;Deliver the corresponding area's "Restoratives"&lt;/color&gt; để khôi phục sự phát triển của Voidbane Eldertrees.</t>
+&lt;color=#ffd12f&gt;Giao "Dược phẩm phục hồi" tương ứng của khu vực&lt;/color&gt; để khôi phục sự phát triển của Voidbane Eldertrees.</t>
         </is>
       </c>
     </row>
@@ -14113,7 +14113,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>Prism Formation có kỹ năng đặc biệt. Khi kích hoạt, nó liên tục bắn tia laser và tạo khiên. Phá vỡ khiên để ngắt kỹ năng.</t>
+          <t>Hình Thành Lăng Kính có kỹ năng đặc biệt. Khi kích hoạt, nó liên tục bắn tia laser và tạo khiên. Phá vỡ khiên để ngắt kỹ năng.</t>
         </is>
       </c>
     </row>
@@ -14178,7 +14178,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>Dreamless sở hữu một kỹ năng cực mạnh. Khi kích hoạt, nó bắt đầu tích năng và nhận một Lớp Shield. Trong quá trình tích năng, Dreamless liên tục tung ra những đòn tấn công như bão tố. Hãy phá vỡ Lớp Shield để ngăn chặn quá trình tích năng này.</t>
+          <t>Vô Mộng sở hữu một kỹ năng cực mạnh. Khi kích hoạt, nó bắt đầu tích năng và nhận một Lớp Khiên. Trong quá trình tích năng, Vô Mộng liên tục tung ra những đòn tấn công như bão tố. Hãy phá vỡ Lớp Khiên để ngăn chặn quá trình tích năng này.</t>
         </is>
       </c>
     </row>
@@ -14243,7 +14243,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Hecate sở hữu kỹ năng mạnh mẽ. Khi kích hoạt, cô bắt đầu nạp năng lượng và nhận một Lớp Shield. Khi nạp xong, cô lóe sáng và triệu hồi Crescent Servant để tung đòn tấn công diện rộng. Hãy phá vỡ Lớp Shield để ngăn chặn quá trình nạp năng lượng.</t>
+          <t>Hecate sở hữu kỹ năng mạnh mẽ. Khi kích hoạt, cô bắt đầu nạp năng lượng và nhận một Lớp Khiên. Khi nạp xong, cô lóe sáng và triệu hồi Crescent Servant để tung đòn tấn công diện rộng. Hãy phá vỡ Lớp Khiên để ngăn chặn quá trình nạp năng lượng.</t>
         </is>
       </c>
     </row>
@@ -14308,7 +14308,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Sư Tử Glory sở hữu kỹ năng mạnh mẽ. Khi kích hoạt, cô ấy bắt đầu nạp năng lượng và nhận một Lớp Shield. Khi nạp xong, cô ấy triệu hồi một khẩu nỏ lớn để bắn. Hãy phá vỡ Lớp Shield để ngăn chặn quá trình nạp.</t>
+          <t>Sư Tử Vinh Quang sở hữu kỹ năng mạnh mẽ. Khi kích hoạt, cô ấy bắt đầu nạp năng lượng và nhận một Lớp Khiên. Khi nạp xong, cô ấy triệu hồi một khẩu nỏ lớn để bắn. Hãy phá vỡ Lớp Khiên để ngăn chặn quá trình nạp.</t>
         </is>
       </c>
     </row>
@@ -14373,7 +14373,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Elegy of the Fallen sở hữu một kỹ năng mạnh mẽ. Khi kích hoạt, nó bắt đầu tích năng và tạo khiên bảo vệ. Trong quá trình tích năng, Elegy of the Fallen sẽ tung ra một loạt đòn tấn công đa giai đoạn. Hãy phá vỡ khiên để ngăn chặn quá trình tích năng này.</t>
+          <t>Khúc Bi Ca Sa Ngã sở hữu một kỹ năng mạnh mẽ. Khi kích hoạt, nó bắt đầu tích năng và tạo khiên bảo vệ. Trong quá trình tích năng, Khúc Bi Ca Sa Ngã sẽ tung ra một loạt đòn tấn công đa giai đoạn. Hãy phá vỡ khiên để ngăn chặn quá trình tích năng này.</t>
         </is>
       </c>
     </row>
@@ -14438,7 +14438,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Hyvatia sở hữu một kỹ năng mạnh mẽ. Khi kích hoạt, nó bắn tia laser liên tục và chịu nhiều sát thương hơn trong thời gian đó.</t>
+          <t>Hyvatia sở hữu một kỹ năng mạnh mẽ. Khi kích hoạt, nó bắn tia laser liên tục và chịu nhiều DMG hơn trong thời gian đó.</t>
         </is>
       </c>
     </row>
@@ -14503,7 +14503,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Reactor Husk sở hữu kỹ năng mạnh mẽ. Khi kích hoạt, nó bắt đầu tích năng và tạo khiên bảo vệ. Khi tích năng hoàn tất, khói sẽ lan tỏa khắp chiến trường, và những quả cầu lửa sẽ trút xuống như mưa. Hãy phá vỡ khiên để ngăn chặn quá trình tích năng.</t>
+          <t>Vỏ Lò Phản Ứng sở hữu kỹ năng mạnh mẽ. Khi kích hoạt, nó bắt đầu tích năng và tạo khiên bảo vệ. Khi tích năng hoàn tất, khói sẽ lan tỏa khắp chiến trường, và những quả cầu lửa sẽ trút xuống như mưa. Hãy phá vỡ khiên để ngăn chặn quá trình tích năng.</t>
         </is>
       </c>
     </row>
@@ -14568,7 +14568,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>Kỹ năng của Nameless Explorer cực kỳ mạnh mẽ. Khi kích hoạt, nó bắt đầu tích năng và tạo khiên bảo vệ. Khi tích năng hoàn tất, Nameless Explorer sẽ triệu hồi một thiên thạch khổng lồ tấn công. Hãy phá vỡ khiên để ngăn chặn quá trình tích năng.</t>
+          <t>Kỹ năng của Nhà Thám Hiểm Vô Danh cực kỳ mạnh mẽ. Khi kích hoạt, nó bắt đầu tích năng và tạo khiên bảo vệ. Khi tích năng hoàn tất, Nhà Thám Hiểm Vô Danh sẽ triệu hồi một thiên thạch khổng lồ tấn công. Hãy phá vỡ khiên để ngăn chặn quá trình tích năng.</t>
         </is>
       </c>
     </row>
@@ -14829,7 +14829,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Năng lượng Động cơ Phản ứng trong Stalaglow Cavern đang bị Vật chất Hư không xói mòn. Không thể hoàn tất thanh tẩy cho đến khi lũ tạo vật Threnodian bị đẩy lui.
+          <t>Năng lượng Động cơ Phản ứng trong Hang Stalaglow đang bị Vật chất Hư không xói mòn. Không thể hoàn tất thanh tẩy cho đến khi lũ tạo vật Threnodian bị đẩy lui.
 Dùng Linh kiện Lumescribe để xua đuổi chúng. Nếu mục tiêu được chiếu sáng là bản sao, bản sao sẽ bị tiêu diệt. Nếu là bản thể thật, bản thể sẽ bị bắn hạ.</t>
         </is>
       </c>
@@ -14961,8 +14961,8 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Khi Dodge các khối, cẩn thận đừng để thanh chồng vượt quá vùng sẵn sàng. Nếu không, trò chơi sẽ thất bại.
-Khi các Voidmatter Blocks lấp đầy một hàng, hàng đó sẽ bị xóa, làm giảm chiều cao của thanh chồng.</t>
+          <t>Khi né các khối, cẩn thận đừng để thanh chồng vượt quá vùng sẵn sàng. Nếu không, trò chơi sẽ thất bại.
+Khi các Khối Vật Chất Hư Không lấp đầy một hàng, hàng đó sẽ bị xóa, làm giảm chiều cao của thanh chồng.</t>
         </is>
       </c>
     </row>
@@ -15028,8 +15028,8 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Khi Dodge các khối, cẩn thận đừng để thanh chồng vượt quá vùng sẵn sàng. Nếu không, trò chơi sẽ thất bại.
-Khi các Voidmatter Blocks lấp đầy một hàng, hàng đó sẽ bị xóa và bạn nhận được điểm thưởng lớn. Càng xóa nhiều hàng cùng lúc, điểm thưởng càng cao.</t>
+          <t>Khi né các khối, cẩn thận đừng để thanh chồng vượt quá vùng sẵn sàng. Nếu không, trò chơi sẽ thất bại.
+Khi các Khối Vật Chất Hư Không lấp đầy một hàng, hàng đó sẽ bị xóa và bạn nhận được điểm thưởng lớn. Càng xóa nhiều hàng cùng lúc, điểm thưởng càng cao.</t>
         </is>
       </c>
     </row>
@@ -15094,7 +15094,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Touch vào Score Ring để tích điểm và hồi năng lượng.</t>
+          <t>Chạm vào Score Ring để tích điểm và hồi năng lượng.</t>
         </is>
       </c>
     </row>
@@ -15160,7 +15160,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Trong các Void Storm Zone tại Dimmr Plains, khi Resonator chịu sát thương từ kẻ địch, họ sẽ nhận 1 lớp Hư Không, làm tăng 10% toàn bộ sát thương nhận vào.
+          <t>Trong các Khu Vực Bão Hư Không tại Đồng Bằng Dimmr, khi Resonator chịu DMG từ kẻ địch, họ sẽ nhận 1 lớp Hư Không, làm tăng 10% toàn bộ DMG nhận vào.
 Sử dụng Kỹ Năng Phá Âm ở đợt kẻ địch thứ hai sẽ phục hồi HP cho Resonator và loại bỏ Hư Không. Khi Resonator tấn công kẻ địch hoặc gây Trạng Thái Tiêu Cực, kẻ địch sẽ mất HP theo thời gian trong một khoảng thời gian nhất định. Hiệu ứng này có thể chồng chất.</t>
         </is>
       </c>
@@ -15293,7 +15293,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>Mỗi lượt đi, &lt;color=#ffd12f&gt;there is a chance&lt;/color&gt; một Cube kích hoạt &lt;color=#ffd12f&gt;Skill&lt;/color&gt; đặc biệt của riêng nó. Skills có những hiệu ứng độc đáo ảnh hưởng đến cách Cube di chuyển. Đường đua cũng chứa các cơ chế có thể cản trở hoặc hỗ trợ chúng.</t>
+          <t>Mỗi lượt đi, &lt;color=#ffd12f&gt;có khả năng&lt;/color&gt; một Khối Lập Phương kích hoạt &lt;color=#ffd12f&gt;Kỹ Năng&lt;/color&gt; đặc biệt của riêng nó. Kỹ Năng có những hiệu ứng độc đáo ảnh hưởng đến cách Khối Lập Phương di chuyển. Đường đua cũng chứa các cơ chế có thể cản trở hoặc hỗ trợ chúng.</t>
         </is>
       </c>
     </row>
@@ -15361,7 +15361,7 @@
       <c r="M215" t="inlineStr">
         <is>
           <t>Trong trận đấu, kết quả tung xúc xắc sẽ quyết định Cube nào di chuyển trước và đi được bao xa.
-&lt;color=#ffd12f&gt;There is a chance&lt;/color&gt; một Cube kích hoạt &lt;color=#ffd12f&gt;Skill&lt;/color&gt; đặc biệt của riêng nó. Các Skills có hiệu ứng riêng biệt ảnh hưởng đến cách di chuyển của Cube.
+&lt;color=#ffd12f&gt;Có xác suất&lt;/color&gt; một Cube kích hoạt &lt;color=#ffd12f&gt;Kỹ Năng&lt;/color&gt; đặc biệt của riêng nó. Các Kỹ Năng có hiệu ứng riêng biệt ảnh hưởng đến cách di chuyển của Cube.
 Những Cube đến sau sẽ chồng lên những Cube đã đến trước trên bệ đích.</t>
         </is>
       </c>
@@ -15427,7 +15427,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Spectro DMG +30% trong 15 giây sau khi dùng Intro Skill.</t>
+          <t>Sát Thương Spectro +30% trong 15 giây sau khi dùng Kỹ Năng Khởi Động.</t>
         </is>
       </c>
     </row>
@@ -15557,7 +15557,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Kích hoạt Resonance Skill sẽ tăng Glacio DMG {0} trong {1} giây và kích hoạt Resonance Liberation sẽ tăng Sát Thương Resonance Skill thêm {2}, hiệu ứng kéo dài {3} giây. Hiệu ứng này có thể chồng chất tối đa {4} lần.</t>
+          <t>Kích hoạt Resonance Skill sẽ tăng Sát Thương Glacio {0} trong {1} giây và kích hoạt Resonance Liberation sẽ tăng Sát Thương Resonance Skill thêm {2}, hiệu ứng kéo dài {3} giây. Hiệu ứng này có thể chồng chất tối đa {4} lần.</t>
         </is>
       </c>
     </row>
@@ -15622,7 +15622,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Kích hoạt Resonance Skill sẽ tăng Glacio DMG. Kích hoạt Resonance Liberation sẽ tăng Sát Thương Resonance Skill.</t>
+          <t>Kích hoạt Resonance Skill sẽ tăng Sát Thương Glacio. Kích hoạt Resonance Liberation sẽ tăng Sát Thương Resonance Skill.</t>
         </is>
       </c>
     </row>
@@ -15687,7 +15687,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Khi dùng Intro Skill, Spectro DMG tăng lên</t>
+          <t>Sát Thương Spectro +30% trong 15 giây sau khi dùng Kỹ Năng Khởi Động.</t>
         </is>
       </c>
     </row>
@@ -15752,7 +15752,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Spectro DMG + {0}</t>
+          <t>Sát Thương Spectro +{0}</t>
         </is>
       </c>
     </row>
@@ -15817,7 +15817,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Gây Hiệu Ứng Nhiễu Loạn Quang Phổ lên kẻ địch sẽ tăng Crit. Rate thêm {0} trong {1} giây. Tấn công kẻ địch bị {2} lớp Nhiễu Loạn Quang Phổ sẽ cộng thêm {3} Tăng Sát Thương Quang Phổ trong {4} giây.</t>
+          <t>Gây Hiệu Ứng Spectro Frazzle lên kẻ địch sẽ tăng Crit. Rate thêm {0} trong {1} giây. Tấn công kẻ địch bị {2} lớp Spectro Frazzle sẽ cộng thêm {3} Tăng Sát Thương Quang Phổ trong {4} giây.</t>
         </is>
       </c>
     </row>
@@ -15882,7 +15882,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Gây Hiệu Ứng Nhiễu Loạn Quang Phổ lên kẻ địch sẽ tăng Crit. Rate. Tấn công kẻ địch bị 10 lớp Nhiễu Loạn Quang Phổ sẽ tăng Sát Thương Quang Phổ.</t>
+          <t>Gây Hiệu Ứng Spectro Frazzle lên kẻ địch sẽ tăng Crit. Rate. Tấn công kẻ địch bị 10 lớp Spectro Frazzle sẽ tăng Sát Thương Quang Phổ.</t>
         </is>
       </c>
     </row>
@@ -15947,7 +15947,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Havoc DMG + 10%.</t>
+          <t>Sát Thương Havoc +10%.</t>
         </is>
       </c>
     </row>
@@ -16012,7 +16012,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Havoc DMG + {0}</t>
+          <t>Sát Thương Havoc +{0}</t>
         </is>
       </c>
     </row>
@@ -16077,7 +16077,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Khi Outro Skill được kích hoạt, gây thêm {0} Havoc DMG lên kẻ địch xung quanh, được tính là Sát Thương Outro Skill, và trao cho Resonator kế tiếp {1} Havoc DMG Bonus trong {2} giây.</t>
+          <t>Khi Kỹ Năng Outro được kích hoạt, gây thêm {0} Sát Thương Havoc lên kẻ địch xung quanh, được tính là Sát Thương Kỹ Năng Outro, và trao cho Resonator kế tiếp {1} Tăng Sát Thương Havoc trong {2} giây.</t>
         </is>
       </c>
     </row>
@@ -16142,7 +16142,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Kích hoạt Kỹ Năng Kết Thúc gây thêm Havoc DMG và ban cho Resonator nhận sát thương thêm Havoc DMG.</t>
+          <t>Kích hoạt Outro Skill gây thêm Sát Thương Havoc và ban cho Resonator nhận DMG thêm Sát Thương Havoc.</t>
         </is>
       </c>
     </row>
@@ -16207,7 +16207,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Havoc DMG +7,5% sau khi tung đòn Basic Attack hoặc Heavy Attack. Hiệu ứng này có thể chồng chất tối đa 4 lần, mỗi lần kéo dài 15 giây.</t>
+          <t>Sát Thương Havoc +7,5% sau khi tung đòn Basic Attack hoặc Heavy Attack. Hiệu ứng này có thể chồng chất tối đa 4 lần, mỗi lần kéo dài 15 giây.</t>
         </is>
       </c>
     </row>
@@ -16272,7 +16272,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Khi sử dụng Basic Attack hoặc Heavy Attack, Havoc DMG tăng lên.</t>
+          <t>Sát Thương Havoc +7,5% sau khi tung đòn Basic Attack hoặc Heavy Attack. Hiệu ứng này có thể chồng chất tối đa 4 lần, mỗi lần kéo dài 15 giây.</t>
         </is>
       </c>
     </row>
@@ -16337,7 +16337,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Energy Regen + {0}</t>
+          <t>Hồi Năng Lượng + {0}</t>
         </is>
       </c>
     </row>
@@ -16402,7 +16402,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Increase Sát Thương Attack Phối Hợp của Resonator thêm {0}. Khi Attack Phối Hợp gây Bạo Kích, tăng Attack của Resonator đang hoạt động thêm {1} trong {2} giây.</t>
+          <t>Tăng Sát Thương ATK Phối Hợp của Resonator thêm {0}. Khi ATK Phối Hợp gây Bạo Kích, tăng ATK của Resonator đang hoạt động thêm {1} trong {2} giây.</t>
         </is>
       </c>
     </row>
@@ -16467,7 +16467,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Increase Sát Thương Attack Phối Hợp. Các đòn Attack Phối Hợp chí mạng sẽ tăng Attack.</t>
+          <t>Tăng Sát Thương ATK Phối Hợp. Các đòn ATK Phối Hợp chí mạng sẽ tăng ATK.</t>
         </is>
       </c>
     </row>
@@ -16532,7 +16532,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Healing Bonus +10%.</t>
+          <t>Tăng Hiệu Quả Hồi Phục +10%.</t>
         </is>
       </c>
     </row>
@@ -16597,7 +16597,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Energy Regen + {0}</t>
+          <t>Hồi Năng Lượng + {0}</t>
         </is>
       </c>
     </row>
@@ -16662,7 +16662,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Increase Tấn Công của Resonator thêm {0}. Khi Nạp Năng Lượng đạt {1}, tăng toàn bộ Sát Thương Thuộc Tính của Resonator thêm {2}.</t>
+          <t>Tăng ATK của Resonator thêm {0}. Khi Nạp Năng Lượng đạt {1}, tăng toàn bộ Sát Thương Thuộc Tính của Resonator thêm {2}.</t>
         </is>
       </c>
     </row>
@@ -16727,7 +16727,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Increase Tấn Công. Khi Tái Tạo Năng Lượng đạt 250%, tăng toàn bộ Sát Thương Thuộc Tính.</t>
+          <t>Tăng ATK. Khi Tái Tạo Năng Lượng đạt 250%, tăng toàn bộ Sát Thương Thuộc Tính.</t>
         </is>
       </c>
     </row>
@@ -16987,7 +16987,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Concerto Regen + {0}.</t>
+          <t>Hồi Năng Lượng + {0}.</t>
         </is>
       </c>
     </row>
@@ -17052,7 +17052,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>Aero DMG + {0}</t>
+          <t>DMG Aero +{0}</t>
         </is>
       </c>
     </row>
@@ -17117,7 +17117,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Gây Erosion Gió lên kẻ địch sẽ tăng Sát Thương Gió cho tất cả Resonators trong đội thêm {0}, và tăng thêm {1} cho Resonators kích hoạt hiệu ứng này, kéo dài trong {2} giây.</t>
+          <t>Gây Aero Erosion lên kẻ địch sẽ tăng Sát Thương Gió cho tất cả Resonator trong đội thêm {0}, và tăng thêm {1} cho Resonator kích hoạt hiệu ứng này, kéo dài trong {2} giây.</t>
         </is>
       </c>
     </row>
@@ -17182,7 +17182,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Gây Erosion Gió lên kẻ địch sẽ tăng Sát Thương Gió cho tất cả Resonators trong đội. Resonators kích hoạt hiệu ứng này sẽ nhận thêm lượng Sát Thương Gió tăng thêm.</t>
+          <t>Gây Aero Erosion lên kẻ địch sẽ tăng Sát Thương Gió cho tất cả Resonator trong đội. Resonator kích hoạt hiệu ứng này sẽ nhận thêm lượng Sát Thương Gió tăng thêm.</t>
         </is>
       </c>
     </row>
@@ -17247,7 +17247,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Aero DMG + {0}</t>
+          <t>DMG Aero +{0}</t>
         </is>
       </c>
     </row>
@@ -17312,7 +17312,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Tấn công mục tiêu bằng Erosion Gió sẽ tăng Crit. Rate thêm {0} và nhận thêm {1} Tăng Sát Thương Gió, hiệu ứng kéo dài {2}s.</t>
+          <t>Tấn công mục tiêu bằng Aero Erosion sẽ tăng Crit. Rate thêm {0} và nhận thêm {1} Tăng Sát Thương Gió, hiệu ứng kéo dài {2}s.</t>
         </is>
       </c>
     </row>
@@ -17377,7 +17377,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Tấn công mục tiêu bằng Erosion Gió sẽ tăng Crit. Rate và nhận thêm hiệu ứng Tăng Sát Thương Gió.</t>
+          <t>Tấn công mục tiêu bằng Aero Erosion sẽ tăng Crit. Rate và nhận thêm hiệu ứng Tăng Sát Thương Gió.</t>
         </is>
       </c>
     </row>
@@ -17442,7 +17442,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>Fusion DMG + {0}</t>
+          <t>Sát Thương Hợp Thể +{0}</t>
         </is>
       </c>
     </row>
@@ -17507,7 +17507,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>Kích hoạt Resonance Liberation tăng {0} Fusion DMG cho tất cả Resonators trong đội và {1} Sát Thương Resonance Liberation cho người sử dụng, kéo dài {2} giây.</t>
+          <t>Kích hoạt Giải Cứu Cộng Hưởng tăng {0} Sát Thương Fusion cho tất cả Resonator trong đội và {1} Sát Thương Giải Cứu Cộng Hưởng cho người sử dụng, kéo dài {2} giây.</t>
         </is>
       </c>
     </row>
@@ -17572,7 +17572,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>Kích hoạt Resonance Liberation tăng Fusion DMG cho tất cả Resonators trong đội và tăng Sát Thương Resonance Liberation cho người sử dụng.</t>
+          <t>Kích hoạt Giải Cứu Cộng Hưởng tăng Sát Thương Fusion cho tất cả Resonator trong đội và tăng Sát Thương Giải Cứu Cộng Hưởng cho người sử dụng.</t>
         </is>
       </c>
     </row>
@@ -17832,7 +17832,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Glacio DMG + 10%.</t>
+          <t>Tấn Công Băng giá tăng thêm 10%.</t>
         </is>
       </c>
     </row>
@@ -17897,7 +17897,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>Khi nhận được Shield, tăng Tấn Công của Resonator thêm {0} và Crit. DMG thêm {1} trong {3} giây. Hiệu ứng này có thể kích hoạt mỗi {4} giây một lần và chồng chất lên đến {2} lần.</t>
+          <t>Khi nhận được Khiên, tăng ATK của Resonator thêm {0} và Crit. DMG thêm {1} trong {3} giây. Hiệu ứng này có thể kích hoạt mỗi {4} giây một lần và chồng chất lên đến {2} lần.</t>
         </is>
       </c>
     </row>
@@ -17962,7 +17962,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>Khi nhận được Shield, tăng Tấn Công và Crit. DMG.</t>
+          <t>Khi nhận được Khiên, tăng ATK và Crit. DMG.</t>
         </is>
       </c>
     </row>
@@ -18028,8 +18028,8 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>Kích hoạt Kỹ Năng Echoes sẽ tăng {0} Sát Thương Heavy Attack cho người sử dụng trong {1} giây.
-Ngoài ra, tất cả Resonators trong đội sẽ nhận được {2} Sát Thương Kỹ Năng Echoes trong {4} giây, có thể tích lũy tối đa {3} lần. Các Echoes cùng tên chỉ có thể kích hoạt hiệu ứng này một lần. Dấu tích kích hoạt Echoes sẽ bị xóa cùng với hiệu ứng này. Khi đạt {3} tầng, kích hoạt lại Kỹ Năng Echoes sẽ làm mới thời gian hiệu ứng.</t>
+          <t>Kích hoạt Kỹ Năng Echo sẽ tăng {0} Sát Thương Đòn Heavy Attack cho người sử dụng trong {1} giây.
+Ngoài ra, tất cả Resonator trong đội sẽ nhận được {2} Sát Thương Kỹ Năng Echo trong {4} giây, có thể tích lũy tối đa {3} lần. Các Echo cùng tên chỉ có thể kích hoạt hiệu ứng này một lần. Dấu tích kích hoạt Echo sẽ bị xóa cùng với hiệu ứng này. Khi đạt {3} tầng, kích hoạt lại Kỹ Năng Echo sẽ làm mới thời gian hiệu ứng.</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Sử dụng Kỹ Năng Echo sẽ tăng Sát Thương Kỹ Năng Echo cho tất cả Resonators trong đội và tăng Sát Thương Heavy Attack cho người sử dụng.</t>
+          <t>Sử dụng Kỹ Năng Echo sẽ tăng Sát Thương Kỹ Năng Echo cho tất cả Resonator trong đội và tăng Sát Thương Heavy Attack cho người sử dụng.</t>
         </is>
       </c>
     </row>
@@ -18159,7 +18159,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Gây sát thương bằng Kỹ Năng Echo sẽ tăng Crit. Rate của Kỹ Năng Nặng thêm {0} trong {1} giây. Gây sát thương bằng Kỹ Năng Nặng sẽ tăng Crit. Rate của Kỹ Năng Echo thêm {2} trong {3} giây. Khi cả hai hiệu ứng cùng kích hoạt, nhận thêm {4} Fusion DMG.</t>
+          <t>Gây DMG bằng Kỹ Năng Echo sẽ tăng Crit. Rate của Kỹ Năng Nặng thêm {0} trong {1} giây. Gây DMG bằng Kỹ Năng Nặng sẽ tăng Crit. Rate của Kỹ Năng Echo thêm {2} trong {3} giây. Khi cả hai hiệu ứng cùng kích hoạt, nhận thêm {4} Sát Thương Fusion.</t>
         </is>
       </c>
     </row>
@@ -18224,7 +18224,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Nhận Thêm Sát Thương Hệ Nguyên Tố. Crit. Rate của Heavy Attack hoặc Kỹ Năng Echo tăng lên.</t>
+          <t>Nhận Thêm Sát Thương Hệ Nguyên Tố. Crit. Rate của Đòn Heavy Attack hoặc Kỹ Năng Echo tăng lên.</t>
         </is>
       </c>
     </row>
@@ -18289,7 +18289,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Gây Hiệu Ứng Hỗn Loạn sẽ tăng Tấn Công của Resonator thêm {0} và cộng thêm {1} Tăng Sát Thương Resonance Liberation trong {2} giây.</t>
+          <t>Gây Hiệu Ứng Hỗn Loạn sẽ tăng ATK của Resonator thêm {0} và cộng thêm {1} Tăng Sát Thương Resonance Liberation trong {2} giây.</t>
         </is>
       </c>
     </row>
@@ -18354,7 +18354,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Gây Tai Họa Hỗn Loạn sẽ tăng Tấn Công và trao thưởng Sát Thương Resonance Liberation.</t>
+          <t>Gây Havoc Bane sẽ tăng ATK và trao thưởng Sát Thương Resonance Liberation.</t>
         </is>
       </c>
     </row>
@@ -18419,7 +18419,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Spectro DMG + {0}</t>
+          <t>Sát Thương Spectro +{0}</t>
         </is>
       </c>
     </row>
@@ -18484,7 +18484,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Kích hoạt Kỹ Năng Kết tăng Tấn Công cho Resonator kế tiếp khi họ kích hoạt Kỹ Năng Giới Thiệu thêm {0}. Mỗi điểm Tăng Cường Phá Nhịp của Resonator kế tiếp sẽ tăng thêm Tấn Công của họ thêm {1}, tối đa {2}. Hiệu ứng này kéo dài trong {3} giây hoặc cho đến khi Resonator bị thay ra.</t>
+          <t>Kích hoạt Kỹ Năng Kết tăng ATK cho Resonator kế tiếp khi họ kích hoạt Kỹ Năng Giới Thiệu thêm {0}. Mỗi điểm Tăng Cường Phá Nhịp của Resonator kế tiếp sẽ tăng thêm ATK của họ thêm {1}, tối đa {2}. Hiệu ứng này kéo dài trong {3} giây hoặc cho đến khi Resonator bị thay ra.</t>
         </is>
       </c>
     </row>
@@ -18549,7 +18549,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>Kích hoạt Kỹ Năng Kết tăng Tấn Công cho Resonator kế tiếp và trao thêm hiệu ứng tăng Tấn Công dựa trên Tăng Cường Phá Nhịp của họ.</t>
+          <t>Kích hoạt Kỹ Năng Kết tăng ATK cho Resonator kế tiếp và trao thêm hiệu ứng tăng ATK dựa trên Tăng Cường Phá Nhịp của họ.</t>
         </is>
       </c>
     </row>
@@ -18614,7 +18614,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Healing Bonus +{0}.</t>
+          <t>Tăng Hiệu Quả Hồi Phục +{0}.</t>
         </is>
       </c>
     </row>
@@ -18679,7 +18679,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Khi hồi phục một Resonators trong đội, mỗi {0} Tỷ Lệ Lệch Nhịp tích lũy sẽ tăng {1} Tấn Công cho tất cả Resonators trong đội trong {3} giây, tối đa {2}. Hiệu ứng cùng tên không thể chồng chất.</t>
+          <t>Khi hồi phục một Resonator trong đội, mỗi {0} Tỷ Lệ Lệch Nhịp tích lũy sẽ tăng {1} ATK cho tất cả Resonator trong đội trong {3} giây, tối đa {2}. Hiệu ứng cùng tên không thể chồng chất.</t>
         </is>
       </c>
     </row>
@@ -18744,7 +18744,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>Hồi phục đồng minh sẽ tăng Tấn Công cho Resonators trong đội dựa trên tỷ lệ Dị Tần Tích Lũy hiện tại.</t>
+          <t>Hồi phục đồng minh sẽ tăng ATK cho Resonator trong đội dựa trên tỷ lệ Dị Tần Tích Lũy hiện tại.</t>
         </is>
       </c>
     </row>
@@ -18809,7 +18809,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Spectro DMG + {0}</t>
+          <t>Sát Thương Spectro +{0}</t>
         </is>
       </c>
     </row>
@@ -18874,7 +18874,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>Gây Sát Thương Basic Attack sẽ tăng Spectro DMG thêm {0} trong {2} giây, có thể tích lũy tối đa {1} lần. Khi đạt {1} tầng, sử dụng Resonance Liberation sẽ tăng {3} Sát Thương Basic Attack.</t>
+          <t>Gây Sát Thương Basic Attack sẽ tăng Sát Thương Spectro thêm {0} trong {2} giây, có thể tích lũy tối đa {1} lần. Khi đạt {1} tầng, sử dụng Resonance Liberation sẽ tăng {3} Sát Thương Basic Attack.</t>
         </is>
       </c>
     </row>
@@ -18939,7 +18939,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Gây Sát Thương Basic Attack sẽ tăng Spectro DMG, có thể tích lũy. Khi đạt tối đa, sử dụng Resonance Liberation sẽ tăng Sát Thương Basic Attack.</t>
+          <t>Gây Sát Thương Basic Attack sẽ tăng Sát Thương Spectro, có thể tích lũy. Khi đạt tối đa, sử dụng Resonance Liberation sẽ tăng Sát Thương Basic Attack.</t>
         </is>
       </c>
     </row>
@@ -19004,7 +19004,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Fusion DMG + {0}</t>
+          <t>Sát Thương Hợp Thể +{0}</t>
         </is>
       </c>
     </row>
@@ -19069,7 +19069,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Gây Nổ Nhiệt Hạch hoặc Tune Rupture - Shifting lên kẻ địch sẽ tăng Crit. Rate của Resonator thêm {0} và trao thưởng {1} Sát Thương Nhiệt Hạch trong {2} giây.</t>
+          <t>Gây Fusion Burst hoặc Đứt Giai Điệu - Dịch Chuyển lên kẻ địch sẽ tăng Crit. Rate của Resonator thêm {0} và trao thưởng {1} Sát Thương Nhiệt Hạch trong {2} giây.</t>
         </is>
       </c>
     </row>
@@ -19134,7 +19134,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Gây Nổ Nhiệt Hạch hoặc Tune Rupture - Shifting sẽ tăng Crit. Rate và trao thưởng Sát Thương Nhiệt Hạch.</t>
+          <t>Gây Fusion Burst hoặc Đứt Giai Điệu - Dịch Chuyển sẽ tăng Crit. Rate và trao thưởng Sát Thương Nhiệt Hạch.</t>
         </is>
       </c>
     </row>
@@ -19199,7 +19199,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Fusion DMG + {0}</t>
+          <t>Sát Thương Hợp Thể +{0}</t>
         </is>
       </c>
     </row>
@@ -19264,7 +19264,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>Khi Resonator gây hiệu ứng Fusion Burst lên kẻ địch, họ sẽ nhận được các hiệu ứng sau: Nhận thêm {0} Fusion DMG trong {1} giây. Trong thời gian hiệu ứng này còn tác dụng, nếu sử dụng Outro Skill, Resonator tiếp theo sẽ nhận thêm {2} Fusion DMG trong {3} giây.</t>
+          <t>Khi Resonator gây hiệu ứng Fusion Burst lên kẻ địch, họ sẽ nhận được các hiệu ứng sau: Nhận thêm {0} Sát Thương Fusion trong {1} giây. Trong thời gian hiệu ứng này còn tác dụng, nếu sử dụng Kỹ Năng Outro, Resonator tiếp theo sẽ nhận thêm {2} Sát Thương Fusion trong {3} giây.</t>
         </is>
       </c>
     </row>
@@ -19329,7 +19329,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Gây Nổ Nhiệt Hạch sẽ tăng thưởng Sát Thương Nhiệt Hạch. Trong thời gian này, sử dụng Outro Skill sẽ trao thưởng Sát Thương Nhiệt Hạch cho Resonator tiếp theo.</t>
+          <t>Gây Fusion Burst sẽ tăng thưởng Sát Thương Nhiệt Hạch. Trong thời gian này, sử dụng Kỹ Năng Outro sẽ trao thưởng Sát Thương Nhiệt Hạch cho Resonator tiếp theo.</t>
         </is>
       </c>
     </row>
@@ -19394,7 +19394,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>Aero DMG + {0}</t>
+          <t>DMG Aero +{0}</t>
         </is>
       </c>
     </row>
@@ -19459,7 +19459,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>Gây sát thương bằng Kỹ Năng Echo lên kẻ địch sẽ tăng Crit. Rate Kỹ Năng Echo của Resonator thêm {0} và tăng {1} Aero DMG trong {2} giây.</t>
+          <t>Gây DMG bằng Kỹ Năng Echo lên kẻ địch sẽ tăng Crit. Rate Kỹ Năng Echo của Resonator thêm {0} và tăng {1} Sát Thương Aero trong {2} giây.</t>
         </is>
       </c>
     </row>
@@ -19524,7 +19524,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>Gây sát thương bằng Kỹ Năng Echo sẽ tăng Crit. Rate của Kỹ Năng Echo và tăng thêm Aero DMG.</t>
+          <t>Gây DMG bằng Kỹ Năng Echo sẽ tăng Crit. Rate của Kỹ Năng Echo và tăng thêm Sát Thương Aero.</t>
         </is>
       </c>
     </row>
@@ -19654,7 +19654,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Attack Băng giá tăng thêm 10% sau khi thực hiện Basic Attack hoặc Heavy Attack. Hiệu ứng này có thể chồng chất lên đến 3 lần, mỗi lần kéo dài 15 giây.</t>
+          <t>Tấn Công Băng giá tăng thêm 10% sau khi thực hiện Đòn Cơ Bản hoặc Đòn Nặng. Hiệu ứng này có thể chồng chất lên đến 3 lần, mỗi lần kéo dài 15 giây.</t>
         </is>
       </c>
     </row>
@@ -19719,7 +19719,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>Khi sử dụng Basic Attack hoặc Heavy Attack, Glacio DMG tăng lên.</t>
+          <t>Tấn Công Băng giá tăng thêm 10% sau khi thực hiện Đòn Cơ Bản hoặc Đòn Nặng. Hiệu ứng này có thể chồng chất lên đến 3 lần, mỗi lần kéo dài 15 giây.</t>
         </is>
       </c>
     </row>
@@ -19849,7 +19849,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>Fusion DMG + 10%.</t>
+          <t>Sát Thương Hợp Thể +10%.</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Fusion DMG +30% trong 15 giây sau khi giải phóng Resonance Skill.</t>
+          <t>Sát Thương Hợp Thể +30% trong 15 giây sau khi giải phóng Resonance Skill.</t>
         </is>
       </c>
     </row>
@@ -19979,7 +19979,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Khi dùng Resonance Skill, Fusion DMG tăng lên</t>
+          <t>Sát Thương Hợp Thể +30% trong 15 giây sau khi giải phóng Resonance Skill.</t>
         </is>
       </c>
     </row>
@@ -20109,7 +20109,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Electro DMG + 10%.</t>
+          <t>Sát Thương Electro +10%.</t>
         </is>
       </c>
     </row>
@@ -20239,7 +20239,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>Electro DMG tăng thêm 15% sau khi tung đòn Heavy Attack hoặc Resonance Skill. Hiệu ứng này có thể chồng chất tối đa 2 lần, mỗi lần kéo dài 15 giây.</t>
+          <t>Sát Thương Electro tăng thêm 15% sau khi tung đòn Heavy Attack hoặc Resonance Skill. Hiệu ứng này có thể chồng chất tối đa 2 lần, mỗi lần kéo dài 15 giây.</t>
         </is>
       </c>
     </row>
@@ -20304,7 +20304,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Khi sử dụng Heavy Attack hoặc Resonance Skill, Electro DMG tăng lên.</t>
+          <t>Sát Thương Electro tăng thêm 15% sau khi tung đòn Heavy Attack hoặc Resonance Skill. Hiệu ứng này có thể chồng chất tối đa 2 lần, mỗi lần kéo dài 15 giây.</t>
         </is>
       </c>
     </row>
@@ -20434,7 +20434,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Aero DMG + 10%.</t>
+          <t>DMG Aero +10%.</t>
         </is>
       </c>
     </row>
@@ -20564,7 +20564,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Aero DMG tăng 30% trong 15 giây sau khi giải phóng Intro Skill.</t>
+          <t>DMG Aero tăng 30% trong 15 giây sau khi giải phóng Kỹ Năng Khởi Động.</t>
         </is>
       </c>
     </row>
@@ -20629,7 +20629,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>Khi dùng Intro Skill, Aero DMG tăng lên</t>
+          <t>DMG Aero tăng 30% trong 15 giây sau khi giải phóng Kỹ Năng Khởi Động.</t>
         </is>
       </c>
     </row>
@@ -20759,7 +20759,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Spectro DMG + 10%.</t>
+          <t>Sát Thương Spectro +10%.</t>
         </is>
       </c>
     </row>
@@ -20826,9 +20826,9 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Gây Trầy Băng Giá sẽ trao thưởng Sát Thương Băng Giá và hiệu ứng Tuyết Rơi:
+          <t>Gây Glacio Chafe sẽ trao thưởng Sát Thương Băng Giá và hiệu ứng Tuyết Rơi:
 - Gây Sát Thương Resonance Liberation sẽ loại bỏ Tuyết Rơi và tăng Crit. Rate. Khi hiệu ứng này đang hoạt động, gây Sát Thương Resonance Liberation sẽ kéo dài thời gian của nó.
-- Sử dụng Outro Skill sẽ loại bỏ Tuyết Rơi và trao thưởng Sát Thương Băng Giá cho Resonator tiếp theo.</t>
+- Sử dụng Kỹ Năng Outro sẽ loại bỏ Tuyết Rơi và trao thưởng Sát Thương Băng Giá cho Resonator tiếp theo.</t>
         </is>
       </c>
     </row>
@@ -20893,7 +20893,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>Gây Hiệu Ứng Vỡ Giai Tune - Dịch Chuyển hoặc Tune Strain - Shifting lên kẻ địch sẽ tăng Tăng Cường Tune Break cho Resonators trong đội.</t>
+          <t>Gây Hiệu Ứng Vỡ Giai Điệu - Dịch Chuyển hoặc Căng Giai Điệu - Dịch Chuyển lên kẻ địch sẽ tăng Tăng Cường Phá Giai Điệu cho các Resonator trong đội.</t>
         </is>
       </c>
     </row>
@@ -20958,7 +20958,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Glacio DMG + {0}</t>
+          <t>Tấn Công Băng giá tăng thêm {0}</t>
         </is>
       </c>
     </row>
@@ -21026,9 +21026,9 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Gây Trầy Băng Giá lên kẻ địch sẽ tăng Sát Thương Băng Giá gây ra thêm {0} trong {1} giây. Resonator nhận hiệu ứng Tuyết Rơi trong {11} giây, có thể kích hoạt một lần mỗi {2} giây. Khi Tuyết Rơi đang hoạt động:
+          <t>Gây Glacio Chafe lên kẻ địch sẽ tăng Sát Thương Băng Giá gây ra thêm {0} trong {1} giây. Resonator nhận hiệu ứng Tuyết Rơi trong {11} giây, có thể kích hoạt một lần mỗi {2} giây. Khi Tuyết Rơi đang hoạt động:
 - Gây Sát Thương Resonance Liberation sẽ loại bỏ Tuyết Rơi và tăng Crit. Rate của Resonator thêm {4} trong {5} giây. Khi hiệu ứng này đang hoạt động, gây Sát Thương Resonance Liberation sẽ kéo dài thời gian của nó thêm {8} giây, kích hoạt một lần mỗi {9} giây, tối đa {10} lần.
-- Sử dụng Outro Skill sẽ loại bỏ Tuyết Rơi và trao thưởng {6} Sát Thương Băng Giá cho Resonator tiếp theo trong {7} giây.
+- Sử dụng Kỹ Năng Outro sẽ loại bỏ Tuyết Rơi và trao thưởng {6} Sát Thương Băng Giá cho Resonator tiếp theo trong {7} giây.
 Khi Tuyết Rơi bị loại bỏ, chỉ một trong hai hiệu ứng trên có thể được kích hoạt.</t>
         </is>
       </c>
@@ -21094,7 +21094,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Tấn Công + {0}</t>
+          <t>ATK + {0}</t>
         </is>
       </c>
     </row>
@@ -21159,7 +21159,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Gây Hiệu Ứng Vỡ Giai Tune - Dịch Chuyển hoặc Tune Strain - Shifting lên kẻ địch sẽ tăng Tăng Cường Tune Break cho Resonators trong đội thêm {0} trong {1} giây. Hiệu ứng cùng tên không cộng dồn.</t>
+          <t>Gây Hiệu Ứng Vỡ Giai Điệu - Dịch Chuyển hoặc Căng Giai Điệu - Dịch Chuyển lên kẻ địch sẽ tăng Tăng Cường Phá Giai Điệu cho các Resonator trong đội thêm {0} trong {1} giây. Hiệu ứng cùng tên không cộng dồn.</t>
         </is>
       </c>
     </row>
@@ -21225,7 +21225,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Effect Bộ Hồi Âm: Dream of the Lost
+          <t>Hiệu Ứng Bộ Hồi Âm: Giấc Mộng Lạc Lối
 3 món: Giữ 0 Resonance Energy sẽ tăng Crit. Rate 20% và tăng Sát Thương Kỹ Năng Hồi Âm 35%.</t>
         </is>
       </c>
@@ -21292,8 +21292,8 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>Effect Bộ Hồi Âm: Vương Miện Valor
-3 món: Khi nhận được Shield, Resonator được bảo vệ sẽ tăng Tấn Công và Crit. DMG lần lượt 6% và 4% trong 4 giây, tối đa 5 lần chồng chất. Hiệu ứng này có thể kích hoạt mỗi 0,5 giây một lần.</t>
+          <t>Hiệu Ứng Bộ Hồi Âm: Vương Miện Dũng Khí
+3 món: Khi nhận được Khiên, Resonator được bảo vệ sẽ tăng ATK và Crit. DMG lần lượt 6% và 4% trong 4 giây, tối đa 5 lần chồng chất. Hiệu ứng này có thể kích hoạt mỗi 0,5 giây một lần.</t>
         </is>
       </c>
     </row>
@@ -21359,8 +21359,8 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Hiệu ứng Bộ Echoes Sonata: Quy Luật Hòa Âm
-3 món: Khi sử dụng Kỹ Năng Echoes, Resonators nhận thêm 30% Sát Thương Heavy Attack trong 4 giây. Đồng thời, tất cả Resonators trong đội nhận thêm 4% Sát Thương Kỹ Năng Echoes trong 30 giây, có thể cộng dồn tối đa 4 lần. Các Echoes cùng tên chỉ kích hoạt hiệu ứng này một lần. Dấu hiệu kích hoạt sẽ bị xóa cùng với hiệu ứng. Khi đạt 4 lần cộng dồn, sử dụng lại Kỹ Năng Echoes sẽ làm mới thời gian hiệu lực.</t>
+          <t>Hiệu ứng Bộ Echo Sonata: Quy Luật Hòa Âm
+3 món: Khi sử dụng Kỹ Năng Echo, Resonator nhận thêm 30% Sát Thương Đòn Heavy Attack trong 4 giây. Đồng thời, tất cả Resonator trong đội nhận thêm 4% Sát Thương Kỹ Năng Echo trong 30 giây, có thể cộng dồn tối đa 4 lần. Các Echo cùng tên chỉ kích hoạt hiệu ứng này một lần. Dấu hiệu kích hoạt sẽ bị xóa cùng với hiệu ứng. Khi đạt 4 lần cộng dồn, sử dụng lại Kỹ Năng Echo sẽ làm mới thời gian hiệu lực.</t>
         </is>
       </c>
     </row>
@@ -21426,8 +21426,8 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Effect Bộ Hồi Âm: Bóng Dáng Cánh Lửa
-3 món: Gây Sát Thương Kỹ Năng Hồi Âm sẽ tăng Crit. Rate của Heavy Attack lên 20% trong 6 giây. Gây Sát Thương Heavy Attack sẽ tăng Crit. Rate của Kỹ Năng Hồi Âm lên 20% trong 6 giây. Khi cả hai hiệu ứng cùng hoạt động, nhận thêm 16% Fusion DMG.</t>
+          <t>Hiệu Ứng Bộ Hồi Âm: Bóng Dáng Cánh Lửa
+3 món: Gây Sát Thương Kỹ Năng Hồi Âm sẽ tăng Crit. Rate của Đòn Nặng lên 20% trong 6 giây. Gây Sát Thương Đòn Nặng sẽ tăng Crit. Rate của Kỹ Năng Hồi Âm lên 20% trong 6 giây. Khi cả hai hiệu ứng cùng hoạt động, nhận thêm 16% Sát Thương Fusion.</t>
         </is>
       </c>
     </row>
@@ -21493,8 +21493,8 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Hiệu ứng Bộ Echo Sonata: Sợi Chỉ Fate Đứt Đoạn
-3 món: Gây hiệu ứng Havoc Bane làm tăng 20% Tấn Công của Resonator và ban thêm 30% Sát Thương Resonance Liberation trong 5 giây.</t>
+          <t>Hiệu ứng Bộ Echo Sonata: Sợi Chỉ Định Mệnh Đứt Đoạn
+3 món: Gây hiệu ứng Havoc Bane làm tăng 20% ATK của Resonator và ban thêm 30% Sát Thương Resonance Liberation trong 5 giây.</t>
         </is>
       </c>
     </row>
@@ -21561,9 +21561,9 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Effect Bộ Hồi Âm: Cơn Gió Của Bầu Trời
-2 món: Aero DMG +10%.
-5 món: Gây Erosion Aero lên kẻ địch sẽ tăng Aero DMG cho tất cả Resonators trong đội lên 15%, và tăng thêm 15% cho Resonators kích hoạt hiệu ứng này, kéo dài trong 20 giây.</t>
+          <t>Hiệu Ứng Bộ Hồi Âm: Cơn Gió Của Bầu Trời
+2 món: Sát Thương Aero +10%.
+5 món: Gây Xói Mòn Aero lên kẻ địch sẽ tăng Sát Thương Aero cho tất cả Resonator trong đội lên 15%, và tăng thêm 15% cho Resonator kích hoạt hiệu ứng này, kéo dài trong 20 giây.</t>
         </is>
       </c>
     </row>
@@ -21631,8 +21631,8 @@
       <c r="M311" t="inlineStr">
         <is>
           <t>Hiệu ứng Bộ Echo Sonata: Hành Hương Gió Nổi
-2 món: Aero DMG +10%.
-5 món: Đánh trúng mục tiêu bị Aero Erosion làm tăng 10% Crit. Rate và ban thêm 30% Aero DMG, kéo dài trong 10 giây.</t>
+2 món: Sát Thương Aero +10%.
+5 món: Đánh trúng mục tiêu bị Aero Erosion làm tăng 10% Crit. Rate và ban thêm 30% Sát Thương Aero, kéo dài trong 10 giây.</t>
         </is>
       </c>
     </row>
@@ -21699,9 +21699,9 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Effect Bộ Hồi Âm: Ý Chí Băng Giá
+          <t>Hiệu Ứng Bộ Hồi Âm: Ý Chí Băng Giá
 2 món: Sát Thương Resonance Skill +12%.
-5 món: Sử dụng Resonance Skill sẽ tăng Glacio DMG 22,5% trong 15 giây, và sử dụng Resonance Liberation sẽ tăng Sát Thương Resonance Skill 18% trong 5 giây. Hiệu ứng này có thể chồng chất tối đa 2 lần.</t>
+5 món: Sử dụng Resonance Skill sẽ tăng Sát Thương Glacio 22,5% trong 15 giây, và sử dụng Resonance Liberation sẽ tăng Sát Thương Resonance Skill 18% trong 5 giây. Hiệu ứng này có thể chồng chất tối đa 2 lần.</t>
         </is>
       </c>
     </row>
@@ -21768,9 +21768,9 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Effect Bộ Hồi Âm: Khúc Ca Thiên Đình
+          <t>Hiệu Ứng Bộ Hồi Âm: Khúc Ca Thiên Đình
 2 món: Hồi Phục Năng Lượng +10%.
-5 món: Increase Sát Thương Đòn Phối Hợp của Resonator lên 80%. Khi Đòn Phối Hợp gây ra bạo kích, tăng Attack của Resonator đang hoạt động lên 20% trong 4 giây.</t>
+5 món: Tăng Sát Thương Đòn Phối Hợp của Resonator lên 80%. Khi Đòn Phối Hợp gây ra bạo kích, tăng ATK của Resonator đang hoạt động lên 20% trong 4 giây.</t>
         </is>
       </c>
     </row>
@@ -21838,8 +21838,8 @@
       <c r="M314" t="inlineStr">
         <is>
           <t>Hiệu ứng Bộ Echo Sonata: Cơn Gió Sierra
-2 món: Aero DMG +10%.
-5 món: Aero DMG +30% trong 15 giây sau khi giải phóng Intro Skill.</t>
+2 món: Sát Thương Aero +10%.
+5 món: Sát Thương Aero +30% trong 15 giây sau khi giải phóng Kỹ Năng Intro.</t>
         </is>
       </c>
     </row>
@@ -21907,8 +21907,8 @@
       <c r="M315" t="inlineStr">
         <is>
           <t>Hiệu ứng Bộ Echo Sonata: Màn Đêm Che Phủ
-2 món: Havoc DMG +10%.
-5 món: Kích hoạt Outro Skill gây thêm 480% Havoc DMG lên kẻ địch xung quanh và ban cho Resonator kế tiếp 15% Havoc DMG trong 15 giây.</t>
+2 món: Sát Thương Havoc +10%.
+5 món: Kích hoạt Kỹ Năng Outro gây thêm 480% Sát Thương Havoc lên kẻ địch xung quanh và ban cho Resonator kế tiếp 15% Sát Thương Havoc trong 15 giây.</t>
         </is>
       </c>
     </row>
@@ -21975,9 +21975,9 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Hiệu ứng Bộ Echo Sonata: Hư Không Thunder
-2 món: Electro DMG + 10%.
-5 món: Electro DMG +15% sau khi giải phóng Heavy Attack hoặc Resonance Skill. Hiệu ứng này có thể cộng dồn tối đa 2 lần, mỗi lần kéo dài 15 giây.</t>
+          <t>Hiệu ứng Bộ Echo Sonata: Hư Không Sấm Sét
+2 món: Sát Thương Electro +10%.
+5 món: Sát Thương Electro +15% sau khi giải phóng Đòn Heavy Attack hoặc Resonance Skill. Hiệu ứng này có thể cộng dồn tối đa 2 lần, mỗi lần kéo dài 15 giây.</t>
         </is>
       </c>
     </row>
@@ -22044,9 +22044,9 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>Effect Bộ Hồi Âm: Nhật Thực Hỗn Loạn
-2 món: Havoc DMG + 10%.
-5 món: Sau khi tung Basic Attack hoặc Heavy Attack, Havoc DMG tăng thêm 7,5%. Hiệu ứng này có thể chồng chất tối đa 4 lần, mỗi lần kéo dài 15 giây.</t>
+          <t>Hiệu Ứng Bộ Hồi Âm: Nhật Thực Hỗn Loạn
+2 món: Sát Thương Havoc +10%.
+5 món: Sau khi tung Đòn Cơ Bản hoặc Đòn Nặng, Sát Thương Havoc tăng thêm 7,5%. Hiệu ứng này có thể chồng chất tối đa 4 lần, mỗi lần kéo dài 15 giây.</t>
         </is>
       </c>
     </row>
@@ -22114,8 +22114,8 @@
       <c r="M318" t="inlineStr">
         <is>
           <t>Hiệu ứng Bộ Echo Sonata: Vết Nứt Nham Thạch
-2 món: Fusion DMG +10%.
-5 món: Fusion DMG +30% trong 15 giây sau khi giải phóng Resonance Skill.</t>
+2 món: Sát Thương Fusion +10%.
+5 món: Sát Thương Fusion +30% trong 15 giây sau khi giải phóng Resonance Skill.</t>
         </is>
       </c>
     </row>
@@ -22182,9 +22182,9 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Effect Bộ Hồi Âm: Ánh Sáng Vĩnh Hằng
-2 món: Spectro DMG +10%.
-5 món: Gây Choáng Spectro lên kẻ địch sẽ tăng Crit. Rate 20% trong 15 giây. Tấn công kẻ địch bị Choáng Spectro 10 tầng sẽ tăng thêm 15% Spectro DMG trong 15 giây.</t>
+          <t>Hiệu Ứng Bộ Hồi Âm: Ánh Sáng Vĩnh Hằng
+2 món: Sát Thương Spectro +10%.
+5 món: Gây Choáng Spectro lên kẻ địch sẽ tăng Crit. Rate 20% trong 15 giây. Tấn công kẻ địch bị Choáng Spectro 10 tầng sẽ tăng thêm 15% Sát Thương Spectro trong 15 giây.</t>
         </is>
       </c>
     </row>
@@ -22250,7 +22250,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>Manh mối khả dụng: Thường xuất hiện ở Tiger's Maw.
+          <t>Manh mối khả dụng: Thường xuất hiện ở Hàm Hổ.
 Diamondclaws ẩn nấp trong những khu vực tối tăm, sử dụng đôi càng kim cương cứng cáp và nặng nề như vũ khí sát thương đối thủ.</t>
         </is>
       </c>
@@ -22317,7 +22317,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>Biến thành Stonewall Bracer và lao về phía trước, gây {0} Sát Thương Physical khi va chạm, sau đó đập mạnh xuống gây {1} Sát Thương Physical, và nhận một lớp Khiên tương đương {2} HP Tối Đa của nhân vật hiện tại, kéo dài {3} giây. Sử dụng Kỹ Năng Echo một lần nữa để thoát khỏi trạng thái biến hình.
+          <t>Biến hình thành Stonewall Bracer và lao về phía trước, gây {0} Sát Thương Vật Lý khi va chạm, sau đó đập mạnh xuống gây {1} Sát Thương Vật Lý, và nhận một lớp Khiên tương đương {2} HP Tối Đa của nhân vật hiện tại, kéo dài {3} giây. Sử dụng Kỹ Năng Echo một lần nữa để thoát khỏi trạng thái biến hình.
 Hồi chiêu: {4} giây</t>
         </is>
       </c>
@@ -22384,7 +22384,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>Summon Vanguard Junrock lao về phía trước, gây {0} Sát Thương Physical cho kẻ địch trên đường đi.
+          <t>Triệu hồi Tiền Phong Junrock lao về phía trước, gây {0} Sát Thương Vật Lý cho kẻ địch trên đường đi.
 Hồi chiêu: {1} giây</t>
         </is>
       </c>
@@ -22450,7 +22450,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>Summon Vanguard Junrock lao về phía trước, gây Sát Thương Physical cho kẻ địch trên đường đi.</t>
+          <t>Triệu hồi Tiền Phong Junrock lao về phía trước, gây Sát Thương Vật Lý cho kẻ địch trên đường đi.</t>
         </is>
       </c>
     </row>
@@ -22516,7 +22516,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Summon Fission Junrock. Tạo hiệu ứng Resonance, mỗi lần hồi {0} HP cho đồng đội. Nếu không trong chiến đấu, cậu có thể thu thập khoáng vật hoặc thực vật gần đó.
+          <t>Triệu hồi Fission Junrock. Tạo hiệu ứng Cộng Hưởng, mỗi lần hồi {0} HP cho đồng đội. Nếu không trong chiến đấu, cậu có thể thu thập khoáng vật hoặc thực vật gần đó.
 Hồi chiêu: {1} giây</t>
         </is>
       </c>
@@ -22583,7 +22583,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Summon Snip Snap Dodgem cầu lửa vào kẻ địch, gây {0} Fusion DMG khi trúng.
+          <t>Triệu hồi Snip Snap ném cầu lửa vào kẻ địch, gây {0} Sát Thương Fusion khi trúng.
 Hồi chiêu: {1} giây.</t>
         </is>
       </c>
@@ -22649,7 +22649,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>Summon Snip Snap Dodgem cầu lửa, gây Fusion DMG.</t>
+          <t>Triệu hồi Snip Snap ném cầu lửa, gây Sát Thương Fusion.</t>
         </is>
       </c>
     </row>
@@ -22715,7 +22715,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Summon Whiff Whaff kích nổ luồng khí, gây {0} Aero DMG và tạo Vùng Áp Suất Low. Vùng này liên tục hút kẻ địch xung quanh vào trung tâm trong {1} giây, gây {2} Aero DMG tối đa 6 lần.
+          <t>Triệu hồi Whiff Whaff kích nổ luồng khí, gây {0} Sát Thương Aero và tạo Vùng Áp Suất Thấp. Vùng này liên tục hút kẻ địch xung quanh vào trung tâm trong {1} giây, gây {2} Sát Thương Aero tối đa 6 lần.
 Hồi chiêu: {3} giây</t>
         </is>
       </c>
@@ -22781,7 +22781,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Summon Whiff Whaff gây Aero DMG và tạo Vùng Áp Suất Low.</t>
+          <t>Triệu hồi Whiff Whaff gây Sát Thương Aero và tạo Vùng Áp Suất Thấp.</t>
         </is>
       </c>
     </row>
@@ -22847,7 +22847,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Summon Zig Zag kích nổ năng lượng Spectro, gây {0} Spectro DMG và tạo ra Vùng Trì Trệ kéo dài 1,8 giây.
+          <t>Triệu hồi Zig Zag kích nổ năng lượng Spectro, gây {0} Sát Thương Spectro và tạo ra Vùng Trì Trệ kéo dài 1,8 giây.
 Hồi chiêu: {1} giây</t>
         </is>
       </c>
@@ -22913,7 +22913,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Summon Zig Zag gây Spectro DMG và tạo ra Vùng Trì Trệ.</t>
+          <t>Triệu hồi Zig Zag gây Sát Thương Spectro và tạo ra Vùng Trì Trệ.</t>
         </is>
       </c>
     </row>
@@ -22979,7 +22979,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Summon Tick Tack lao vào và cắn kẻ địch. Pha lao của Tick Tack gây {0} Sát Thương Hỗn Loạn, còn cú cắn gây {1} Sát Thương Hỗn Loạn. deplete Vibration Strength của kẻ địch tối đa {3} trong {2} giây.
+          <t>Triệu hồi Tick Tack lao vào và cắn kẻ địch. Pha lao của Tick Tack gây {0} Sát Thương Hỗn Loạn, còn cú cắn gây {1} Sát Thương Hỗn Loạn. Giảm Sức Rung của kẻ địch tối đa {3} trong {2} giây.
 Hồi chiêu: {4} giây</t>
         </is>
       </c>
@@ -23045,7 +23045,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>Summon Tick Tack gây Sát Thương Hỗn Loạn và giảm Vibration Strength của kẻ địch.</t>
+          <t>Triệu hồi Tick Tack gây Sát Thương Hỗn Loạn và giảm Sức Rung của kẻ địch.</t>
         </is>
       </c>
     </row>
@@ -23111,7 +23111,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>Summon Glacio Prism bắn liên tục ba mảnh tinh thể, mỗi mảnh gây {0} Glacio DMG.
+          <t>Triệu hồi Lăng Kính Glacio bắn liên tục ba mảnh tinh thể, mỗi mảnh gây {0} Sát Thương Glacio.
 Hồi chiêu: {1} giây</t>
         </is>
       </c>
@@ -23177,7 +23177,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>Summon Glacio Prism bắn các mảnh tinh thể gây Glacio DMG.</t>
+          <t>Triệu hồi Lăng Kính Glacio bắn các mảnh tinh thể gây Sát Thương Glacio.</t>
         </is>
       </c>
     </row>
@@ -23243,7 +23243,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>Summon Prism Hợp Thể bắn một mảnh pha lê, gây {0} Sát Thương Hợp Thể.
+          <t>Triệu hồi Lăng Kính Hợp Thể bắn một mảnh pha lê, gây {0} Sát Thương Hợp Thể.
 Hồi chiêu: {1} giây</t>
         </is>
       </c>
@@ -23309,7 +23309,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>Summon Prism Hợp Thể bắn mảnh pha lê gây Sát Thương Hợp Thể.</t>
+          <t>Triệu hồi Lăng Kính Hợp Thể bắn mảnh pha lê gây Sát Thương Hợp Thể.</t>
         </is>
       </c>
     </row>
@@ -23375,7 +23375,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>Summon Prism Ngân Hưởng phát ra tia laser tấn công kẻ địch tối đa {0} times, mỗi lần gây {1} Sát Thương Ngân Hưởng.
+          <t>Triệu hồi Lăng Kính Ngân Hưởng phát ra tia laser tấn công kẻ địch tối đa {0} lần, mỗi lần gây {1} Sát Thương Ngân Hưởng.
 Hồi chiêu: {2} giây</t>
         </is>
       </c>
@@ -23441,7 +23441,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>Summon Prism Ngân Hưởng bắn tia laser gây Sát Thương Ngân Hưởng.</t>
+          <t>Triệu hồi Lăng Kính Ngân Hưởng bắn tia laser gây Sát Thương Ngân Hưởng.</t>
         </is>
       </c>
     </row>
@@ -23507,7 +23507,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Summon một Havoc Prism bắn ra năm mảnh tinh thể, mỗi mảnh gây {0} Havoc DMG.
+          <t>Triệu hồi một Havoc Prism bắn ra năm mảnh tinh thể, mỗi mảnh gây {0} Sát Thương Havoc.
 Hồi chiêu: {1} giây</t>
         </is>
       </c>
@@ -23573,7 +23573,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Summon một Havoc Prism gây Havoc DMG bằng các mảnh tinh thể.</t>
+          <t>Triệu hồi một Havoc Prism gây Sát Thương Havoc bằng các mảnh tinh thể.</t>
         </is>
       </c>
     </row>
@@ -23639,7 +23639,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Biến thành Fusion Warrior để phản đòn. Nếu phản đòn thành công, Cooldown chiêu của kỹ năng này sẽ giảm {0} giây và gây {1} Fusion DMG.
+          <t>Biến hình thành Chiến Binh Fusion để phản đòn. Nếu phản đòn thành công, thời gian hồi chiêu của kỹ năng này sẽ giảm {0} giây và gây {1} Sát Thương Fusion.
 Hồi chiêu: {2}s</t>
         </is>
       </c>
@@ -23705,7 +23705,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>Biến thành Fusion Warrior để chặn đòn tấn công của kẻ địch. Khi chặn thành công, gây Fusion DMG và giảm Cooldown chiêu của Kỹ Năng Echo này.</t>
+          <t>Biến hình thành Chiến Binh Fusion để chặn đòn tấn công của kẻ địch. Khi chặn thành công, gây Sát Thương Fusion và giảm thời gian hồi chiêu của Kỹ Năng Echo này.</t>
         </is>
       </c>
     </row>
@@ -23771,7 +23771,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Biến thành Chiến Binh Havoc để tấn công tối đa 3 lần, mỗi lần gây {0} Havoc DMG.
+          <t>Biến hình thành Chiến Binh Havoc để tấn công tối đa 3 lần, mỗi lần gây {0} Sát Thương Havoc.
 Hồi chiêu: {1}s</t>
         </is>
       </c>
@@ -23837,7 +23837,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>Biến thành Chiến Binh Havoc để liên tục gây Havoc DMG.</t>
+          <t>Biến hình thành Chiến Binh Havoc để liên tục gây Sát Thương Havoc.</t>
         </is>
       </c>
     </row>
@@ -23903,7 +23903,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Summon Glacio Predator phóng một ngọn giáo băng, gây {0} Glacio DMG khi trúng đích. Gây {1} Glacio DMG tối đa 10 lần trong thời gian nạp, và {2} Glacio DMG khi giáo nổ.
+          <t>Triệu hồi Glacio Predator phóng một ngọn giáo băng, gây {0} Sát Thương Glacio khi trúng đích. Gây {1} Sát Thương Glacio tối đa 10 lần trong thời gian nạp, và {2} Sát Thương Glacio khi giáo nổ.
 Hồi chiêu: {3} giây</t>
         </is>
       </c>
@@ -23969,7 +23969,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Summon Glacio Predator phóng ngọn giáo băng gây Glacio DMG.</t>
+          <t>Triệu hồi Glacio Predator phóng ngọn giáo băng gây Sát Thương Glacio.</t>
         </is>
       </c>
     </row>
@@ -24035,7 +24035,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>Summon Kẻ Săn Mồi Sét bắn kẻ địch 5 phát. 4 phát đầu gây {0} Sát Thương Sét, phát cuối gây {1} Sát Thương Sét.
+          <t>Triệu hồi Kẻ Săn Mồi Sét bắn kẻ địch 5 phát. 4 phát đầu gây {0} Sát Thương Sét, phát cuối gây {1} Sát Thương Sét.
 Hồi chiêu: {2} giây.</t>
         </is>
       </c>
@@ -24101,7 +24101,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>Summon Kẻ Săn Mồi Sét bắn mưa tên, gây Sát Thương Sét.</t>
+          <t>Triệu hồi Kẻ Săn Mồi Sét bắn mưa tên, gây Sát Thương Sét.</t>
         </is>
       </c>
     </row>
@@ -24167,7 +24167,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>Summon một Aero Predator phóng phi tiêu về phía trước. Phi tiêu sẽ nảy giữa các kẻ địch tối đa ba lần, mỗi lần trúng gây {0} Aero DMG.
+          <t>Triệu hồi một Aero Predator phóng phi tiêu về phía trước. Phi tiêu sẽ nảy giữa các kẻ địch tối đa ba lần, mỗi lần trúng gây {0} Sát Thương Aero.
 Hồi chiêu: {1} giây.</t>
         </is>
       </c>
@@ -24233,7 +24233,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>Summon Kẻ Săn Mồi Gió để gây Sát Thương Gió.</t>
+          <t>Triệu hồi Kẻ Săn Mồi Gió để gây Sát Thương Gió.</t>
         </is>
       </c>
     </row>
@@ -24299,7 +24299,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Biến thành Violet-Feathered Heron và vào tư thế Phản Đòn. Khi tư thế kết thúc, phản công gây {0} Electro DMG. Nếu bị tấn công trong tư thế Phản Đòn, có thể phản công sớm và hồi phục thêm {1} Concerto Energy.
+          <t>Biến thành Violet-Feathered Heron và vào tư thế Phản Đòn. Khi tư thế kết thúc, phản công gây {0} DMG Electro. Nếu bị tấn công trong tư thế Phản Đòn, có thể phản công sớm và hồi phục thêm {1} Concerto Energy.
 Hồi chiêu: {2} giây.</t>
         </is>
       </c>
@@ -24365,7 +24365,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Biến thành Violet-Feathered Heron để đỡ đòn tấn công của kẻ địch. Counterattack gây Electro DMG và hồi phục Concerto Energy.</t>
+          <t>Biến thành Violet-Feathered Heron để đỡ đòn tấn công của kẻ địch. Phản công gây DMG Electro và hồi phục Concerto Energy.</t>
         </is>
       </c>
     </row>
@@ -24431,7 +24431,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Biến thành Cyan-Feathered Heron và lao vào kẻ địch, gây {0} Aero DMG; Skills này sẽ làm gián đoạn &lt;color=Highlight&gt;Special Skills&lt;/color&gt; của kẻ địch khi gây sát thương.
+          <t>Biến hình thành Cyan-Feathered Heron và lao vào kẻ địch, gây {0} Sát Thương Aero; Kỹ Năng này sẽ làm gián đoạn &lt;color=Highlight&gt;Kỹ Năng Đặc Biệt&lt;/color&gt; của kẻ địch khi gây DMG.
 Hồi chiêu: {1}s</t>
         </is>
       </c>
@@ -24497,7 +24497,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>Biến thành Diệc Lông Lam, lao về phía kẻ địch, gây Aero DMG và làm gián đoạn &lt;color=Highlight&gt;Special Skill&lt;/color&gt; của chúng.</t>
+          <t>Biến hình thành Diệc Lông Lam, lao về phía kẻ địch, gây Sát Thương Aero và làm gián đoạn &lt;color=Highlight&gt;Kỹ Năng Đặc Biệt&lt;/color&gt; của chúng.</t>
         </is>
       </c>
     </row>
@@ -24563,7 +24563,7 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>Biến thành Flautist, liên tục phát ra các tia laser Electro, gây {0} Electro DMG tổng cộng 10 lần. Mỗi lần trúng đích sẽ hồi phục {1} Concerto Energy.
+          <t>Biến hình thành Flautist, liên tục phát ra các tia laser Electro, gây {0} Sát Thương Electro tổng cộng 10 lần. Mỗi lần trúng đích sẽ hồi phục {1} Concerto Energy.
 Hồi chiêu: {2} giây</t>
         </is>
       </c>
@@ -24629,7 +24629,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Biến thành Flautist để gây Electro DMG và hồi phục Concerto Energy khi trúng đích.</t>
+          <t>Biến hình thành Flautist để gây Sát Thương Electro và hồi phục Concerto Energy khi trúng đích.</t>
         </is>
       </c>
     </row>
@@ -24694,7 +24694,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Biến thành Rocksteady Guardian và bước vào Tư Thế Dodge Đòn. Counterattack khi bị trúng đòn &lt;color=Highlight&gt;Special Skill&lt;/color&gt; để làm gián đoạn &lt;color=Highlight&gt;Special Skills&lt;/color&gt; của kẻ địch và gây Spectro DMG dựa trên HP Tối Đa.</t>
+          <t>Biến hình thành Rocksteady Guardian và bước vào Tư Thế Né Đòn. Phản công khi bị trúng đòn &lt;color=Highlight&gt;Kỹ Năng Đặc Biệt&lt;/color&gt; để làm gián đoạn &lt;color=Highlight&gt;Kỹ Năng Đặc Biệt&lt;/color&gt; của kẻ địch và gây Sát Thương Spectro dựa trên HP Tối Đa.</t>
         </is>
       </c>
     </row>
@@ -24760,7 +24760,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>Biến thành Chasm Guardian để thực hiện Đòn Nhảy Tấn Công gây {0} Havoc DMG khi trúng đích. Resonator hiện tại mất {1} HP sau khi đòn đánh trúng. Định kỳ hồi phục HP cho Resonator hiện tại sau mỗi {2} giây, tối đa {3} HP tối đa.
+          <t>Biến hình thành Người Bảo Vệ Vực Sâu để thực hiện Đòn Nhảy Tấn Công gây {0} Sát Thương Havoc khi trúng đích. Cộng Hưởng Giả hiện tại mất {1} HP sau khi đòn đánh trúng. Định kỳ hồi phục HP cho Cộng Hưởng Giả hiện tại sau mỗi {2} giây, tối đa {3} HP tối đa.
 Hồi chiêu: {4} giây</t>
         </is>
       </c>
@@ -24826,7 +24826,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>Biến thành Chasm Guardian để thực hiện một đòn tấn công mạnh gây Havoc DMG. Mất một ít HP khi đánh trúng và sau đó hồi phục HP theo thời gian.</t>
+          <t>Biến hình thành Người Bảo Vệ Vực Sâu để thực hiện một đòn tấn công mạnh gây Sát Thương Havoc. Mất một ít HP khi đánh trúng và sau đó hồi phục HP theo thời gian.</t>
         </is>
       </c>
     </row>
@@ -24892,7 +24892,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>Summon Cruisewing hồi phục HP cho tất cả thành viên trong đội hiện tại bằng {0} HP tối đa cộng thêm {1} điểm HP, tối đa 4 lần.
+          <t>Triệu hồi Cruisewing hồi phục HP cho tất cả thành viên trong đội hiện tại bằng {0} HP tối đa cộng thêm {1} điểm HP, tối đa 4 lần.
 Hồi chiêu: {2} giây</t>
         </is>
       </c>
@@ -24959,7 +24959,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Summon Sabyr Boar húc tung kẻ địch lên không, gây {0} Sát Thương Physical.
+          <t>Triệu hồi Lợn Rừng Sabyr húc tung kẻ địch lên không, gây {0} Sát Thương Vật Lý.
 Hồi chiêu: {1} giây.</t>
         </is>
       </c>
@@ -25025,7 +25025,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>Summon Sabyr Boar lao tới và gây Sát Thương Physical.</t>
+          <t>Triệu hồi Lợn Rừng Sabyr lao tới và gây Sát Thương Vật Lý.</t>
         </is>
       </c>
     </row>
@@ -25091,7 +25091,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>Summon Gulpuff thổi bong bóng {0} times, mỗi lần gây {1} Glacio DMG.
+          <t>Triệu hồi Gulpuff thổi bong bóng {0} lần, mỗi lần gây {1} Sát Thương Glacio.
 Hồi chiêu: {2} giây</t>
         </is>
       </c>
@@ -25157,7 +25157,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>Summon Gulpuff thổi bong bóng gây Glacio DMG.</t>
+          <t>Triệu hồi Gulpuff thổi bong bóng gây Sát Thương Glacio.</t>
         </is>
       </c>
     </row>
@@ -25223,7 +25223,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>Summon một Chirpuff tự phồng lên và thổi ra một luồng gió mạnh về phía trước {0} times. Mỗi luồng gây {1} Aero DMG và đẩy lùi kẻ địch.
+          <t>Triệu hồi một Chirpuff tự phồng lên và thổi ra một luồng gió mạnh về phía trước {0} lần. Mỗi luồng gây {1} Sát Thương Aero và đẩy lùi kẻ địch.
 Hồi chiêu: {2} giây</t>
         </is>
       </c>
@@ -25289,7 +25289,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Summon một Chirpuff tạo ra luồng gió mạnh, gây Aero DMG và đẩy lùi kẻ địch.</t>
+          <t>Triệu hồi một Chirpuff tạo ra luồng gió mạnh, gây DMG Aero và đẩy lùi kẻ địch.</t>
         </is>
       </c>
     </row>
@@ -25355,7 +25355,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Biến thành Excarat và đào đất di chuyển. Trong trạng thái này, bạn có thể thay đổi hướng di chuyển và miễn nhiễm sát thương.
+          <t>Biến hình thành Excarat và đào đất di chuyển. Trong trạng thái này, bạn có thể thay đổi hướng di chuyển và miễn nhiễm sát thương.
 Hồi chiêu: {0} giây</t>
         </is>
       </c>
@@ -25421,7 +25421,7 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>Biến thành Excarat để di chuyển nhanh và miễn nhiễm sát thương.</t>
+          <t>Biến hình thành Excarat để di chuyển nhanh và miễn nhiễm sát thương.</t>
         </is>
       </c>
     </row>
@@ -25487,7 +25487,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Biến thành Khủng Long Lửa Xanh Nhỏ để nghỉ ngơi tại chỗ và từ từ hồi phục HP.
+          <t>Biến hình thành Khủng Long Lửa Xanh Nhỏ để nghỉ ngơi tại chỗ và từ từ hồi phục HP.
 Hồi chiêu: {0} giây</t>
         </is>
       </c>
@@ -25553,7 +25553,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>Biến thành Khủng Long Lửa Xanh Nhỏ, nghỉ ngơi tại chỗ để hồi phục HP.</t>
+          <t>Biến hình thành Khủng Long Lửa Xanh Nhỏ, nghỉ ngơi tại chỗ để hồi phục HP.</t>
         </is>
       </c>
     </row>
@@ -25619,7 +25619,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Summon Thằn Lằn Lửa Viridblaze phun lửa liên tục, gây {0} Fusion DMG 10 lần.
+          <t>Triệu hồi Thằn Lằn Lửa Viridblaze phun lửa liên tục, gây {0} Sát Thương Fusion 10 lần.
 Hồi chiêu: {1} giây</t>
         </is>
       </c>
@@ -25685,7 +25685,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>Summon Thằn Lằn Lửa Viridblaze phun lửa liên tục, gây Fusion DMG.</t>
+          <t>Triệu hồi Thằn Lằn Lửa Viridblaze phun lửa liên tục, gây Sát Thương Fusion.</t>
         </is>
       </c>
     </row>
@@ -25751,7 +25751,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Summon một Baby Roseshroom bắn tia laser, gây {0} Havoc DMG.
+          <t>Triệu hồi một Baby Roseshroom bắn tia laser, gây {0} Sát Thương Havoc.
 Hồi chiêu: {1} giây</t>
         </is>
       </c>
@@ -25817,7 +25817,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Summon một Baby Roseshroom bắn tia laser, gây Havoc DMG.</t>
+          <t>Triệu hồi một Baby Roseshroom bắn tia laser, gây Sát Thương Havoc.</t>
         </is>
       </c>
     </row>
@@ -25883,7 +25883,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Summon Roseshroom bắn tia laser, gây {1} Havoc DMG tối đa {0} times.
+          <t>Triệu hồi Nấm Hồng bắn tia laser, gây {1} Sát Thương Havoc tối đa {0} lần.
 Hồi chiêu: {2} giây</t>
         </is>
       </c>
@@ -25949,7 +25949,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>Summon Roseshroom bắn tia laser, gây Havoc DMG.</t>
+          <t>Triệu hồi Nấm Hồng bắn tia laser, gây Sát Thương Havoc.</t>
         </is>
       </c>
     </row>
@@ -26015,7 +26015,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>Biến thành Hoartoise và từ từ hồi phục HP. Sử dụng lại Kỹ Năng Echo để thoát khỏi trạng thái biến hình.
+          <t>Biến hình thành Hoartoise và từ từ hồi phục HP. Sử dụng lại Kỹ Năng Echo để thoát khỏi trạng thái biến hình.
 Hồi chiêu: {0}s</t>
         </is>
       </c>
@@ -26081,7 +26081,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Biến thành Hoartoise và từ từ phục hồi HP.</t>
+          <t>Biến hình thành Hoartoise và từ từ phục hồi HP.</t>
         </is>
       </c>
     </row>
@@ -26147,7 +26147,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Summon Spearback thực hiện 5 đòn tấn công liên tiếp. 4 đòn đầu gây {0} Sát Thương Physical, đòn cuối gây {1} Sát Thương Physical.
+          <t>Triệu hồi Spearback thực hiện 5 đòn tấn công liên tiếp. 4 đòn đầu gây {0} Sát Thương Vật Lý, đòn cuối gây {1} Sát Thương Vật Lý.
 Hồi chiêu: {2} giây.</t>
         </is>
       </c>
@@ -26213,7 +26213,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Summon Spearback thực hiện các đòn cào liên tục, gây Sát Thương Physical.</t>
+          <t>Triệu hồi Spearback thực hiện các đòn cào liên tục, gây Sát Thương Vật Lý.</t>
         </is>
       </c>
     </row>
@@ -26279,7 +26279,7 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>Biến thành Havoc Dreadmane để thực hiện tối đa 2 cú quất đuôi. Mỗi đòn gây {0} Havoc DMG và khi trúng mục tiêu sẽ gây thêm {1} Havoc DMG.
+          <t>Biến hình thành Havoc Dreadmane để thực hiện tối đa 2 cú quất đuôi. Mỗi đòn gây {0} Sát Thương Havoc và khi trúng mục tiêu sẽ gây thêm {1} Sát Thương Havoc.
 Hồi chiêu: {2} giây</t>
         </is>
       </c>
@@ -26345,7 +26345,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Biến thành Havoc Dreadmane để tung ra các cú quất đuôi, gây Havoc DMG.</t>
+          <t>Biến hình thành Havoc Dreadmane để tung ra các cú quất đuôi, gây Sát Thương Havoc.</t>
         </is>
       </c>
     </row>
@@ -26411,7 +26411,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Summon Dreadmane Hợp Thể tấn công kẻ địch dữ dội, gây {0} Sát Thương Hợp Thể.
+          <t>Triệu hồi Dreadmane Hợp Thể tấn công kẻ địch dữ dội, gây {0} Sát Thương Hợp Thể.
 Hồi chiêu: {1} giây</t>
         </is>
       </c>
@@ -26477,7 +26477,7 @@
       </c>
       <c r="M384" t="inlineStr">
         <is>
-          <t>Summon Dreadmane Hợp Thể tấn công kẻ địch dữ dội, gây Sát Thương Hợp Thể.</t>
+          <t>Triệu hồi Dreadmane Hợp Thể tấn công kẻ địch dữ dội, gây Sát Thương Hợp Thể.</t>
         </is>
       </c>
     </row>
@@ -26543,7 +26543,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>Biến thành Crystal Scorpion và vào trạng thái Dodge. Counterattack khi trạng thái Dodge kết thúc, gây {0} Sát Thương Physical.
+          <t>Biến hình thành Crystal Scorpion và vào trạng thái Né Tránh. Phản công khi trạng thái Né Tránh kết thúc, gây {0} Sát Thương Vật Lý.
 Hồi chiêu: {1}s</t>
         </is>
       </c>
@@ -26609,7 +26609,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>Biến thành Crystal Scorpion để vào tư thế Phòng Thủ. Counterattack gây Sát Thương Physical.</t>
+          <t>Biến hình thành Crystal Scorpion để vào tư thế Phòng Thủ. Phản công gây Sát Thương Vật Lý.</t>
         </is>
       </c>
     </row>
@@ -26675,7 +26675,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>Biến thành Hooscamp Flinger và lao vào kẻ địch, gây {0} Sát Thương Hệ Aero.
+          <t>Biến hình thành Hooscamp Flinger và lao vào kẻ địch, gây {0} Sát Thương Hệ Aero.
 Hồi chiêu: {1} giây</t>
         </is>
       </c>
@@ -26741,7 +26741,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>Biến thành Hooscamp Flinger và nhảy bổ, gây Sát Thương Hệ Aero.</t>
+          <t>Biến hình thành Hooscamp Flinger và nhảy bổ, gây Sát Thương Hệ Aero.</t>
         </is>
       </c>
     </row>
@@ -26807,7 +26807,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Biến thành Hoochief và quật kẻ địch, gây {0} Aero DMG.
+          <t>Biến hình thành Hoochief và quật kẻ địch, gây {0} Sát Thương Aero.
 Hồi chiêu: {1}s</t>
         </is>
       </c>
@@ -26873,7 +26873,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>Biến thành Hoochief để gây Sát Thương Hệ Aero.</t>
+          <t>Biến hình thành Hoochief để gây Sát Thương Hệ Aero.</t>
         </is>
       </c>
     </row>
@@ -26939,7 +26939,7 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>Biến thành Giáp Xoay để thực hiện đòn tấn công xoay tròn gây {0} Aero DMG, tiếp theo là một nhát chém gây {1} Aero DMG.
+          <t>Biến hình thành Giáp Xoay để thực hiện đòn tấn công xoay tròn gây {0} Sát Thương Aero, tiếp theo là một nhát chém gây {1} Sát Thương Aero.
 Hồi chiêu: {2} giây</t>
         </is>
       </c>
@@ -27005,7 +27005,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Biến thành Giáp Xoay để thực hiện các đòn tấn công xoay tròn, gây Aero DMG.</t>
+          <t>Biến hình thành Giáp Xoay để thực hiện các đòn tấn công xoay tròn, gây Sát Thương Aero.</t>
         </is>
       </c>
     </row>
@@ -27071,7 +27071,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>Biến thành Scout Tự Động, gây {0} Glacio DMG lên khu vực xung quanh và tạo tối đa 3 Bức Ice Wall để chặn địch.
+          <t>Biến hình thành Scout Tự Động, gây {0} Sát Thương Glacio lên khu vực xung quanh và tạo tối đa 3 Bức Tường Băng để chặn địch.
 Hồi chiêu: {1} giây</t>
         </is>
       </c>
@@ -27137,7 +27137,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Biến thành Autopuppet Scout để gây Glacio DMG cho kẻ địch xung quanh và tạo Bức Ice Wall.</t>
+          <t>Biến hình thành Autopuppet Scout để gây Sát Thương Glacio cho kẻ địch xung quanh và tạo Bức Tường Băng.</t>
         </is>
       </c>
     </row>
@@ -27203,7 +27203,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>Summon Đèn Giao Thông, khóa chân kẻ địch trong tối đa {0} giây. Hiệu ứng sẽ mất khi kẻ địch bị tấn công.
+          <t>Triệu hồi Đèn Giao Thông, khóa chân kẻ địch trong tối đa {0} giây. Hiệu ứng sẽ mất khi kẻ địch bị tấn công.
 Hồi chiêu: {1} giây</t>
         </is>
       </c>
@@ -27269,7 +27269,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>Summon Đèn Giao Thông để khóa chân kẻ địch.</t>
+          <t>Triệu hồi Đèn Giao Thông để khóa chân kẻ địch.</t>
         </is>
       </c>
     </row>
@@ -27335,7 +27335,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>Summon một Clang Bang bám theo kẻ địch và tự phát nổ, gây {0} Glacio DMG.
+          <t>Triệu hồi một Clang Bang bám theo kẻ địch và tự phát nổ, gây {0} DMG Glacio.
 Hồi chiêu: {1} giây.</t>
         </is>
       </c>
@@ -27401,7 +27401,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>Summon một Clang Bang bám theo kẻ địch và tự phát nổ, gây Glacio DMG.</t>
+          <t>Triệu hồi một Clang Bang bám theo kẻ địch và tự phát nổ, gây DMG Glacio.</t>
         </is>
       </c>
     </row>
@@ -27473,14 +27473,14 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Biến thành Twin Nova: Collapsar Blade để bắn liên tục vào kẻ địch trong 5 giây, mỗi đòn gây {0} Electro DMG.
-Resonator trang bị Echo này ở vị trí chính sẽ nhận thêm {6} Electro DMG Bonus và {7} Tăng Sát Thương Basic Attack.
+          <t>Biến hình thành Twin Nova: Collapsar Blade để bắn liên tục vào kẻ địch trong 5 giây, mỗi đòn gây {0} Sát Thương Electro.
+Resonator trang bị Echo này ở vị trí chính sẽ nhận thêm {6} Tăng Sát Thương Electro và {7} Tăng Sát Thương Basic Attack.
 Hồi chiêu: {11} giây.
 Nếu Twin Nova: Nebulous Cannon được trang bị ở vị trí khác trên Resonator:
 - Sử dụng Kỹ Năng Echo liên tiếp sẽ biến hình luân phiên giữa Collapsar Blade và Nebulous Cannon, và được tính là sử dụng Kỹ Năng Echo cùng tên.
-- Sát Thương gây ra bởi Twin Nova: Collapsar Blade sẽ chuyển thành Spectro DMG. Electro DMG Bonus từ việc trang bị ở vị trí chính sẽ chuyển thành Spectro DMG Bonus.
+- Sát Thương gây ra bởi Twin Nova: Collapsar Blade sẽ chuyển thành Sát Thương Spectro. Tăng Sát Thương Electro từ việc trang bị ở vị trí chính sẽ chuyển thành Tăng Sát Thương Spectro.
 - Thực hiện Basic Attack sẽ nhận &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=điểm P=điểm} Dyad Origins. Sử dụng Resonance Skill sẽ nhận &lt;SapTag=2&gt;{2}&lt;/SapTag&gt; {Cus:Sap,S=điểm P=điểm} Dyad Origins. Dyad Origins có thể tích lũy tối đa {3} lần và duy trì trong {4} giây. Mỗi điểm tăng {5} Sát Thương Kỹ Năng Echo, và toàn bộ điểm sẽ bị xóa sau khi Kỹ Năng Echo kết thúc.
-- Skill này có giới hạn tối đa {10} lần sử dụng. Ban đầu, kỹ năng có thể sử dụng {8} lần, và mỗi {9} giây sẽ hồi phục thêm 1 lần.</t>
+- Kỹ năng này có giới hạn tối đa {10} lần sử dụng. Ban đầu, kỹ năng có thể sử dụng {8} lần, và mỗi {9} giây sẽ hồi phục thêm 1 lần.</t>
         </is>
       </c>
     </row>
@@ -27547,9 +27547,9 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>Biến thành Twin Nova: Collapsar Blade để bắn vào kẻ địch, gây Electro DMG.
-Resonator trang bị Echo này ở vị trí chính sẽ nhận thêm Electro DMG Bonus và Basic Attack.
-Trang bị đồng thời Twin Nova: Nebulous Cannon sẽ kích hoạt hiệu ứng đặc biệt cho Kỹ Năng Echo.</t>
+          <t>Biến hình thành Twin Nova: Collapsar Blade to fire at enemies, dealing Electro DMG.
+The Resonator with this Echo equipped in the main slot gains Electro and Basic Attack Bonuses.
+Equipping Twin Nova: Nebulous Cannon at the same time grants special Echo Skill effects.</t>
         </is>
       </c>
     </row>
@@ -27621,14 +27621,14 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Biến thành Twin Nova: Nebulous Cannon để chém kẻ địch hai lần, mỗi đòn gây {0} Spectro DMG.
-Resonator trang bị Echo này ở vị trí chính sẽ nhận thêm {6} Spectro DMG Bonus và {7} Tăng Sát Thương Basic Attack.
+          <t>Biến hình thành Twin Nova: Nebulous Cannon để chém kẻ địch hai lần, mỗi đòn gây {0} Sát Thương Spectro.
+Resonator trang bị Echo này ở vị trí chính sẽ nhận thêm {6} Tăng Sát Thương Spectro và {7} Tăng Sát Thương Basic Attack.
 Hồi chiêu: {11} giây.
 Nếu Twin Nova: Collapsar Blade được trang bị ở vị trí khác trên Resonator:
 - Sử dụng Kỹ Năng Echo liên tiếp sẽ biến hình luân phiên giữa Nebulous Cannon và Collapsar Blade, và được tính là sử dụng Kỹ Năng Echo cùng tên. Tăng Sát Thương từ Echo ở vị trí chính không thay đổi.
-- Sát Thương gây ra bởi Twin Nova: Collapsar Blade sẽ chuyển thành Spectro DMG.
+- Sát Thương gây ra bởi Twin Nova: Collapsar Blade sẽ chuyển thành Sát Thương Spectro.
 - Thực hiện Basic Attack sẽ nhận &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=điểm P=điểm} Dyad Origins. Sử dụng Resonance Skill sẽ nhận &lt;SapTag=2&gt;{2}&lt;/SapTag&gt; {Cus:Sap,S=điểm P=điểm} Dyad Origins. Dyad Origins có thể tích lũy tối đa {3} lần và duy trì trong {4} giây. Mỗi điểm tăng {5} Sát Thương Kỹ Năng Echo, và toàn bộ điểm sẽ bị xóa sau khi Kỹ Năng Echo kết thúc.
-- Skill này có giới hạn tối đa {10} lần sử dụng. Ban đầu, kỹ năng có thể sử dụng {8} lần, và mỗi {9} giây sẽ hồi phục thêm 1 lần.</t>
+- Kỹ năng này có giới hạn tối đa {10} lần sử dụng. Ban đầu, kỹ năng có thể sử dụng {8} lần, và mỗi {9} giây sẽ hồi phục thêm 1 lần.</t>
         </is>
       </c>
     </row>
@@ -27695,9 +27695,9 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>Biến thành Twin Nova: Nebulous Cannon để phóng những lưỡi kiếm vào kẻ địch, gây Spectro DMG.
-Resonator trang bị Echo này ở vị trí chính sẽ nhận thêm Spectro DMG Bonus và Basic Attack.
-Trang bị đồng thời Twin Nova: Collapsar Blade sẽ kích hoạt hiệu ứng đặc biệt cho Kỹ Năng Echo.</t>
+          <t>Biến hình thành Twin Nova: Nebulous Cannon to launch slashes at enemies, dealing Spectro DMG.
+The Resonator with this Echo equipped in the main slot gains Spectro and Basic Attack Bonuses.
+Equipping Twin Nova: Collapsar Blade at the same time grants special Echo Skill effects.</t>
         </is>
       </c>
     </row>
@@ -27763,7 +27763,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Summon Flora Reindeer tấn công kẻ địch trong phạm vi lớn, gây {0} Aero DMG.
+          <t>Triệu hồi Flora Reindeer tấn công kẻ địch trong phạm vi lớn, gây {0} Sát Thương Aero.
 Hồi chiêu: {1} giây.</t>
         </is>
       </c>
@@ -27829,7 +27829,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>Summon Flora Reindeer tấn công kẻ địch, gây Aero DMG.</t>
+          <t>Triệu hồi Flora Reindeer tấn công kẻ địch, gây Sát Thương Aero.</t>
         </is>
       </c>
     </row>
@@ -27895,7 +27895,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>Summon Mining Reindeer phóng một đòn tấn công tích năng vào kẻ địch, gây {0} Electro DMG.
+          <t>Triệu hồi Tuần Lộc Khai Thác phóng một đòn tấn công tích năng vào kẻ địch, gây {0} DMG Electro.
 Hồi chiêu: {1} giây.</t>
         </is>
       </c>
@@ -27961,7 +27961,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>Summon Mining Reindeer tấn công kẻ địch, gây Electro DMG.</t>
+          <t>Triệu hồi Tuần Lộc Khai Thác tấn công kẻ địch, gây DMG Electro.</t>
         </is>
       </c>
     </row>
@@ -28027,7 +28027,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>Summon Spacetrek Explorer để tạo Shield cho Resonators trong đội ở gần, tương đương {0} HP tối đa của người triệu hồi, kéo dài {1} giây.
+          <t>Triệu hồi Spacetrek Explorer để tạo Khiên cho các Resonator trong đội ở gần, tương đương {0} HP tối đa của người triệu hồi, kéo dài {1} giây.
 Hồi chiêu: {2} giây.</t>
         </is>
       </c>
@@ -28094,7 +28094,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>Summon Mãnh Hổ Sabercat tấn công kẻ địch, gây {0} Fusion DMG.
+          <t>Triệu hồi Mãnh Hổ Sabercat tấn công kẻ địch, gây {0} Sát Thương Fusion.
 Hồi chiêu: {1} giây.</t>
         </is>
       </c>
@@ -28160,7 +28160,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>Summon Mãnh Hổ Sabercat tấn công kẻ địch, gây Fusion DMG.</t>
+          <t>Triệu hồi Mãnh Hổ Sabercat tấn công kẻ địch, gây Sát Thương Fusion.</t>
         </is>
       </c>
     </row>
@@ -28226,7 +28226,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>Summon Mãnh Hổ Sabercat bắn chùm tia vào kẻ địch, gây {0} Havoc DMG.
+          <t>Triệu hồi Mãnh Hổ Sabercat bắn chùm tia vào kẻ địch, gây {0} Sát Thương Havoc.
 Hồi chiêu: {1} giây.</t>
         </is>
       </c>
@@ -28292,7 +28292,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>Summon Mãnh Hổ Sabercat tấn công kẻ địch, gây Havoc DMG.</t>
+          <t>Triệu hồi Mãnh Hổ Sabercat tấn công kẻ địch, gây Sát Thương Havoc.</t>
         </is>
       </c>
     </row>
@@ -28358,7 +28358,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>Summon Frostbite Coleoid đấm kẻ địch, gây {0} Glacio DMG.
+          <t>Triệu hồi Frostbite Coleoid đấm kẻ địch, gây {0} Sát Thương Glacio.
 Hồi chiêu: {1} giây.</t>
         </is>
       </c>
@@ -28424,7 +28424,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>Summon Frostbite Coleoid đấm kẻ địch, gây Glacio DMG.</t>
+          <t>Triệu hồi Frostbite Coleoid đấm kẻ địch, gây Sát Thương Glacio.</t>
         </is>
       </c>
     </row>
@@ -28490,7 +28490,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Biến thành Windlash Coleoid để đá vào kẻ địch, gây {0} Aero DMG.
+          <t>Biến hình thành Windlash Coleoid để đá vào kẻ địch, gây {0} Sát Thương Aero.
 Hồi chiêu: {1} giây.</t>
         </is>
       </c>
@@ -28556,7 +28556,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>Biến thành Windlash Coleoid để đá vào kẻ địch, gây Aero DMG.</t>
+          <t>Biến hình thành Windlash Coleoid để đá vào kẻ địch, gây Sát Thương Aero.</t>
         </is>
       </c>
     </row>
@@ -28622,7 +28622,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>Summon Flora Drone, gây {0} Aero DMG lên kẻ địch và hồi phục Resonators trong phạm vi {1} HP tối đa cộng thêm {2} HP.
+          <t>Triệu hồi Flora Drone, gây {0} Sát Thương Aero lên kẻ địch và hồi phục Resonator trong phạm vi {1} HP tối đa cộng thêm {2} HP.
 Hồi chiêu: {3} giây</t>
         </is>
       </c>
@@ -28688,7 +28688,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>Summon Flora Drone, gây Aero DMG lên kẻ địch và hồi phục Resonators.</t>
+          <t>Triệu hồi Flora Drone, gây Sát Thương Aero lên kẻ địch và hồi phục Resonator.</t>
         </is>
       </c>
     </row>
@@ -28754,7 +28754,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>Biến thành Mining Drone để tấn công kẻ địch, gây {0} Havoc DMG hai lần.
+          <t>Biến hình thành Mining Drone để tấn công kẻ địch, gây {0} Sát Thương Havoc hai lần.
 Hồi chiêu: {1} giây.</t>
         </is>
       </c>
@@ -28820,7 +28820,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>Biến thành Mining Drone để tấn công kẻ địch, gây Havoc DMG.</t>
+          <t>Biến hình thành Mining Drone để tấn công kẻ địch, gây Sát Thương Havoc.</t>
         </is>
       </c>
     </row>
@@ -28886,7 +28886,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>Summon Geospider S4 tấn công kẻ địch, gây {0} Spectro DMG một lần và {1} Spectro DMG một lần nữa.
+          <t>Triệu hồi Geospider S4 tấn công kẻ địch, gây {0} Sát Thương Spectro một lần và {1} Sát Thương Spectro một lần nữa.
 Hồi chiêu: {2} giây.</t>
         </is>
       </c>
@@ -28952,7 +28952,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Summon Geospider S4 tấn công kẻ địch, gây Spectro DMG.</t>
+          <t>Triệu hồi Geospider S4 tấn công kẻ địch, gây Sát Thương Spectro.</t>
         </is>
       </c>
     </row>
@@ -29019,7 +29019,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>Biến thành Reactor Husk, bật lên không trung và giáng một nhát chém mạnh gây {0} Fusion DMG cho kẻ địch.
+          <t>Biến hình thành Reactor Husk, bật lên không trung và giáng một nhát chém mạnh gây {0} Sát Thương Fusion cho kẻ địch.
 Resonator trang bị Echo này ở vị trí chính sẽ được phục hồi {1} Năng Lượng.
 Hồi chiêu: {4} giây.</t>
         </is>
@@ -29087,7 +29087,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Biến thành Reactor Husk để tấn công kẻ địch, gây Fusion DMG.
+          <t>Biến hình thành Reactor Husk để tấn công kẻ địch, gây Sát Thương Fusion.
 Resonator trang bị Echo này ở vị trí chính sẽ được phục hồi Năng Lượng.</t>
         </is>
       </c>
@@ -29154,7 +29154,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>Biến thành Kronablight, bay lên không trung và lao xuống gây {0} Electro DMG cho kẻ địch.
+          <t>Biến hình thành Kronablight, bay lên không trung và lao xuống gây {0} Sát Thương Electro cho kẻ địch.
 Hồi chiêu: {1} giây</t>
         </is>
       </c>
@@ -29220,7 +29220,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>Biến thành Kronablight để tấn công kẻ địch, gây Electro DMG.</t>
+          <t>Biến hình thành Kronablight để tấn công kẻ địch, gây Sát Thương Electro.</t>
         </is>
       </c>
     </row>
@@ -29286,7 +29286,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Biến thành Kronaclaw và bay lên không trung để gây {0} Aero DMG tối đa 8 lần và {1} Aero DMG 2 lần, sau đó lao xuống gây {2} Aero DMG 1 lần.
+          <t>Biến hình thành Kronaclaw và bay lên không trung để gây {0} Sát Thương Aero tối đa 8 lần và {1} Sát Thương Aero 2 lần, sau đó lao xuống gây {2} Sát Thương Aero 1 lần.
 Hồi chiêu: {3} giây</t>
         </is>
       </c>
@@ -29352,7 +29352,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>Biến thành Kronaclaw để tấn công kẻ địch, gây Aero DMG.</t>
+          <t>Biến hình thành Kronaclaw để tấn công kẻ địch, gây Sát Thương Aero.</t>
         </is>
       </c>
     </row>
@@ -29419,8 +29419,8 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>Summon Glommoth giẫm nát kẻ địch, gây {0} Glacio DMG.
-Dùng Outro Skill trong {1} giây sau khi triệu hồi Glommoth sẽ tăng {2} Glacio DMG cho Resonator kế tiếp trong {3} giây.
+          <t>Triệu hồi Glommoth giẫm nát kẻ địch, gây {0} Sát Thương Glacio.
+Dùng Kỹ Năng Outro trong {1} giây sau khi triệu hồi Glommoth sẽ tăng {2} Sát Thương Glacio cho Resonator kế tiếp trong {3} giây.
 Hồi chiêu: {4} giây.</t>
         </is>
       </c>
@@ -29486,7 +29486,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>Summon Glommoth tấn công kẻ địch, gây Glacio DMG và tăng Glacio DMG cho Resonator kế tiếp.</t>
+          <t>Triệu hồi Glommoth tấn công kẻ địch, gây Sát Thương Glacio và tăng Sát Thương Glacio cho Resonator kế tiếp.</t>
         </is>
       </c>
     </row>
@@ -29552,7 +29552,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Biến thành Iceglint Dancer để tấn công kẻ địch, gây {0} Glacio DMG.
+          <t>Biến hình thành Iceglint Dancer để tấn công kẻ địch, gây {0} Sát Thương Glacio.
 Hồi chiêu: {1} giây.</t>
         </is>
       </c>
@@ -29618,7 +29618,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Biến thành Iceglint Dancer để tấn công kẻ địch, gây Glacio DMG.</t>
+          <t>Biến hình thành Iceglint Dancer để tấn công kẻ địch, gây Sát Thương Glacio.</t>
         </is>
       </c>
     </row>
@@ -29684,7 +29684,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Summon Shadow Stepper tấn công kẻ địch, gây {0} Havoc DMG.
+          <t>Triệu hồi Shadow Stepper tấn công kẻ địch, gây {0} Sát Thương Havoc.
 Hồi chiêu: {1} giây.</t>
         </is>
       </c>
@@ -29750,7 +29750,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>Summon Shadow Stepper tấn công kẻ địch, gây Havoc DMG.</t>
+          <t>Triệu hồi Shadow Stepper tấn công kẻ địch, gây Sát Thương Havoc.</t>
         </is>
       </c>
     </row>
@@ -29817,8 +29817,8 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>Summon Hyvatia bắn tia laser từ trên không vào kẻ địch, gây {0} Spectro DMG 10 lần.
-Sử dụng Outro Skill trong vòng {1} giây sau khi triệu hồi Hyvatia sẽ tăng {2} Sát Thương Toàn Thuộc Tính cho Resonator kế tiếp sử dụng Intro Skill trong {3} giây.
+          <t>Triệu hồi Hyvatia bắn tia laser từ trên không vào kẻ địch, gây {0} DMG Spectro 10 lần.
+Sử dụng Kỹ Năng Outro trong vòng {1} giây sau khi triệu hồi Hyvatia sẽ tăng {2} Sát Thương Toàn Thuộc Tính cho Resonator kế tiếp sử dụng Kỹ Năng Intro trong {3} giây.
 Hồi chiêu: {4} giây.</t>
         </is>
       </c>
@@ -29884,7 +29884,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Summon Hyvatia tấn công kẻ địch, gây Spectro DMG và tăng Sát Thương Toàn Thuộc Tính cho Resonator kế tiếp sử dụng Intro Skill.</t>
+          <t>Triệu hồi Hyvatia tấn công kẻ địch, gây DMG Spectro và tăng Sát Thương Toàn Thuộc Tính cho Resonator kế tiếp sử dụng Kỹ Năng Intro.</t>
         </is>
       </c>
     </row>
@@ -29951,8 +29951,8 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>Summon Sigillum tung ra hai đòn tấn công, lần lượt gây {0} và {1} Fusion DMG.
-Khi Aemeath trang bị ở vị trí chính, cộng thêm {2} Tăng Sát Thương Giải Phóng Echo.
+          <t>Triệu hồi Sigillum tung ra hai đòn tấn công, lần lượt gây {0} và {1} Sát Thương Fusion.
+Khi Aemeath trang bị ở vị trí chính, cộng thêm {2} Tăng Sát Thương Giải Phóng Tiếng Vang.
 Hồi chiêu: {3} giây.</t>
         </is>
       </c>
@@ -30019,8 +30019,8 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Summon Sigillum tấn công kẻ địch, gây Fusion DMG.
-Khi Aemeath trang bị ở vị trí chính, cộng thêm Tăng Sát Thương Giải Phóng Echo.</t>
+          <t>Triệu hồi Sigillum tấn công kẻ địch, gây Sát Thương Fusion.
+Khi Aemeath trang bị ở vị trí chính, cộng thêm Tăng Sát Thương Giải Phóng Tiếng Vang.</t>
         </is>
       </c>
     </row>
@@ -30087,8 +30087,8 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Summon Nameless Explorer tấn công kẻ địch trên đường đi, gây {0} Aero DMG.
-Resonator trang bị Echo này ở vị trí chính sẽ nhận thêm {1} Aero DMG Bonus và {2} Tăng Sát Thương Kỹ Năng Echo.
+          <t>Triệu hồi Nhà Thám Hiểm Vô Danh tấn công kẻ địch trên đường đi, gây {0} Sát Thương Aero.
+Resonator trang bị Echo này ở vị trí chính sẽ nhận thêm {1} Tăng Sát Thương Aero và {2} Tăng Sát Thương Kỹ Năng Echo.
 Hồi chiêu: {3} giây.</t>
         </is>
       </c>
@@ -30155,8 +30155,8 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>Summon Nameless Explorer tấn công kẻ địch, gây Aero DMG.
-Resonator trang bị Echo này ở vị trí chính sẽ nhận thêm Aero DMG Bonus và Tăng Sát Thương Kỹ Năng Echo.</t>
+          <t>Triệu hồi Nhà Thám Hiểm Vô Danh tấn công kẻ địch, gây Sát Thương Aero.
+Resonator trang bị Echo này ở vị trí chính sẽ nhận thêm Tăng Sát Thương Aero và Tăng Sát Thương Kỹ Năng Echo.</t>
         </is>
       </c>
     </row>
@@ -30222,7 +30222,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>Biến thành Tremor Warrior và tấn công dữ dội kẻ địch phía trước, gây {0} Electro DMG.
+          <t>Biến hình thành Tremor Warrior và tấn công dữ dội kẻ địch phía trước, gây {0} Sát Thương Electro.
 Hồi chiêu: {1} giây.</t>
         </is>
       </c>
@@ -30288,7 +30288,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>Biến thành Tremor Warrior để tấn công kẻ địch, gây Electro DMG.</t>
+          <t>Biến hình thành Tremor Warrior để tấn công kẻ địch, gây Sát Thương Electro.</t>
         </is>
       </c>
     </row>
@@ -30354,7 +30354,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>Summon Zip Zap phóng ra các đòn xoay tấn công kẻ địch, gây {0} Electro DMG 5 lần.
+          <t>Triệu hồi Zip Zap phóng ra các đòn xoay tấn công kẻ địch, gây {0} Sát Thương Electro 5 lần.
 Hồi chiêu: {1} giây.</t>
         </is>
       </c>
@@ -30420,7 +30420,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Summon Zip Zap tấn công kẻ địch, gây Electro DMG.</t>
+          <t>Triệu hồi Zip Zap tấn công kẻ địch, gây Sát Thương Electro.</t>
         </is>
       </c>
     </row>
@@ -30486,7 +30486,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>Biến thành Ironhoof và xông thẳng vào kẻ địch, gây {0} Fusion DMG. Khi kết thúc đòn lao tới, tung ra đòn húc gây {1} Fusion DMG 3 lần và {2} Fusion DMG 1 lần.
+          <t>Biến hình thành Ironhoof và xông thẳng vào kẻ địch, gây {0} Sát Thương Fusion. Khi kết thúc đòn lao tới, tung ra đòn húc gây {1} Sát Thương Fusion 3 lần và {2} Sát Thương Fusion 1 lần.
 Hồi chiêu: {3} giây.</t>
         </is>
       </c>
@@ -30552,7 +30552,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>Biến thành Ironhoof và xông thẳng vào kẻ địch, gây Fusion DMG.</t>
+          <t>Biến hình thành Ironhoof và xông thẳng vào kẻ địch, gây Sát Thương Fusion.</t>
         </is>
       </c>
     </row>
@@ -30620,8 +30620,8 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>Biến thành Kẻ Giả Mạo Quân Chủ và lao tới trong đòn xoay tấn công, gây {0} Electro DMG 4 lần.
-Resonator gắn Echo này ở vị trí chính sẽ nhận {1} Electro DMG Bonus và {2} Tăng Sát Thương Heavy Attack. Khi kích hoạt Intro Skill, Kẻ Giả Mạo Quân Chủ cũng được triệu hồi để gây {3} Electro DMG.
+          <t>Biến hình thành Kẻ Giả Mạo Quân Chủ và lao tới trong đòn xoay tấn công, gây {0} Sát Thương Electro 4 lần.
+Resonator gắn Echo này ở vị trí chính sẽ nhận {1} Tăng Sát Thương Electro và {2} Tăng Sát Thương Đòn Nặng. Khi kích hoạt Kỹ Năng Khởi Động, Kẻ Giả Mạo Quân Chủ cũng được triệu hồi để gây {3} Sát Thương Electro.
 Bắt đầu với {4} lần tích năng. Mỗi {5} giây tích được 1 lần, tối đa {6} lần.
 Hồi chiêu: {7} giây.</t>
         </is>
@@ -30689,8 +30689,8 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Biến thành Kẻ Giả Mạo Quân Chủ để tấn công kẻ địch xung quanh, gây Electro DMG.
-Resonator gắn Echo này ở vị trí chính sẽ nhận Electro DMG Bonus và Heavy Attack. Khi kích hoạt Intro Skill, triệu hồi Kẻ Giả Mạo Quân Chủ để gây Electro DMG.</t>
+          <t>Biến hình thành Kẻ Giả Mạo Quân Chủ để tấn công kẻ địch xung quanh, gây Sát Thương Electro.
+Resonator gắn Echo này ở vị trí chính sẽ nhận Tăng Sát Thương Electro và Đòn Nặng. Khi kích hoạt Kỹ Năng Khởi Động, triệu hồi Kẻ Giả Mạo Quân Chủ để gây Sát Thương Electro.</t>
         </is>
       </c>
     </row>
@@ -30757,7 +30757,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Summon Bão Thủy Triều tấn công kẻ địch 10 lần gây {0} Sát Thương Phong và 1 lần gây {1} Sát Thương Phong.
+          <t>Triệu hồi Bão Thủy Triều tấn công kẻ địch 10 lần gây {0} Sát Thương Phong và 1 lần gây {1} Sát Thương Phong.
 Resonator trang bị Echo này ở vị trí chính sẽ nhận thêm {2} Tăng Sát Thương Phong và {3} Tăng Sát Thương Resonance Liberation.
 Hồi chiêu: {4} giây</t>
         </is>
@@ -30825,7 +30825,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>Summon Bão Thủy Triều gây Sát Thương Phong gây cho kẻ địch.
+          <t>Triệu hồi Bão Thủy Triều gây Sát Thương Phong gây cho kẻ địch.
 Resonator trang bị Echo này ở vị trí chính sẽ nhận thêm Tăng Sát Thương Phong và Tăng Sát Thương Resonance Liberation.</t>
         </is>
       </c>
@@ -30893,7 +30893,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Summon Corrosaurus tấn công kẻ địch, gây {0} Sát Thương Dung Hợp.
+          <t>Triệu hồi Corrosaurus tấn công kẻ địch, gây {0} Sát Thương Dung Hợp.
 Resonator trang bị Echo này ở vị trí chính sẽ nhận được {1} Tăng Sát Thương Dung Hợp và {2} Tăng Sát Thương Kỹ Năng Echo.
 Hồi chiêu: {3} giây</t>
         </is>
@@ -30961,7 +30961,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Summon Corrosaurus gây Sát Thương Dung Hợp lên kẻ địch.
+          <t>Triệu hồi Corrosaurus gây Sát Thương Dung Hợp lên kẻ địch.
 Resonator trang bị Echo này ở vị trí chính sẽ nhận được Tăng Sát Thương Dung Hợp và Kỹ Năng Echo.</t>
         </is>
       </c>
@@ -31030,8 +31030,8 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>Summon Chân Trời Sụp Đổ, gây {0} Sát Thương Hỗn Loạn hai lần lên kẻ địch xung quanh và nhận được Core Sụp Đổ trong {1} giây.
-Trong thời gian tồn tại, Core Sụp Đổ gây {2} Sát Thương Hỗn Loạn mỗi khi Resonator trong đội gây sát thương. Hiệu ứng này có thể kích hoạt mỗi {4} giây, tối đa &lt;SapTag=3&gt;{3}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=3}. Kẻ địch mang Ác Tính Hỗn Loạn sẽ chịu thêm {5} sát thương từ hiệu ứng này.
+          <t>Triệu hồi Chân Trời Sụp Đổ, gây {0} Sát Thương Hỗn Loạn hai lần lên kẻ địch xung quanh và nhận được Lõi Sụp Đổ trong {1} giây.
+Trong thời gian tồn tại, Lõi Sụp Đổ gây {2} Sát Thương Hỗn Loạn mỗi khi Resonator trong đội gây DMG. Hiệu ứng này có thể kích hoạt mỗi {4} giây, tối đa &lt;SapTag=3&gt;{3}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=3}. Kẻ địch mang Ác Tính Hỗn Loạn sẽ chịu thêm {5} DMG từ hiệu ứng này.
 Resonator trang bị Echo này ở vị trí chính sẽ nhận được {6} Tăng Sát Thương Hỗn Loạn và {7} Tăng Sát Thương Resonance Liberation.
 Hồi chiêu: {8} giây</t>
         </is>
@@ -31099,8 +31099,8 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Summon Chân Trời Sụp Đổ, gây Sát Thương Hỗn Loạn. Resonators trong đội sẽ gây thêm Sát Thương Hỗn Loạn khi tấn công kẻ địch.
-Resonators trang bị Echo này ở vị trí chính sẽ gây nhiều Sát Thương Hỗn Loạn và Sát Thương Resonance Liberation hơn.</t>
+          <t>Triệu hồi Chân Trời Sụp Đổ, gây Sát Thương Hỗn Loạn. Resonator trong đội sẽ gây thêm Sát Thương Hỗn Loạn khi tấn công kẻ địch.
+Resonator trang bị Echo này ở vị trí chính sẽ gây nhiều Sát Thương Hỗn Loạn và Sát Thương Resonance Liberation hơn.</t>
         </is>
       </c>
     </row>
@@ -31312,20 +31312,20 @@
         <is>
           <t>&lt;size=40&gt;&lt;color=Title&gt;Basic Attack&lt;/color&gt;&lt;/size&gt;
 Thực hiện tối đa 4 đòn tấn công liên tiếp, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;. Sát thương từ Basic Attack Stage 1-3 được tính là &lt;color=Highlight&gt;Heavy Attack DMG&lt;/color&gt;, còn Basic Attack Stage 4 là &lt;color=Highlight&gt;Echo Skill DMG&lt;/color&gt;.
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack ngay sau khi thực hiện &lt;color=Highlight&gt;Basic Attack Stage 4&lt;/color&gt; để thực hiện &lt;color=Highlight&gt;Basic Attack Stage 2&lt;/color&gt;.
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Normal Attack ngay sau khi thực hiện &lt;color=Highlight&gt;Basic Attack Stage 4&lt;/color&gt; để thực hiện &lt;color=Highlight&gt;Basic Attack Stage 2&lt;/color&gt;.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Heavy Attack - Volley of Death&lt;/color&gt;&lt;/size&gt;
 Tiêu hao STA để tấn công mục tiêu và thực hiện tối đa 3 đòn liên tiếp, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;. Sát thương Stage 3 được tính là &lt;color=Highlight&gt;Echo Skill DMG&lt;/color&gt;.
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack ngay sau khi thực hiện &lt;color=Highlight&gt;Heavy Attack - Volley of Death Stage 1&lt;/color&gt; để thực hiện &lt;color=Highlight&gt;Basic Attack Stage 2&lt;/color&gt;. {Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack ngay sau khi thực hiện &lt;color=Highlight&gt;Heavy Attack - Volley of Death Stage 2 or 3&lt;/color&gt; để thực hiện &lt;color=Highlight&gt;Basic Attack Stage 3&lt;/color&gt;.
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Normal Attack ngay sau khi thực hiện &lt;color=Highlight&gt;Heavy Attack - Volley of Death Stage 1&lt;/color&gt; để thực hiện &lt;color=Highlight&gt;Basic Attack Stage 2&lt;/color&gt;. {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Normal Attack ngay sau khi thực hiện &lt;color=Highlight&gt;Heavy Attack - Volley of Death Stage 2 or 3&lt;/color&gt; để thực hiện &lt;color=Highlight&gt;Basic Attack Stage 3&lt;/color&gt;.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Mid-air Attack - Ashfall Barrage&lt;/color&gt;&lt;/size&gt;
-Khi ở trên không, {Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack để tiêu hao STA và thực hiện Đòn Lao Xuống, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;, được tính là &lt;color=Highlight&gt;Heavy Attack DMG&lt;/color&gt;.
+Khi ở trên không, {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Normal Attack để tiêu hao STA và thực hiện Đòn Lao Xuống, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;, được tính là &lt;color=Highlight&gt;Heavy Attack DMG&lt;/color&gt;.
 Khi ở trên không, giữ Normal Attack để liên tục tiêu hao STA và bắn loạt đạn xuống mục tiêu bên dưới, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;, được tính là &lt;color=Highlight&gt;Heavy Attack DMG&lt;/color&gt;. Nếu Galbrena chưa tiếp đất khi bị gián đoạn trong loạt đạn, cô không thể sử dụng kỹ năng này ngay lập tức. Thả Normal Attack trong loạt đạn để thực hiện Đòn Lao Xuống.
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack ngay sau khi thực hiện Đòn Lao Xuống để thực hiện &lt;color=Highlight&gt;Basic Attack Stage 3&lt;/color&gt;.
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Normal Attack ngay sau khi thực hiện Đòn Lao Xuống để thực hiện &lt;color=Highlight&gt;Basic Attack Stage 3&lt;/color&gt;.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Dodge Counter - Blood for Blood&lt;/color&gt;&lt;/size&gt;
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack ngay sau khi Dodge thành công để tấn công mục tiêu, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;, được tính là &lt;color=Highlight&gt;Heavy Attack DMG&lt;/color&gt;.
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack ngay sau khi sử dụng kỹ năng này để thực hiện &lt;color=Highlight&gt;Basic Attack Stage 4&lt;/color&gt;.</t>
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Normal Attack ngay sau khi Dodge thành công để tấn công mục tiêu, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;, được tính là &lt;color=Highlight&gt;Heavy Attack DMG&lt;/color&gt;.
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Normal Attack ngay sau khi sử dụng kỹ năng này để thực hiện &lt;color=Highlight&gt;Basic Attack Stage 4&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -31409,11 +31409,11 @@
 Tiêu hao STA để gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Mid-air Attack&lt;/color&gt;&lt;/size&gt;
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack để tiêu hao STA thực hiện Đòn Hạ Gục khi đang ở trên không, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Normal Attack để tiêu hao STA thực hiện Đòn Hạ Gục khi đang ở trên không, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
 Giữ Normal Attack để liên tục tiêu hao STA bắn loạt đạn xuống mục tiêu bên dưới, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Dodge Counter&lt;/color&gt;&lt;/size&gt;
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack ngay sau khi Dodge thành công để tấn công mục tiêu, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Normal Attack ngay sau khi Dodge thành công để tấn công mục tiêu, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
 &lt;size=10&gt;&lt;/size&gt;</t>
         </is>
       </c>
@@ -31642,7 +31642,7 @@
       <c r="M460" t="inlineStr">
         <is>
           <t>Tấn công mục tiêu và gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;, được tính là &lt;color=Highlight&gt;Echo Skill DMG&lt;/color&gt;. Trong trạng thái &lt;color=Highlight&gt;&lt;te href=120805&gt;Basic Attack - Seraphic Execution&lt;/te&gt;&lt;/color&gt;, nhận tăng {0} Hệ Số Sát Thương cho &lt;color=Highlight&gt;Heavy Attack - Flamewing Verdict&lt;/color&gt;, &lt;color=Highlight&gt;Mid-air Attack - Hellsent Barrage&lt;/color&gt;, &lt;color=Highlight&gt;Dodge Counter - Purgatory Scourge&lt;/color&gt; và &lt;color=Highlight&gt;Demon Hypostasis&lt;/color&gt; trong {1} giây.
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack sau khi kích hoạt Resonance Liberation để thực hiện &lt;color=Highlight&gt;Basic Attack Stage 2&lt;/color&gt;. Trong trạng thái &lt;color=Highlight&gt;&lt;te href=120805&gt;Demon Hypostasis&lt;/te&gt;&lt;/color&gt;, thay vào đó sẽ thực hiện &lt;color=Highlight&gt;Basic Attack - Seraphic Execution Stage 2&lt;/color&gt;.
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Normal Attack sau khi kích hoạt Resonance Liberation để thực hiện &lt;color=Highlight&gt;Basic Attack Stage 2&lt;/color&gt;. Trong trạng thái &lt;color=Highlight&gt;&lt;te href=120805&gt;Demon Hypostasis&lt;/te&gt;&lt;/color&gt;, thay vào đó sẽ thực hiện &lt;color=Highlight&gt;Basic Attack - Seraphic Execution Stage 2&lt;/color&gt;.
 Có thể kích hoạt khi đang ở gần mặt đất giữa không trung.</t>
         </is>
       </c>
@@ -32039,7 +32039,7 @@
         <is>
           <t>Tấn công mục tiêu và gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
 Giữ Normal Attack sau khi kích hoạt kỹ năng này để thực hiện &lt;color=Highlight&gt;Heavy Attack - Volley of Death Stage 2&lt;/color&gt;. Trong trạng thái &lt;color=Highlight&gt;&lt;te href=120805&gt;Demon Hypostasis&lt;/te&gt;&lt;/color&gt;, thay vào đó sẽ thực hiện &lt;color=Highlight&gt;Heavy Attack - Flamewing Verdict Stage 2&lt;/color&gt;.
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack ngay sau khi kích hoạt kỹ năng này để thực hiện &lt;color=Highlight&gt;Basic Attack Stage 2&lt;/color&gt;, sẽ được thay thế bằng &lt;color=Highlight&gt;Basic Attack - Seraphic Execution Stage 2&lt;/color&gt; nếu Galbrena đang ở trạng thái &lt;color=Highlight&gt;&lt;te href=120805&gt;Demon Hypostasis&lt;/te&gt;&lt;/color&gt;.</t>
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Normal Attack ngay sau khi kích hoạt kỹ năng này để thực hiện &lt;color=Highlight&gt;Basic Attack Stage 2&lt;/color&gt;, sẽ được thay thế bằng &lt;color=Highlight&gt;Basic Attack - Seraphic Execution Stage 2&lt;/color&gt; nếu Galbrena đang ở trạng thái &lt;color=Highlight&gt;&lt;te href=120805&gt;Demon Hypostasis&lt;/te&gt;&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -32222,27 +32222,27 @@
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Basic Attack - Seraphic Execution&lt;/color&gt;&lt;/size&gt;
 Thực hiện tối đa 5 đòn tấn công liên tiếp, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;. Tiêu hao &lt;color=Highlight&gt;&lt;te href=120803&gt;Purging Flame&lt;/te&gt;&lt;/color&gt; khi trúng đích. Sát thương từ Giai đoạn 1 đến 3 được tính là &lt;color=Highlight&gt;Heavy Attack DMG&lt;/color&gt;, và Sát thương từ Giai đoạn 4 &amp; 5 là &lt;color=Highlight&gt;Echo Skill DMG&lt;/color&gt;.
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack sau khi sử dụng &lt;color=Highlight&gt;Basic Attack - Seraphic Execution Stage 5&lt;/color&gt; để thực hiện &lt;color=Highlight&gt;Basic Attack - Seraphic Execution Stage 3&lt;/color&gt;.
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Normal Attack sau khi sử dụng &lt;color=Highlight&gt;Basic Attack - Seraphic Execution Stage 5&lt;/color&gt; để thực hiện &lt;color=Highlight&gt;Basic Attack - Seraphic Execution Stage 3&lt;/color&gt;.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Heavy Attack - Flamewing Verdict&lt;/color&gt;&lt;/size&gt;
 Tiêu hao STA để tấn công mục tiêu và thực hiện tối đa 3 đòn tấn công liên tiếp, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;. Tiêu hao &lt;color=Highlight&gt;&lt;te href=120803&gt;Purging Flame&lt;/te&gt;&lt;/color&gt; khi trúng đích. Sát thương từ Giai đoạn 3 được tính là &lt;color=Highlight&gt;Echo Skill DMG&lt;/color&gt;.
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack sau khi sử dụng &lt;color=Highlight&gt;Heavy Attack - Flamewing Verdict Stage 1&lt;/color&gt; để thực hiện &lt;color=Highlight&gt;Basic Attack - Seraphic Execution Stage 2&lt;/color&gt;.
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack sau khi sử dụng &lt;color=Highlight&gt;Heavy Attack - Flamewing Verdict Stage 2 &amp; 3&lt;/color&gt; để thực hiện &lt;color=Highlight&gt;Basic Attack - Seraphic Execution Stage 3&lt;/color&gt;.
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Normal Attack sau khi sử dụng &lt;color=Highlight&gt;Heavy Attack - Flamewing Verdict Stage 1&lt;/color&gt; để thực hiện &lt;color=Highlight&gt;Basic Attack - Seraphic Execution Stage 2&lt;/color&gt;.
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Normal Attack sau khi sử dụng &lt;color=Highlight&gt;Heavy Attack - Flamewing Verdict Stage 2 &amp; 3&lt;/color&gt; để thực hiện &lt;color=Highlight&gt;Basic Attack - Seraphic Execution Stage 3&lt;/color&gt;.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Mid-air Attack - Hellsent Barrage&lt;/color&gt;&lt;/size&gt;
-Khi ở giữa không, {Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack để tiêu hao STA và thực hiện đòn tấn công trên không, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;, được tính là &lt;color=Highlight&gt;Heavy Attack DMG&lt;/color&gt;. Tiêu hao &lt;color=Highlight&gt;&lt;te href=120803&gt;Purging Flame&lt;/te&gt;&lt;/color&gt; khi trúng đích.
+Khi ở giữa không, {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Normal Attack để tiêu hao STA và thực hiện đòn tấn công trên không, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;, được tính là &lt;color=Highlight&gt;Heavy Attack DMG&lt;/color&gt;. Tiêu hao &lt;color=Highlight&gt;&lt;te href=120803&gt;Purging Flame&lt;/te&gt;&lt;/color&gt; khi trúng đích.
 Khi ở giữa không, giữ Normal Attack để liên tục tiêu hao STA và bắn một loạt đạn vào mục tiêu, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;, được tính là &lt;color=Highlight&gt;Heavy Attack DMG&lt;/color&gt;. Tiêu hao &lt;color=Highlight&gt;&lt;te href=120803&gt;Purging Flame&lt;/te&gt;&lt;/color&gt; khi trúng đích. Nếu Galbrena không tiếp đất khi bị gián đoạn trong loạt đạn, cô không thể sử dụng kỹ năng này ngay lập tức. Thả Normal Attack trong loạt đạn để thực hiện Đòn Đòn Lao Xuống.
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack sau Đòn Đòn Lao Xuống để thực hiện &lt;color=Highlight&gt;Basic Attack - Seraphic Execution Stage 3&lt;/color&gt;.
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Normal Attack sau Đòn Đòn Lao Xuống để thực hiện &lt;color=Highlight&gt;Basic Attack - Seraphic Execution Stage 3&lt;/color&gt;.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Dodge Counter - Purgatory Scourge&lt;/color&gt;&lt;/size&gt;
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack ngay sau khi Dodge thành công để tấn công mục tiêu, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;, được tính là &lt;color=Highlight&gt;Heavy Attack DMG&lt;/color&gt;.
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack ngay sau khi sử dụng kỹ năng này để thực hiện &lt;color=Highlight&gt;Basic Attack - Seraphic Execution Stage 4&lt;/color&gt;.
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Normal Attack ngay sau khi Dodge thành công để tấn công mục tiêu, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;, được tính là &lt;color=Highlight&gt;Heavy Attack DMG&lt;/color&gt;.
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Normal Attack ngay sau khi sử dụng kỹ năng này để thực hiện &lt;color=Highlight&gt;Basic Attack - Seraphic Execution Stage 4&lt;/color&gt;.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Resonance Skill - Ravage&lt;/color&gt;&lt;/size&gt;
-Lao về phía trước và nhảy lên không. Lật người lại khi trúng mục tiêu, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;, được tính là &lt;color=Highlight&gt;Heavy Attack DMG&lt;/color&gt;. Tiêu hao &lt;color=Highlight&gt;&lt;te href=120803&gt;Purging Flame&lt;/te&gt;&lt;/color&gt; khi trúng đích. &lt;color=Highlight&gt;Resonance Skill - Ravage&lt;/color&gt; và &lt;color=Highlight&gt;Resonance Skill - Encroach&lt;/color&gt; chia sẻ Cooldown chiêu.
+Lao về phía trước và nhảy lên không. Lật người lại khi trúng mục tiêu, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;, được tính là &lt;color=Highlight&gt;Heavy Attack DMG&lt;/color&gt;. Tiêu hao &lt;color=Highlight&gt;&lt;te href=120803&gt;Purging Flame&lt;/te&gt;&lt;/color&gt; khi trúng đích. &lt;color=Highlight&gt;Resonance Skill - Ravage&lt;/color&gt; và &lt;color=Highlight&gt;Resonance Skill - Encroach&lt;/color&gt; chia sẻ Thời gian hồi chiêu.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Hellstride&lt;/color&gt;&lt;/size&gt;
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} Dodge trên mặt đất trong khi sử dụng &lt;color=Highlight&gt;Galbrena's own skills&lt;/color&gt; để thực hiện &lt;color=Highlight&gt;Hellstride&lt;/color&gt;, gây một lượng &lt;color=Fire&gt;Fusion DMG&lt;/color&gt; cố định, được tính là Sát Thương Basic Attack và không chịu ảnh hưởng từ các hiệu ứng tăng Sát Thương. &lt;color=Highlight&gt;Hellstride&lt;/color&gt; có thể kích hoạt Dodge thành công. &lt;color=Highlight&gt;Hellstride&lt;/color&gt; không thể sử dụng liên tiếp.
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Dodge trên mặt đất trong khi sử dụng &lt;color=Highlight&gt;Galbrena's own skills&lt;/color&gt; để thực hiện &lt;color=Highlight&gt;Hellstride&lt;/color&gt;, gây một lượng &lt;color=Fire&gt;Fusion DMG&lt;/color&gt; cố định, được tính là Sát Thương Basic Attack và không chịu ảnh hưởng từ các hiệu ứng tăng Sát Thương. &lt;color=Highlight&gt;Hellstride&lt;/color&gt; có thể kích hoạt Dodge thành công. &lt;color=Highlight&gt;Hellstride&lt;/color&gt; không thể sử dụng liên tiếp.
 Sử dụng kỹ năng này không làm reset chu kỳ tấn công trong một khoảng thời gian ngắn.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Burning Drive&lt;/color&gt;&lt;/size&gt;
@@ -32369,17 +32369,17 @@
 Tiêu hao STA để gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Enhanced Mid-air Attack&lt;/color&gt;&lt;/size&gt;
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack để tiêu hao STA, tăng cường Mid-air Attack, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Normal Attack để tiêu hao STA, tăng cường Mid-air Attack, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
 Giữ Normal Attack để liên tục tiêu hao STA, bắn loạt đạn vào mục tiêu, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;. Thả Normal Attack để thực hiện Đòn Lao Xuống tăng cường.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Enhanced Dodge Counter&lt;/color&gt;&lt;/size&gt;
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack ngay sau khi Dodge thành công để tấn công mục tiêu, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Normal Attack ngay sau khi Dodge thành công để tấn công mục tiêu, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Enhanced Resonance Skill&lt;/color&gt;&lt;/size&gt;
 Xông lên phía trước, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Hellstride&lt;/color&gt;&lt;/size&gt;
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} Dodge trong khi thực hiện hành động chiến đấu để gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} Dodge trong khi thực hiện hành động chiến đấu để gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;.
 Skills này không làm gián đoạn bộ đếm đòn của các giai đoạn Basic Attack và Heavy Attack.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Burning Drive&lt;/color&gt;&lt;/size&gt;
@@ -32663,13 +32663,13 @@
 Thực hiện tối đa 3 đòn tấn công liên tiếp, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Heavy Attack&lt;/color&gt;&lt;/size&gt;
-Tiêu hao STA để tấn công mục tiêu, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;. {Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; trong khoảng thời gian nhất định sau khi sử dụng kỹ năng này để thực hiện Basic Attack &lt;color=Highlight&gt;Thus Spoke the Blade: Inkwash&lt;/color&gt; Stage 4.
+Tiêu hao STA để tấn công mục tiêu, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;. {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; trong khoảng thời gian nhất định sau khi sử dụng kỹ năng này để thực hiện Basic Attack &lt;color=Highlight&gt;Thus Spoke the Blade: Inkwash&lt;/color&gt; Stage 4.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Mid-air Attack&lt;/color&gt;&lt;/size&gt;
 Tiêu hao STA để thực hiện Đòn Lao Xuống, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Dodge Counter&lt;/color&gt;&lt;/size&gt;
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi &lt;color=Highlight&gt;Dodge&lt;/color&gt; thành công để tấn công mục tiêu, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;, được tính là &lt;color=Highlight&gt;Heavy Attack&lt;/color&gt;.
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi &lt;color=Highlight&gt;Dodge&lt;/color&gt; thành công để tấn công mục tiêu, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;, được tính là &lt;color=Highlight&gt;Heavy Attack&lt;/color&gt;.
 Ngay sau khi thực hiện &lt;color=Highlight&gt;Basic Attack&lt;/color&gt; hoặc &lt;color=Highlight&gt;Heavy Attack&lt;/color&gt;, Qiuyuan sẽ miễn nhiễm với lần sát thương tiếp theo và tự động thực hiện &lt;color=Highlight&gt;Dodge Counter&lt;/color&gt; khi bị tấn công, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;.</t>
         </is>
       </c>
@@ -32825,7 +32825,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>{Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; để lao về phía trước một đoạn, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;, được tính là Sát Thương Kỹ Năng Vọng Âm. Nếu &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; được thi triển khi bị tấn công bởi mục tiêu địch, Qiuyuan sẽ miễn nhiễm với sát thương trong lần này và làm chậm kẻ địch xung quanh, đồng thời không bị gián đoạn trong quá trình thi triển &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt;.
+          <t>{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; để lao về phía trước một đoạn, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;, được tính là Sát Thương Kỹ Năng Vọng Âm. Nếu &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; được thi triển khi bị tấn công bởi mục tiêu địch, Qiuyuan sẽ miễn nhiễm với sát thương trong lần này và làm chậm kẻ địch xung quanh, đồng thời không bị gián đoạn trong quá trình thi triển &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt;.
 Chuyển sang Resonators khác sẽ loại bỏ hiệu ứng Trì Trệ khỏi kẻ địch.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Undaunted Wayfarer&lt;/color&gt;&lt;/size&gt;
@@ -33443,7 +33443,7 @@
       <c r="M484" t="inlineStr">
         <is>
           <t>Gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;.
-Trong một khoảng thời gian sau khi sử dụng kỹ năng này, {Cus:Ipt,Touch=tấn PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; để thực hiện Basic Attack &lt;color=Highlight&gt;Thus Spoke the Blade: Inkwash&lt;/color&gt; Stage 3.</t>
+Trong một khoảng thời gian sau khi sử dụng kỹ năng này, {Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; để thực hiện Basic Attack &lt;color=Highlight&gt;Thus Spoke the Blade: Inkwash&lt;/color&gt; Stage 3.</t>
         </is>
       </c>
     </row>
@@ -33537,7 +33537,7 @@
 Khi &lt;te href=141101&gt;Swordster's Soliloquy&lt;/te&gt; đạt tối đa, Qiuyuan sẽ bước vào trạng thái &lt;color=Highlight&gt;Inksplash of Mind&lt;/color&gt; trong {4} giây, trong đó &lt;color=Highlight&gt;Heavy Attack&lt;/color&gt; sẽ được thay thế bằng Heavy Attack &lt;color=Highlight&gt;Thus Spoke the Blade: To Save&lt;/color&gt;.
 Trong trạng thái này, giữ &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; để tiêu hao Swordster's Soliloquy, thực hiện lần lượt các Heavy Attack &lt;color=Highlight&gt;Thus Spoke the Blade: To Teach&lt;/color&gt;, &lt;color=Highlight&gt;Thus Spoke the Blade: To Save&lt;/color&gt; và &lt;color=Highlight&gt;Thus Spoke the Blade: To Sacrifice&lt;/color&gt;, gây &lt;color=Wind&gt;Aero DMG&lt;/color&gt;, được tính là Sát Thương Heavy Attack.
 - Thực hiện &lt;color=Highlight&gt;Thus Spoke the Blade: To Teach&lt;/color&gt;, &lt;color=Highlight&gt;Thus Spoke the Blade: To Save&lt;/color&gt; hoặc &lt;color=Highlight&gt;Thus Spoke the Blade: To Sacrifice&lt;/color&gt; được tính là sử dụng &lt;color=Highlight&gt;Echo Skill&lt;/color&gt;.
-- Trạng thái Dodget Mực Tâm Linh sẽ kết thúc khi Swordster's Soliloquy được sử dụng hết.
+- Trạng thái nét Mực Tâm Linh sẽ kết thúc khi Swordster's Soliloquy được sử dụng hết.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Swordster's Soliloquy&lt;/color&gt;&lt;/size&gt;
 Qiuyuan có thể tích lũy tối đa {5} điểm Swordster's Soliloquy.
@@ -33545,8 +33545,8 @@
 - Nhận được {7} điểm Swordster's Soliloquy khi thực hiện mỗi giai đoạn của Basic Attack &lt;color=Highlight&gt;Thus Spoke the Blade: Inkwash&lt;/color&gt;.
 - Nhận được {8} điểm Swordster's Soliloquy khi thực hiện &lt;color=Highlight&gt;Dodge Counter&lt;/color&gt;.
 - Nhận được {9} điểm Swordster's Soliloquy khi thực hiện &lt;color=Highlight&gt;Intro Skill&lt;/color&gt;.
-- Không thể tích lũy Swordster's Soliloquy trong trạng thái Dodget Mực Tâm Linh.
-- Swordster's Soliloquy sẽ bị xóa khi trạng thái Dodget Mực Tâm Linh kết thúc.</t>
+- Không thể tích lũy Swordster's Soliloquy trong trạng thái nét Mực Tâm Linh.
+- Swordster's Soliloquy sẽ bị xóa khi trạng thái nét Mực Tâm Linh kết thúc.</t>
         </is>
       </c>
     </row>
@@ -34017,18 +34017,18 @@
         <is>
           <t>&lt;size=40&gt;&lt;color=Title&gt;Basic Attack&lt;/color&gt;&lt;/size&gt;
 Thực hiện tối đa 2 đòn tấn công liên tiếp, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;.
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi sử dụng &lt;color=Highlight&gt;Basic Attack Stage 2&lt;/color&gt; để thi triển &lt;color=Highlight&gt;Rending Lunge&lt;/color&gt;.
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi sử dụng &lt;color=Highlight&gt;Basic Attack Stage 2&lt;/color&gt; để thi triển &lt;color=Highlight&gt;Rending Lunge&lt;/color&gt;.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Rending Lunge&lt;/color&gt;&lt;/size&gt;
 Gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;.
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi thi triển kỹ năng này trên mặt đất để sử dụng &lt;color=Highlight&gt;Death Snip&lt;/color&gt;.
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi thi triển kỹ năng này trên mặt đất để sử dụng &lt;color=Highlight&gt;Death Snip&lt;/color&gt;.
 Sử dụng &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi thi triển kỹ năng này giữa không trung để sử dụng &lt;color=Highlight&gt;Hanging Finality&lt;/color&gt;.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Death Snip&lt;/color&gt;&lt;/size&gt;
 Mở kéo, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;. Sau một lúc, kéo sẽ cắt xuống, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt; và hồi HP cho tất cả Resonators trong đội ở gần.
 Sử dụng &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; trong khi thi triển kỹ năng này để gây thêm &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;. Nhấn &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; lần nữa để cắt mục tiêu ngay lập tức.
 Sát thương của kỹ năng được tính là &lt;color=Highlight&gt;Resonance Liberation DMG&lt;/color&gt;.
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi thi triển &lt;color=Highlight&gt;Death Snip&lt;/color&gt; để sử dụng &lt;color=Highlight&gt;Thread Withdrawn&lt;/color&gt;.
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi thi triển &lt;color=Highlight&gt;Death Snip&lt;/color&gt; để sử dụng &lt;color=Highlight&gt;Thread Withdrawn&lt;/color&gt;.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Thread Withdrawn&lt;/color&gt;&lt;/size&gt;
 Gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;.
@@ -34038,13 +34038,13 @@
 Nhảy lên không và tiêu hao STA để tấn công mục tiêu, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;.
 Không thể thi triển kỹ năng này khi đang ở &lt;color=Highlight&gt;Chainsaw Mode&lt;/color&gt;.
 Thực hiện các hành động sau trong một khoảng thời gian nhất định sau khi thi triển kỹ năng này để sử dụng &lt;color=Highlight&gt;Hanging Finality&lt;/color&gt;:
-- {Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt;;
-- Thi triển &lt;color=Highlight&gt;Lifethread - Glide&lt;/color&gt; và {Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; trước khi tiếp đất.
+- {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt;;
+- Thi triển &lt;color=Highlight&gt;Lifethread - Glide&lt;/color&gt; và {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; trước khi tiếp đất.
 Giữ &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; trước khi tiếp đất sau khi thi triển &lt;color=Highlight&gt;Heavy Attack&lt;/color&gt; để sử dụng &lt;color=Highlight&gt;Heavy Attack - Severed Facet&lt;/color&gt;.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Mid-air Attack&lt;/color&gt;&lt;/size&gt;
 Tiêu hao STA để thực hiện Đòn Lao Xuống, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;.
-Khi không ở &lt;color=Highlight&gt;Chainsaw Mode&lt;/color&gt;, {Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; trong một khoảng thời gian nhất định sau khi thi triển Mid-air Attack Trung để sử dụng &lt;color=Highlight&gt;Basic Attack Stage 2&lt;/color&gt;.
+Khi không ở &lt;color=Highlight&gt;Chainsaw Mode&lt;/color&gt;, {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; trong một khoảng thời gian nhất định sau khi thi triển Mid-air Attack Trung để sử dụng &lt;color=Highlight&gt;Basic Attack Stage 2&lt;/color&gt;.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Heavy Attack - Severed Facet&lt;/color&gt;&lt;/size&gt;
 Gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;.
@@ -34053,16 +34053,16 @@
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Hanging Finality&lt;/color&gt;&lt;/size&gt;
 Tiêu hao STA để thực hiện Đòn Lao Xuống, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;.
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi thi triển kỹ năng này trên mặt đất để sử dụng &lt;color=Highlight&gt;Death Snip&lt;/color&gt;.
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi thi triển kỹ năng này trên mặt đất để sử dụng &lt;color=Highlight&gt;Death Snip&lt;/color&gt;.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Dodge Counter&lt;/color&gt;&lt;/size&gt;
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi &lt;color=Highlight&gt;Dodge&lt;/color&gt; thành công để tấn công mục tiêu, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;.
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi thi triển kỹ năng này để sử dụng &lt;color=Highlight&gt;Rending Lunge&lt;/color&gt;.
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi &lt;color=Highlight&gt;Dodge&lt;/color&gt; thành công để tấn công mục tiêu, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;.
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi thi triển kỹ năng này để sử dụng &lt;color=Highlight&gt;Rending Lunge&lt;/color&gt;.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Dodge Counter - Eye of Unraveling: Retraction&lt;/color&gt;&lt;/size&gt;
 Giữ &lt;color=Highlight&gt;Dodge&lt;/color&gt; sau khi &lt;color=Highlight&gt;Dodge&lt;/color&gt; thành công trên mặt đất để thi triển &lt;color=Highlight&gt;Dodge Counter - Eye of Unraveling: Retraction&lt;/color&gt;, tấn công và gây Trì Hoãn mục tiêu, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;.
-- Khi không ở &lt;color=Highlight&gt;Chainsaw Mode&lt;/color&gt;, sau khi thi triển kỹ năng này, {Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; trên mặt đất hoặc sử dụng &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; giữa không trung để sử dụng &lt;color=Highlight&gt;Rending Lunge&lt;/color&gt;. Hiệu ứng này sẽ bị loại bỏ khi Chisa vào &lt;color=Highlight&gt;Chainsaw Mode&lt;/color&gt;.
-- Khi ở &lt;color=Highlight&gt;Chainsaw Mode&lt;/color&gt;, {Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi thi triển kỹ năng này để sử dụng &lt;color=Highlight&gt;Sawring - Blitz Stage 3&lt;/color&gt;.</t>
+- Khi không ở &lt;color=Highlight&gt;Chainsaw Mode&lt;/color&gt;, sau khi thi triển kỹ năng này, {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; trên mặt đất hoặc sử dụng &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; giữa không trung để sử dụng &lt;color=Highlight&gt;Rending Lunge&lt;/color&gt;. Hiệu ứng này sẽ bị loại bỏ khi Chisa vào &lt;color=Highlight&gt;Chainsaw Mode&lt;/color&gt;.
+- Khi ở &lt;color=Highlight&gt;Chainsaw Mode&lt;/color&gt;, {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi thi triển kỹ năng này để sử dụng &lt;color=Highlight&gt;Sawring - Blitz Stage 3&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -34134,12 +34134,12 @@
       <c r="M492" t="inlineStr">
         <is>
           <t>&lt;size=40&gt;&lt;color=Title&gt;Rending Lunge&lt;/color&gt;&lt;/size&gt;
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi dùng &lt;color=Highlight&gt;Basic Attack Stage 2&lt;/color&gt; để thi triển &lt;color=Highlight&gt;Rending Lunge&lt;/color&gt;, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;. 
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi dùng kỹ năng này trên mặt đất để thi triển &lt;color=Highlight&gt;Death Snip&lt;/color&gt;.
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi dùng &lt;color=Highlight&gt;Basic Attack Stage 2&lt;/color&gt; để thi triển &lt;color=Highlight&gt;Rending Lunge&lt;/color&gt;, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;. 
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi dùng kỹ năng này trên mặt đất để thi triển &lt;color=Highlight&gt;Death Snip&lt;/color&gt;.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Death Snip&lt;/color&gt;&lt;/size&gt;
 Gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt; và phục hồi HP cho tất cả Resonators trong đội ở gần. 
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} hoặc giữ &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; trong khi dùng kỹ năng này để gây thêm &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;.</t>
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} hoặc giữ &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; trong khi dùng kỹ năng này để gây thêm &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -34217,15 +34217,15 @@
         <is>
           <t>&lt;size=40&gt;&lt;color=Title&gt;Eye of Unraveling&lt;/color&gt;&lt;/size&gt;
 Gây Trì Trệ và gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;.
-- Khi không ở trong &lt;color=Highlight&gt;Chainsaw Mode&lt;/color&gt;, sau khi sử dụng kỹ năng này, {Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; trên mặt đất hoặc sử dụng &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; giữa không trung để tung ra &lt;color=Highlight&gt;Rending Lunge&lt;/color&gt;. Hiệu ứng này sẽ bị loại bỏ khi Chisa bước vào &lt;color=Highlight&gt;Chainsaw Mode&lt;/color&gt;.
-- Khi ở trong &lt;color=Highlight&gt;Chainsaw Mode&lt;/color&gt; và trên mặt đất, {Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi sử dụng kỹ năng này để tung ra &lt;color=Highlight&gt;Sawring - Blitz Stage 2&lt;/color&gt;.
+- Khi không ở trong &lt;color=Highlight&gt;Chainsaw Mode&lt;/color&gt;, sau khi sử dụng kỹ năng này, {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; trên mặt đất hoặc sử dụng &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; giữa không trung để tung ra &lt;color=Highlight&gt;Rending Lunge&lt;/color&gt;. Hiệu ứng này sẽ bị loại bỏ khi Chisa bước vào &lt;color=Highlight&gt;Chainsaw Mode&lt;/color&gt;.
+- Khi ở trong &lt;color=Highlight&gt;Chainsaw Mode&lt;/color&gt; và trên mặt đất, {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi sử dụng kỹ năng này để tung ra &lt;color=Highlight&gt;Sawring - Blitz Stage 2&lt;/color&gt;.
 Có thể sử dụng giữa không trung.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Serrated Loop&lt;/color&gt;&lt;/size&gt;
 Khi ở trên mặt đất và &lt;color=Highlight&gt;&lt;te href=150803&gt;Ring of Chainsaw&lt;/te&gt;&lt;/color&gt; đã đầy, &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; sẽ được thay thế bằng &lt;color=Highlight&gt;Serrated Loop&lt;/color&gt;.
 Gây Trì Trệ cho mục tiêu, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt; và kéo các mục tiêu gần đó về.
 Sử dụng kỹ năng này sẽ đưa Chisa vào &lt;color=Highlight&gt;Chainsaw Mode&lt;/color&gt; và thay thế &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; bằng &lt;color=Highlight&gt;Eye of Unraveling&lt;/color&gt;.
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi sử dụng kỹ năng này để tung ra &lt;color=Highlight&gt;Sawring - Blitz Stage 2&lt;/color&gt;.
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi sử dụng kỹ năng này để tung ra &lt;color=Highlight&gt;Sawring - Blitz Stage 2&lt;/color&gt;.
 Giữ &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; khi sử dụng kỹ năng này để tấn công liên tục và kéo các mục tiêu gần đó về. Thả nút &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; trong khoảng thời gian này hoặc giữ nút trong một khoảng thời gian nhất định để tung ra &lt;color=Highlight&gt;Sawring - Blitz Stage 1&lt;/color&gt;.</t>
         </is>
       </c>
@@ -34530,7 +34530,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>Khi một Resonator trong đội tiêu diệt mục tiêu bị đánh dấu bởi &lt;color=Highlight&gt;&lt;te href=150801&gt;Unseen Snare&lt;/te&gt;&lt;/color&gt;, Cooldown chiêu của Resonance Skill &lt;color=Highlight&gt;Eye of Unraveling&lt;/color&gt; của Chisa sẽ được đặt lại, hiệu ứng này chỉ có thể kích hoạt tối đa một lần mỗi {0} giây.</t>
+          <t>Khi một Resonator trong đội tiêu diệt mục tiêu bị đánh dấu bởi &lt;color=Highlight&gt;&lt;te href=150801&gt;Unseen Snare&lt;/te&gt;&lt;/color&gt;, Thời gian hồi chiêu của Resonance Skill &lt;color=Highlight&gt;Eye of Unraveling&lt;/color&gt; của Chisa sẽ được đặt lại, hiệu ứng này chỉ có thể kích hoạt tối đa một lần mỗi {0} giây.</t>
         </is>
       </c>
     </row>
@@ -34595,7 +34595,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>Khi một Resonator trong đội tiêu diệt mục tiêu &lt;color=Highlight&gt;marked&lt;/color&gt;, Cooldown chiêu của &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; của Chisa sẽ được đặt lại.</t>
+          <t>Khi một Resonator trong đội tiêu diệt mục tiêu &lt;color=Highlight&gt;marked&lt;/color&gt;, Thời gian hồi chiêu của &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; của Chisa sẽ được đặt lại.</t>
         </is>
       </c>
     </row>
